--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>text</t>
   </si>
@@ -81,13 +81,79 @@
   <si>
     <t>刷新塞莱梅</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷心菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>茄子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马铃薯</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>芜菁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萝卜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大葱</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣椒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大蒜</t>
+  </si>
+  <si>
+    <t>草莓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +165,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -123,10 +196,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -408,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -524,6 +603,550 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H5" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="H7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1005</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1005</v>
+      </c>
+      <c r="H9" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1006</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1006</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1007</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1007</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1008</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1008</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1009</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1009</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1010</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1010</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1011</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1011</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1012</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1012</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1013</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1013</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1014</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1014</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1015</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1015</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1016</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1016</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1017</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1017</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="GameRandomData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>text</t>
   </si>
@@ -147,6 +147,42 @@
   <si>
     <t>草莓</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜欢礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不喜欢礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜欢礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不喜欢礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不喜欢礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认礼物对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不喜欢礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -196,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -205,6 +241,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -487,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1147,6 +1186,557 @@
         <v>2</v>
       </c>
     </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>6000</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>6001</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>6001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4">
+        <v>6002</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>6002</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4">
+        <v>6003</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>6003</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4">
+        <v>6004</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>6004</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4">
+        <v>6005</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>6005</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4">
+        <v>6006</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>6006</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>30</v>
+      </c>
+      <c r="H29" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>8</v>
+      </c>
+      <c r="H30" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
+        <v>12</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>24</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>25</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1">
+        <v>19</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>19</v>
+      </c>
+      <c r="H36" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="1">
+        <v>30004</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <v>6007</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>6007</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1">
+        <v>4</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4</v>
+      </c>
+      <c r="H38" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>17</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -652,8 +652,8 @@
       <c r="C5" s="1">
         <v>0</v>
       </c>
-      <c r="D5" s="2">
-        <v>1001</v>
+      <c r="D5" s="1">
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -684,8 +684,8 @@
       <c r="C6" s="1">
         <v>0</v>
       </c>
-      <c r="D6" s="2">
-        <v>1002</v>
+      <c r="D6" s="1">
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>20</v>
@@ -716,8 +716,8 @@
       <c r="C7" s="1">
         <v>0</v>
       </c>
-      <c r="D7" s="2">
-        <v>1003</v>
+      <c r="D7" s="1">
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>21</v>
@@ -748,8 +748,8 @@
       <c r="C8" s="1">
         <v>0</v>
       </c>
-      <c r="D8" s="2">
-        <v>1004</v>
+      <c r="D8" s="1">
+        <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>22</v>
@@ -780,8 +780,8 @@
       <c r="C9" s="1">
         <v>0</v>
       </c>
-      <c r="D9" s="2">
-        <v>1005</v>
+      <c r="D9" s="1">
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>23</v>
@@ -812,8 +812,8 @@
       <c r="C10" s="1">
         <v>0</v>
       </c>
-      <c r="D10" s="2">
-        <v>1006</v>
+      <c r="D10" s="1">
+        <v>7</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>24</v>
@@ -844,8 +844,8 @@
       <c r="C11" s="1">
         <v>0</v>
       </c>
-      <c r="D11" s="2">
-        <v>1007</v>
+      <c r="D11" s="1">
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -876,8 +876,8 @@
       <c r="C12" s="1">
         <v>0</v>
       </c>
-      <c r="D12" s="2">
-        <v>1008</v>
+      <c r="D12" s="1">
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -908,8 +908,8 @@
       <c r="C13" s="1">
         <v>0</v>
       </c>
-      <c r="D13" s="2">
-        <v>1009</v>
+      <c r="D13" s="1">
+        <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -940,8 +940,8 @@
       <c r="C14" s="1">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>1010</v>
+      <c r="D14" s="1">
+        <v>11</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>28</v>
@@ -972,8 +972,8 @@
       <c r="C15" s="1">
         <v>0</v>
       </c>
-      <c r="D15" s="2">
-        <v>1011</v>
+      <c r="D15" s="1">
+        <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
@@ -1004,8 +1004,8 @@
       <c r="C16" s="1">
         <v>0</v>
       </c>
-      <c r="D16" s="2">
-        <v>1012</v>
+      <c r="D16" s="1">
+        <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>30</v>
@@ -1036,8 +1036,8 @@
       <c r="C17" s="1">
         <v>0</v>
       </c>
-      <c r="D17" s="2">
-        <v>1013</v>
+      <c r="D17" s="1">
+        <v>14</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>31</v>
@@ -1068,8 +1068,8 @@
       <c r="C18" s="1">
         <v>0</v>
       </c>
-      <c r="D18" s="2">
-        <v>1014</v>
+      <c r="D18" s="1">
+        <v>15</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>32</v>
@@ -1100,8 +1100,8 @@
       <c r="C19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="2">
-        <v>1015</v>
+      <c r="D19" s="1">
+        <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>33</v>
@@ -1132,8 +1132,8 @@
       <c r="C20" s="1">
         <v>0</v>
       </c>
-      <c r="D20" s="2">
-        <v>1016</v>
+      <c r="D20" s="1">
+        <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>34</v>
@@ -1164,8 +1164,8 @@
       <c r="C21" s="1">
         <v>0</v>
       </c>
-      <c r="D21" s="2">
-        <v>1017</v>
+      <c r="D21" s="1">
+        <v>18</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>35</v>
@@ -1196,8 +1196,8 @@
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="4">
-        <v>6000</v>
+      <c r="D22" s="1">
+        <v>19</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1225,8 +1225,8 @@
       <c r="C23" s="1">
         <v>1</v>
       </c>
-      <c r="D23" s="4">
-        <v>6001</v>
+      <c r="D23" s="1">
+        <v>20</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1254,8 +1254,8 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="4">
-        <v>6002</v>
+      <c r="D24" s="1">
+        <v>21</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1283,8 +1283,8 @@
       <c r="C25" s="1">
         <v>1</v>
       </c>
-      <c r="D25" s="4">
-        <v>6003</v>
+      <c r="D25" s="1">
+        <v>22</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1312,8 +1312,8 @@
       <c r="C26" s="1">
         <v>1</v>
       </c>
-      <c r="D26" s="4">
-        <v>6004</v>
+      <c r="D26" s="1">
+        <v>23</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1341,8 +1341,8 @@
       <c r="C27" s="1">
         <v>1</v>
       </c>
-      <c r="D27" s="4">
-        <v>6005</v>
+      <c r="D27" s="1">
+        <v>24</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1370,8 +1370,8 @@
       <c r="C28" s="1">
         <v>1</v>
       </c>
-      <c r="D28" s="4">
-        <v>6006</v>
+      <c r="D28" s="1">
+        <v>25</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="1">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1">
-        <v>6007</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="1">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="100">
   <si>
     <t>text</t>
   </si>
@@ -182,6 +182,199 @@
   </si>
   <si>
     <t>默认礼物表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海边鱼池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山地鱼池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城市鱼池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场鱼池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门鱼池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>蛤蜊</t>
+  </si>
+  <si>
+    <t>海鳗</t>
+  </si>
+  <si>
+    <t>扇贝</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>牡蛎</t>
+  </si>
+  <si>
+    <t>𩽾𩾌</t>
+  </si>
+  <si>
+    <t>河豚鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>溪鳟鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>线鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小龙虾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥鳅</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>小龙虾</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>梭鲈</t>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥鳅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭鲈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -189,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +403,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -232,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -245,6 +451,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,11 +738,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="1" customWidth="1"/>
     <col min="4" max="5" width="13.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
@@ -1737,6 +1949,1734 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>38</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1100</v>
+      </c>
+      <c r="H41" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>39</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>1101</v>
+      </c>
+      <c r="H42" s="1">
+        <v>9500</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>40</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1102</v>
+      </c>
+      <c r="H43" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>41</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1103</v>
+      </c>
+      <c r="H44" s="1">
+        <v>8500</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>42</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1104</v>
+      </c>
+      <c r="H45" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>43</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1105</v>
+      </c>
+      <c r="H46" s="1">
+        <v>7500</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1">
+        <v>44</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>1106</v>
+      </c>
+      <c r="H47" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>45</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1107</v>
+      </c>
+      <c r="H48" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1">
+        <v>46</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1108</v>
+      </c>
+      <c r="H49" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1">
+        <v>47</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1109</v>
+      </c>
+      <c r="H50" s="1">
+        <v>5500</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1">
+        <v>48</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1110</v>
+      </c>
+      <c r="H51" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1">
+        <v>49</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1111</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1">
+        <v>50</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>1112</v>
+      </c>
+      <c r="H53" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1">
+        <v>51</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1113</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1">
+        <v>52</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1114</v>
+      </c>
+      <c r="H55" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="1">
+        <v>53</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1115</v>
+      </c>
+      <c r="H56" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="1">
+        <v>54</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1116</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" s="1">
+        <v>40000</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1">
+        <v>55</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1117</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1">
+        <v>56</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1005</v>
+      </c>
+      <c r="H59" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1">
+        <v>57</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1007</v>
+      </c>
+      <c r="H60" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1">
+        <v>58</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1009</v>
+      </c>
+      <c r="H61" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1">
+        <v>59</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1011</v>
+      </c>
+      <c r="H62" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1">
+        <v>60</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1014</v>
+      </c>
+      <c r="H63" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1">
+        <v>61</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1016</v>
+      </c>
+      <c r="H64" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1">
+        <v>62</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1017</v>
+      </c>
+      <c r="H65" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1">
+        <v>63</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1022</v>
+      </c>
+      <c r="H66" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B67" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1">
+        <v>64</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1024</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1">
+        <v>65</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H68" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1">
+        <v>66</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1002</v>
+      </c>
+      <c r="H69" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B70" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="1">
+        <v>67</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H70" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B71" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1">
+        <v>68</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1008</v>
+      </c>
+      <c r="H71" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B72" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="1">
+        <v>69</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1010</v>
+      </c>
+      <c r="H72" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B73" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1">
+        <v>70</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1013</v>
+      </c>
+      <c r="H73" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="1">
+        <v>71</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1018</v>
+      </c>
+      <c r="H74" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B75" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="1">
+        <v>72</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1020</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B76" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="1">
+        <v>73</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>1023</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="1">
+        <v>74</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H77" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+      <c r="D78" s="1">
+        <v>75</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H78" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1</v>
+      </c>
+      <c r="D79" s="1">
+        <v>76</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1002</v>
+      </c>
+      <c r="H79" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B80" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="1">
+        <v>77</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H80" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="1">
+        <v>78</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1006</v>
+      </c>
+      <c r="H81" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B82" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="1">
+        <v>79</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1007</v>
+      </c>
+      <c r="H82" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I82" s="1">
+        <v>1</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B83" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="1">
+        <v>80</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1012</v>
+      </c>
+      <c r="H83" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1">
+        <v>81</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1019</v>
+      </c>
+      <c r="H84" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="1">
+        <v>40003</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="1">
+        <v>82</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>1020</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I85" s="1">
+        <v>1</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="1">
+        <v>83</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H86" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="1">
+        <v>84</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H87" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I87" s="1">
+        <v>1</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="1">
+        <v>85</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H88" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="1">
+        <v>86</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>1006</v>
+      </c>
+      <c r="H89" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I89" s="1">
+        <v>1</v>
+      </c>
+      <c r="J89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B90" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" s="1">
+        <v>87</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>1007</v>
+      </c>
+      <c r="H90" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B91" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="1">
+        <v>88</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>1012</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B92" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="1">
+        <v>89</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>1015</v>
+      </c>
+      <c r="H92" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="1">
+        <v>90</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>1019</v>
+      </c>
+      <c r="H93" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="1">
+        <v>91</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>1021</v>
+      </c>
+      <c r="H94" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I94" s="1">
+        <v>1</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -790,7 +790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1975,10 +1975,10 @@
         <v>10000</v>
       </c>
       <c r="I41" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J41" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2007,10 +2007,10 @@
         <v>9500</v>
       </c>
       <c r="I42" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J42" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -2039,10 +2039,10 @@
         <v>9000</v>
       </c>
       <c r="I43" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J43" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -2071,10 +2071,10 @@
         <v>8500</v>
       </c>
       <c r="I44" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -2103,10 +2103,10 @@
         <v>8000</v>
       </c>
       <c r="I45" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J45" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -2135,10 +2135,10 @@
         <v>7500</v>
       </c>
       <c r="I46" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J46" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2167,10 +2167,10 @@
         <v>7000</v>
       </c>
       <c r="I47" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -2199,10 +2199,10 @@
         <v>6500</v>
       </c>
       <c r="I48" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -2231,10 +2231,10 @@
         <v>6000</v>
       </c>
       <c r="I49" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -2263,10 +2263,10 @@
         <v>5500</v>
       </c>
       <c r="I50" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2295,10 +2295,10 @@
         <v>5000</v>
       </c>
       <c r="I51" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J51" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -2327,10 +2327,10 @@
         <v>4500</v>
       </c>
       <c r="I52" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
@@ -2359,10 +2359,10 @@
         <v>4000</v>
       </c>
       <c r="I53" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J53" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
@@ -2391,10 +2391,10 @@
         <v>3500</v>
       </c>
       <c r="I54" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J54" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
@@ -2423,10 +2423,10 @@
         <v>3000</v>
       </c>
       <c r="I55" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2455,10 +2455,10 @@
         <v>2500</v>
       </c>
       <c r="I56" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -2487,10 +2487,10 @@
         <v>2000</v>
       </c>
       <c r="I57" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J57" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -2519,10 +2519,10 @@
         <v>1500</v>
       </c>
       <c r="I58" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J58" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
@@ -2551,10 +2551,10 @@
         <v>10000</v>
       </c>
       <c r="I59" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J59" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -2583,10 +2583,10 @@
         <v>9000</v>
       </c>
       <c r="I60" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J60" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
@@ -2615,10 +2615,10 @@
         <v>8000</v>
       </c>
       <c r="I61" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J61" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -2647,10 +2647,10 @@
         <v>7000</v>
       </c>
       <c r="I62" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -2679,10 +2679,10 @@
         <v>6000</v>
       </c>
       <c r="I63" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J63" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -2711,10 +2711,10 @@
         <v>5000</v>
       </c>
       <c r="I64" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J64" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
@@ -2743,10 +2743,10 @@
         <v>4000</v>
       </c>
       <c r="I65" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J65" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
@@ -2775,10 +2775,10 @@
         <v>3000</v>
       </c>
       <c r="I66" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J66" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
@@ -2807,10 +2807,10 @@
         <v>2000</v>
       </c>
       <c r="I67" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J67" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -2839,10 +2839,10 @@
         <v>10000</v>
       </c>
       <c r="I68" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J68" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
@@ -2871,10 +2871,10 @@
         <v>9000</v>
       </c>
       <c r="I69" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J69" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
@@ -2903,10 +2903,10 @@
         <v>8000</v>
       </c>
       <c r="I70" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J70" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -2935,10 +2935,10 @@
         <v>7000</v>
       </c>
       <c r="I71" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J71" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -2967,10 +2967,10 @@
         <v>6000</v>
       </c>
       <c r="I72" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J72" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
@@ -2999,10 +2999,10 @@
         <v>5000</v>
       </c>
       <c r="I73" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J73" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -3031,10 +3031,10 @@
         <v>4000</v>
       </c>
       <c r="I74" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J74" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -3063,10 +3063,10 @@
         <v>3000</v>
       </c>
       <c r="I75" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J75" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
@@ -3095,10 +3095,10 @@
         <v>2000</v>
       </c>
       <c r="I76" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J76" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
@@ -3127,10 +3127,10 @@
         <v>10000</v>
       </c>
       <c r="I77" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J77" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
@@ -3159,10 +3159,10 @@
         <v>9000</v>
       </c>
       <c r="I78" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
@@ -3191,10 +3191,10 @@
         <v>8000</v>
       </c>
       <c r="I79" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J79" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
@@ -3223,10 +3223,10 @@
         <v>7000</v>
       </c>
       <c r="I80" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J80" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
@@ -3255,10 +3255,10 @@
         <v>6000</v>
       </c>
       <c r="I81" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J81" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
@@ -3287,10 +3287,10 @@
         <v>5000</v>
       </c>
       <c r="I82" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J82" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
@@ -3319,10 +3319,10 @@
         <v>4000</v>
       </c>
       <c r="I83" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J83" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
@@ -3351,10 +3351,10 @@
         <v>3000</v>
       </c>
       <c r="I84" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J84" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
@@ -3383,10 +3383,10 @@
         <v>2000</v>
       </c>
       <c r="I85" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J85" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -3415,10 +3415,10 @@
         <v>10000</v>
       </c>
       <c r="I86" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J86" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -3447,10 +3447,10 @@
         <v>9000</v>
       </c>
       <c r="I87" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J87" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
@@ -3479,10 +3479,10 @@
         <v>8000</v>
       </c>
       <c r="I88" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J88" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
@@ -3511,10 +3511,10 @@
         <v>7000</v>
       </c>
       <c r="I89" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3543,10 +3543,10 @@
         <v>6000</v>
       </c>
       <c r="I90" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J90" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
@@ -3575,10 +3575,10 @@
         <v>5000</v>
       </c>
       <c r="I91" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J91" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
@@ -3607,10 +3607,10 @@
         <v>4000</v>
       </c>
       <c r="I92" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J92" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
@@ -3639,10 +3639,10 @@
         <v>3000</v>
       </c>
       <c r="I93" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J93" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
@@ -3671,10 +3671,10 @@
         <v>2000</v>
       </c>
       <c r="I94" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J94" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="GameRandomData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="101">
   <si>
     <t>text</t>
   </si>
@@ -211,26 +212,10 @@
     <t>竹荚鱼</t>
   </si>
   <si>
-    <t>蛤蜊</t>
-  </si>
-  <si>
     <t>海鳗</t>
   </si>
   <si>
-    <t>扇贝</t>
-  </si>
-  <si>
-    <t>鱿鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>比目鱼</t>
-  </si>
-  <si>
-    <t>牡蛎</t>
-  </si>
-  <si>
-    <t>𩽾𩾌</t>
   </si>
   <si>
     <t>河豚鱼</t>
@@ -261,7 +246,65 @@
     <t>斑马狮子鱼</t>
   </si>
   <si>
-    <t>溪鳟鱼</t>
+    <t>丁鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>线鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -269,120 +312,75 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>丁鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>线鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>樱桃鲑鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲷鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孔雀鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>洞穴天使鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龙虾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>锦鲤</t>
-  </si>
-  <si>
-    <t>兰寿金鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-  </si>
-  <si>
-    <t>银龙鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>泥鳅</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>小龙虾</t>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-  </si>
-  <si>
-    <t>梭鲈</t>
-  </si>
-  <si>
-    <t>罗非鱼</t>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>泥鳅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>梭鲈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>虹鳟鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>罗非鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鲑鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>fishName</t>
+  </si>
+  <si>
+    <t>丁鱼</t>
+  </si>
+  <si>
+    <t>线鱼</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,20 +408,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -438,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -455,7 +464,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -738,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1949,1118 +1970,1153 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="8">
         <v>40000</v>
       </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1">
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8">
         <v>38</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41">
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <f>VLOOKUP(E41,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1100</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="8">
         <v>10000</v>
       </c>
-      <c r="I41" s="1">
-        <v>10</v>
-      </c>
-      <c r="J41" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="I41" s="8">
+        <v>10</v>
+      </c>
+      <c r="J41" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="8">
         <v>40000</v>
       </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8">
         <v>39</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42">
+      <c r="F42" s="8">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <f>VLOOKUP(E42,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1101</v>
       </c>
-      <c r="H42" s="1">
-        <v>9500</v>
-      </c>
-      <c r="I42" s="1">
-        <v>10</v>
-      </c>
-      <c r="J42" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+      <c r="H42" s="8">
+        <v>9400</v>
+      </c>
+      <c r="I42" s="8">
+        <v>10</v>
+      </c>
+      <c r="J42" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="8">
         <v>40000</v>
       </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8">
         <v>40</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>1102</v>
-      </c>
-      <c r="H43" s="1">
-        <v>9000</v>
-      </c>
-      <c r="I43" s="1">
-        <v>10</v>
-      </c>
-      <c r="J43" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+      <c r="F43" s="8">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9">
+        <f>VLOOKUP(E43,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1103</v>
+      </c>
+      <c r="H43" s="8">
+        <v>8800</v>
+      </c>
+      <c r="I43" s="8">
+        <v>10</v>
+      </c>
+      <c r="J43" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="8">
         <v>40000</v>
       </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8">
         <v>41</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <f>VLOOKUP(E44,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1105</v>
+      </c>
+      <c r="H44" s="8">
+        <v>8200</v>
+      </c>
+      <c r="I44" s="8">
+        <v>10</v>
+      </c>
+      <c r="J44" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8">
+        <v>42</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>1103</v>
-      </c>
-      <c r="H44" s="1">
-        <v>8500</v>
-      </c>
-      <c r="I44" s="1">
-        <v>10</v>
-      </c>
-      <c r="J44" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="F45" s="8">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9">
+        <f>VLOOKUP(E45,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1106</v>
+      </c>
+      <c r="H45" s="8">
+        <v>7600</v>
+      </c>
+      <c r="I45" s="8">
+        <v>10</v>
+      </c>
+      <c r="J45" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B46" s="8">
         <v>40000</v>
       </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1">
-        <v>42</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8">
+        <v>43</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>1104</v>
-      </c>
-      <c r="H45" s="1">
-        <v>8000</v>
-      </c>
-      <c r="I45" s="1">
-        <v>10</v>
-      </c>
-      <c r="J45" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="F46" s="8">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <f>VLOOKUP(E46,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1109</v>
+      </c>
+      <c r="H46" s="8">
+        <v>7000</v>
+      </c>
+      <c r="I46" s="8">
+        <v>10</v>
+      </c>
+      <c r="J46" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B47" s="8">
         <v>40000</v>
       </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1">
-        <v>43</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8">
+        <v>44</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>1105</v>
-      </c>
-      <c r="H46" s="1">
-        <v>7500</v>
-      </c>
-      <c r="I46" s="1">
-        <v>10</v>
-      </c>
-      <c r="J46" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <f>VLOOKUP(E47,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1110</v>
+      </c>
+      <c r="H47" s="8">
+        <v>6400</v>
+      </c>
+      <c r="I47" s="8">
+        <v>10</v>
+      </c>
+      <c r="J47" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B48" s="8">
         <v>40000</v>
       </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" s="1">
-        <v>44</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8">
+        <v>45</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>1106</v>
-      </c>
-      <c r="H47" s="1">
-        <v>7000</v>
-      </c>
-      <c r="I47" s="1">
-        <v>10</v>
-      </c>
-      <c r="J47" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="F48" s="8">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <f>VLOOKUP(E48,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1111</v>
+      </c>
+      <c r="H48" s="8">
+        <v>5800</v>
+      </c>
+      <c r="I48" s="8">
+        <v>10</v>
+      </c>
+      <c r="J48" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B49" s="8">
         <v>40000</v>
       </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+      <c r="D49" s="8">
+        <v>46</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <f>VLOOKUP(E49,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1112</v>
+      </c>
+      <c r="H49" s="8">
+        <v>5200</v>
+      </c>
+      <c r="I49" s="8">
+        <v>10</v>
+      </c>
+      <c r="J49" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="B50" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+      <c r="D50" s="8">
+        <v>47</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="8">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <f>VLOOKUP(E50,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1113</v>
+      </c>
+      <c r="H50" s="8">
+        <v>4600</v>
+      </c>
+      <c r="I50" s="8">
+        <v>10</v>
+      </c>
+      <c r="J50" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8">
+        <v>48</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <f>VLOOKUP(E51,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1114</v>
+      </c>
+      <c r="H51" s="8">
+        <v>4000</v>
+      </c>
+      <c r="I51" s="8">
+        <v>10</v>
+      </c>
+      <c r="J51" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+      <c r="D52" s="8">
+        <v>49</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" s="8">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <f>VLOOKUP(E52,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1115</v>
+      </c>
+      <c r="H52" s="8">
+        <v>3400</v>
+      </c>
+      <c r="I52" s="8">
+        <v>10</v>
+      </c>
+      <c r="J52" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+      <c r="D53" s="8">
+        <v>50</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <f>VLOOKUP(E53,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1116</v>
+      </c>
+      <c r="H53" s="8">
+        <v>2800</v>
+      </c>
+      <c r="I53" s="8">
+        <v>10</v>
+      </c>
+      <c r="J53" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8">
+        <v>51</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" s="8">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <f>VLOOKUP(E54,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1117</v>
+      </c>
+      <c r="H54" s="8">
+        <v>2200</v>
+      </c>
+      <c r="I54" s="8">
+        <v>10</v>
+      </c>
+      <c r="J54" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C55" s="10">
+        <v>1</v>
+      </c>
+      <c r="D55" s="10">
+        <v>53</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0</v>
+      </c>
+      <c r="G55" s="11">
+        <f>VLOOKUP(E55,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1009</v>
+      </c>
+      <c r="H55" s="10">
+        <v>8800</v>
+      </c>
+      <c r="I55" s="10">
+        <v>10</v>
+      </c>
+      <c r="J55" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C56" s="10">
+        <v>1</v>
+      </c>
+      <c r="D56" s="10">
+        <v>54</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" s="10">
+        <v>0</v>
+      </c>
+      <c r="G56" s="11">
+        <f>VLOOKUP(E56,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1011</v>
+      </c>
+      <c r="H56" s="10">
+        <v>7600</v>
+      </c>
+      <c r="I56" s="10">
+        <v>10</v>
+      </c>
+      <c r="J56" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C57" s="10">
+        <v>1</v>
+      </c>
+      <c r="D57" s="10">
+        <v>55</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F57" s="10">
+        <v>0</v>
+      </c>
+      <c r="G57" s="11">
+        <f>VLOOKUP(E57,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1014</v>
+      </c>
+      <c r="H57" s="10">
+        <v>6400</v>
+      </c>
+      <c r="I57" s="10">
+        <v>10</v>
+      </c>
+      <c r="J57" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C58" s="10">
+        <v>1</v>
+      </c>
+      <c r="D58" s="10">
+        <v>56</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0</v>
+      </c>
+      <c r="G58" s="11">
+        <f>VLOOKUP(E58,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1016</v>
+      </c>
+      <c r="H58" s="10">
+        <v>5200</v>
+      </c>
+      <c r="I58" s="10">
+        <v>10</v>
+      </c>
+      <c r="J58" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C59" s="10">
+        <v>1</v>
+      </c>
+      <c r="D59" s="10">
         <v>57</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>1107</v>
-      </c>
-      <c r="H48" s="1">
-        <v>6500</v>
-      </c>
-      <c r="I48" s="1">
-        <v>10</v>
-      </c>
-      <c r="J48" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="E59" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" s="10">
+        <v>0</v>
+      </c>
+      <c r="G59" s="11">
+        <f>VLOOKUP(E59,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1017</v>
+      </c>
+      <c r="H59" s="10">
+        <v>4000</v>
+      </c>
+      <c r="I59" s="10">
+        <v>10</v>
+      </c>
+      <c r="J59" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="B60" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C60" s="10">
+        <v>1</v>
+      </c>
+      <c r="D60" s="10">
         <v>58</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>1108</v>
-      </c>
-      <c r="H49" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I49" s="1">
-        <v>10</v>
-      </c>
-      <c r="J49" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="E60" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0</v>
+      </c>
+      <c r="G60" s="11">
+        <f>VLOOKUP(E60,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1022</v>
+      </c>
+      <c r="H60" s="10">
+        <v>2800</v>
+      </c>
+      <c r="I60" s="10">
+        <v>10</v>
+      </c>
+      <c r="J60" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="10">
+        <v>40001</v>
+      </c>
+      <c r="C61" s="10">
+        <v>1</v>
+      </c>
+      <c r="D61" s="10">
+        <v>59</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0</v>
+      </c>
+      <c r="G61" s="11">
+        <f>VLOOKUP(E61,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1024</v>
+      </c>
+      <c r="H61" s="10">
+        <v>1600</v>
+      </c>
+      <c r="I61" s="10">
+        <v>10</v>
+      </c>
+      <c r="J61" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>1109</v>
-      </c>
-      <c r="H50" s="1">
-        <v>5500</v>
-      </c>
-      <c r="I50" s="1">
-        <v>10</v>
-      </c>
-      <c r="J50" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C51" s="1">
-        <v>1</v>
-      </c>
-      <c r="D51" s="1">
+      <c r="B62" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1</v>
+      </c>
+      <c r="D62" s="6">
+        <v>60</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7">
+        <f>VLOOKUP(E62,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="H62" s="6">
+        <v>10000</v>
+      </c>
+      <c r="I62" s="6">
+        <v>10</v>
+      </c>
+      <c r="J62" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C63" s="6">
+        <v>1</v>
+      </c>
+      <c r="D63" s="6">
+        <v>62</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" s="7">
+        <f>VLOOKUP(E63,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
+      </c>
+      <c r="H63" s="6">
+        <v>7200</v>
+      </c>
+      <c r="I63" s="6">
+        <v>10</v>
+      </c>
+      <c r="J63" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B64" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C64" s="6">
+        <v>1</v>
+      </c>
+      <c r="D64" s="6">
+        <v>63</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="6">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7">
+        <f>VLOOKUP(E64,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1013</v>
+      </c>
+      <c r="H64" s="6">
+        <v>5800</v>
+      </c>
+      <c r="I64" s="6">
+        <v>10</v>
+      </c>
+      <c r="J64" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6">
+        <v>64</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7">
+        <f>VLOOKUP(E65,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1018</v>
+      </c>
+      <c r="H65" s="6">
+        <v>4400</v>
+      </c>
+      <c r="I65" s="6">
+        <v>10</v>
+      </c>
+      <c r="J65" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B66" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C66" s="6">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <v>65</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="6">
+        <v>0</v>
+      </c>
+      <c r="G66" s="7">
+        <f>VLOOKUP(E66,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1020</v>
+      </c>
+      <c r="H66" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I66" s="6">
+        <v>10</v>
+      </c>
+      <c r="J66" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="6">
+        <v>40002</v>
+      </c>
+      <c r="C67" s="6">
+        <v>1</v>
+      </c>
+      <c r="D67" s="6">
+        <v>66</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0</v>
+      </c>
+      <c r="G67" s="7">
+        <f>VLOOKUP(E67,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1023</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1600</v>
+      </c>
+      <c r="I67" s="6">
+        <v>10</v>
+      </c>
+      <c r="J67" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>1110</v>
-      </c>
-      <c r="H51" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I51" s="1">
-        <v>10</v>
-      </c>
-      <c r="J51" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1">
+      <c r="B68" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C68" s="10">
+        <v>1</v>
+      </c>
+      <c r="D68" s="10">
+        <v>67</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" s="10">
+        <v>0</v>
+      </c>
+      <c r="G68" s="11">
+        <f>VLOOKUP(E68,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="H68" s="10">
+        <v>10000</v>
+      </c>
+      <c r="I68" s="10">
+        <v>10</v>
+      </c>
+      <c r="J68" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C69" s="10">
+        <v>1</v>
+      </c>
+      <c r="D69" s="10">
+        <v>68</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11">
+        <f>VLOOKUP(E69,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1009</v>
+      </c>
+      <c r="H69" s="10">
+        <v>8600</v>
+      </c>
+      <c r="I69" s="10">
+        <v>10</v>
+      </c>
+      <c r="J69" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C70" s="10">
+        <v>1</v>
+      </c>
+      <c r="D70" s="10">
+        <v>70</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F70" s="10">
+        <v>0</v>
+      </c>
+      <c r="G70" s="11">
+        <f>VLOOKUP(E70,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
+      </c>
+      <c r="H70" s="10">
+        <v>7200</v>
+      </c>
+      <c r="I70" s="10">
+        <v>10</v>
+      </c>
+      <c r="J70" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C71" s="10">
+        <v>1</v>
+      </c>
+      <c r="D71" s="10">
+        <v>71</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F71" s="10">
+        <v>0</v>
+      </c>
+      <c r="G71" s="11">
+        <f>VLOOKUP(E71,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
+      </c>
+      <c r="H71" s="10">
+        <v>5800</v>
+      </c>
+      <c r="I71" s="10">
+        <v>10</v>
+      </c>
+      <c r="J71" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C72" s="10">
+        <v>1</v>
+      </c>
+      <c r="D72" s="10">
+        <v>72</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" s="10">
+        <v>0</v>
+      </c>
+      <c r="G72" s="11">
+        <f>VLOOKUP(E72,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1014</v>
+      </c>
+      <c r="H72" s="10">
+        <v>4400</v>
+      </c>
+      <c r="I72" s="10">
+        <v>10</v>
+      </c>
+      <c r="J72" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C73" s="10">
+        <v>1</v>
+      </c>
+      <c r="D73" s="10">
+        <v>73</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" s="10">
+        <v>0</v>
+      </c>
+      <c r="G73" s="11">
+        <f>VLOOKUP(E73,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1017</v>
+      </c>
+      <c r="H73" s="10">
+        <v>3000</v>
+      </c>
+      <c r="I73" s="10">
+        <v>10</v>
+      </c>
+      <c r="J73" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="10">
+        <v>40003</v>
+      </c>
+      <c r="C74" s="10">
+        <v>1</v>
+      </c>
+      <c r="D74" s="10">
+        <v>74</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F74" s="10">
+        <v>0</v>
+      </c>
+      <c r="G74" s="11">
+        <f>VLOOKUP(E74,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1020</v>
+      </c>
+      <c r="H74" s="10">
+        <v>1600</v>
+      </c>
+      <c r="I74" s="10">
+        <v>10</v>
+      </c>
+      <c r="J74" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>1111</v>
-      </c>
-      <c r="H52" s="1">
-        <v>4500</v>
-      </c>
-      <c r="I52" s="1">
-        <v>10</v>
-      </c>
-      <c r="J52" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1">
-        <v>50</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>1112</v>
-      </c>
-      <c r="H53" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I53" s="1">
-        <v>10</v>
-      </c>
-      <c r="J53" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1">
-        <v>51</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>1113</v>
-      </c>
-      <c r="H54" s="1">
-        <v>3500</v>
-      </c>
-      <c r="I54" s="1">
-        <v>10</v>
-      </c>
-      <c r="J54" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="1">
-        <v>52</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>1114</v>
-      </c>
-      <c r="H55" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I55" s="1">
-        <v>10</v>
-      </c>
-      <c r="J55" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="1">
-        <v>53</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>1115</v>
-      </c>
-      <c r="H56" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I56" s="1">
-        <v>10</v>
-      </c>
-      <c r="J56" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="D57" s="1">
-        <v>54</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>1116</v>
-      </c>
-      <c r="H57" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I57" s="1">
-        <v>10</v>
-      </c>
-      <c r="J57" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="1">
-        <v>55</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>1117</v>
-      </c>
-      <c r="H58" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I58" s="1">
-        <v>10</v>
-      </c>
-      <c r="J58" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="1">
-        <v>56</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>1005</v>
-      </c>
-      <c r="H59" s="1">
+      <c r="B75" s="1">
+        <v>40004</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="1">
+        <v>75</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <f>VLOOKUP(E75,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="H75" s="1">
         <v>10000</v>
-      </c>
-      <c r="I59" s="1">
-        <v>10</v>
-      </c>
-      <c r="J59" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1">
-        <v>57</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>1007</v>
-      </c>
-      <c r="H60" s="1">
-        <v>9000</v>
-      </c>
-      <c r="I60" s="1">
-        <v>10</v>
-      </c>
-      <c r="J60" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="1">
-        <v>58</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>1009</v>
-      </c>
-      <c r="H61" s="1">
-        <v>8000</v>
-      </c>
-      <c r="I61" s="1">
-        <v>10</v>
-      </c>
-      <c r="J61" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B62" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1">
-        <v>59</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>1011</v>
-      </c>
-      <c r="H62" s="1">
-        <v>7000</v>
-      </c>
-      <c r="I62" s="1">
-        <v>10</v>
-      </c>
-      <c r="J62" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B63" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="1">
-        <v>60</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>1014</v>
-      </c>
-      <c r="H63" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I63" s="1">
-        <v>10</v>
-      </c>
-      <c r="J63" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B64" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1">
-        <v>61</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>1016</v>
-      </c>
-      <c r="H64" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I64" s="1">
-        <v>10</v>
-      </c>
-      <c r="J64" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B65" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="1">
-        <v>62</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1017</v>
-      </c>
-      <c r="H65" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I65" s="1">
-        <v>10</v>
-      </c>
-      <c r="J65" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="1">
-        <v>63</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1022</v>
-      </c>
-      <c r="H66" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I66" s="1">
-        <v>10</v>
-      </c>
-      <c r="J66" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B67" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="1">
-        <v>64</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1024</v>
-      </c>
-      <c r="H67" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I67" s="1">
-        <v>10</v>
-      </c>
-      <c r="J67" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B68" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="1">
-        <v>65</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H68" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I68" s="1">
-        <v>10</v>
-      </c>
-      <c r="J68" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B69" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="1">
-        <v>66</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>1002</v>
-      </c>
-      <c r="H69" s="1">
-        <v>9000</v>
-      </c>
-      <c r="I69" s="1">
-        <v>10</v>
-      </c>
-      <c r="J69" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="1">
-        <v>67</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>1003</v>
-      </c>
-      <c r="H70" s="1">
-        <v>8000</v>
-      </c>
-      <c r="I70" s="1">
-        <v>10</v>
-      </c>
-      <c r="J70" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B71" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="1">
-        <v>68</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>1008</v>
-      </c>
-      <c r="H71" s="1">
-        <v>7000</v>
-      </c>
-      <c r="I71" s="1">
-        <v>10</v>
-      </c>
-      <c r="J71" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1</v>
-      </c>
-      <c r="D72" s="1">
-        <v>69</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>1010</v>
-      </c>
-      <c r="H72" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I72" s="1">
-        <v>10</v>
-      </c>
-      <c r="J72" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B73" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="1">
-        <v>70</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1">
-        <v>1013</v>
-      </c>
-      <c r="H73" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I73" s="1">
-        <v>10</v>
-      </c>
-      <c r="J73" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B74" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1</v>
-      </c>
-      <c r="D74" s="1">
-        <v>71</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1">
-        <v>1018</v>
-      </c>
-      <c r="H74" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I74" s="1">
-        <v>10</v>
-      </c>
-      <c r="J74" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B75" s="1">
-        <v>40002</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="1">
-        <v>72</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>1020</v>
-      </c>
-      <c r="H75" s="1">
-        <v>3000</v>
       </c>
       <c r="I75" s="1">
         <v>10</v>
@@ -3071,28 +3127,29 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B76" s="1">
-        <v>40002</v>
+        <v>40004</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
       <c r="D76" s="1">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
       </c>
-      <c r="G76" s="1">
-        <v>1023</v>
+      <c r="G76">
+        <f>VLOOKUP(E76,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
       </c>
       <c r="H76" s="1">
-        <v>2000</v>
+        <v>7200</v>
       </c>
       <c r="I76" s="1">
         <v>10</v>
@@ -3103,28 +3160,29 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B77" s="1">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
-      <c r="G77" s="1">
-        <v>1000</v>
+      <c r="G77">
+        <f>VLOOKUP(E77,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
       </c>
       <c r="H77" s="1">
-        <v>10000</v>
+        <v>5800</v>
       </c>
       <c r="I77" s="1">
         <v>10</v>
@@ -3135,28 +3193,29 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B78" s="1">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
       </c>
       <c r="D78" s="1">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
       </c>
-      <c r="G78" s="1">
-        <v>1001</v>
+      <c r="G78">
+        <f>VLOOKUP(E78,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
       </c>
       <c r="H78" s="1">
-        <v>9000</v>
+        <v>4400</v>
       </c>
       <c r="I78" s="1">
         <v>10</v>
@@ -3167,28 +3226,29 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B79" s="1">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="C79" s="1">
         <v>1</v>
       </c>
       <c r="D79" s="1">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
-      <c r="G79" s="1">
-        <v>1002</v>
+      <c r="G79">
+        <f>VLOOKUP(E79,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1015</v>
       </c>
       <c r="H79" s="1">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="I79" s="1">
         <v>10</v>
@@ -3199,481 +3259,34 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B80" s="1">
-        <v>40003</v>
+        <v>40004</v>
       </c>
       <c r="C80" s="1">
         <v>1</v>
       </c>
       <c r="D80" s="1">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
-      <c r="G80" s="1">
-        <v>1003</v>
+      <c r="G80">
+        <f>VLOOKUP(E80,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1021</v>
       </c>
       <c r="H80" s="1">
-        <v>7000</v>
+        <v>1600</v>
       </c>
       <c r="I80" s="1">
         <v>10</v>
       </c>
       <c r="J80" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B81" s="1">
-        <v>40003</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="1">
-        <v>78</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1">
-        <v>1006</v>
-      </c>
-      <c r="H81" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I81" s="1">
-        <v>10</v>
-      </c>
-      <c r="J81" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B82" s="1">
-        <v>40003</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="1">
-        <v>79</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>1007</v>
-      </c>
-      <c r="H82" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I82" s="1">
-        <v>10</v>
-      </c>
-      <c r="J82" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B83" s="1">
-        <v>40003</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="1">
-        <v>80</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
-        <v>1012</v>
-      </c>
-      <c r="H83" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I83" s="1">
-        <v>10</v>
-      </c>
-      <c r="J83" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B84" s="1">
-        <v>40003</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="1">
-        <v>81</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1">
-        <v>1019</v>
-      </c>
-      <c r="H84" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I84" s="1">
-        <v>10</v>
-      </c>
-      <c r="J84" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B85" s="1">
-        <v>40003</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="1">
-        <v>82</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1">
-        <v>1020</v>
-      </c>
-      <c r="H85" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I85" s="1">
-        <v>10</v>
-      </c>
-      <c r="J85" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="1">
-        <v>83</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H86" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I86" s="1">
-        <v>10</v>
-      </c>
-      <c r="J86" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B87" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="1">
-        <v>84</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0</v>
-      </c>
-      <c r="G87" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H87" s="1">
-        <v>9000</v>
-      </c>
-      <c r="I87" s="1">
-        <v>10</v>
-      </c>
-      <c r="J87" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B88" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="1">
-        <v>85</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F88" s="1">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1">
-        <v>1003</v>
-      </c>
-      <c r="H88" s="1">
-        <v>8000</v>
-      </c>
-      <c r="I88" s="1">
-        <v>10</v>
-      </c>
-      <c r="J88" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B89" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="1">
-        <v>86</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F89" s="1">
-        <v>0</v>
-      </c>
-      <c r="G89" s="1">
-        <v>1006</v>
-      </c>
-      <c r="H89" s="1">
-        <v>7000</v>
-      </c>
-      <c r="I89" s="1">
-        <v>10</v>
-      </c>
-      <c r="J89" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B90" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1">
-        <v>87</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
-      <c r="G90" s="1">
-        <v>1007</v>
-      </c>
-      <c r="H90" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I90" s="1">
-        <v>10</v>
-      </c>
-      <c r="J90" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B91" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="1">
-        <v>88</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-      <c r="G91" s="1">
-        <v>1012</v>
-      </c>
-      <c r="H91" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I91" s="1">
-        <v>10</v>
-      </c>
-      <c r="J91" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B92" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1">
-        <v>89</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F92" s="1">
-        <v>0</v>
-      </c>
-      <c r="G92" s="1">
-        <v>1015</v>
-      </c>
-      <c r="H92" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I92" s="1">
-        <v>10</v>
-      </c>
-      <c r="J92" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B93" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="1">
-        <v>90</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F93" s="1">
-        <v>0</v>
-      </c>
-      <c r="G93" s="1">
-        <v>1019</v>
-      </c>
-      <c r="H93" s="1">
-        <v>3000</v>
-      </c>
-      <c r="I93" s="1">
-        <v>10</v>
-      </c>
-      <c r="J93" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B94" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="1">
-        <v>91</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F94" s="1">
-        <v>0</v>
-      </c>
-      <c r="G94" s="1">
-        <v>1021</v>
-      </c>
-      <c r="H94" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I94" s="1">
-        <v>10</v>
-      </c>
-      <c r="J94" s="1">
         <v>30</v>
       </c>
     </row>
@@ -3682,4 +3295,389 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5">
+        <v>1006</v>
+      </c>
+      <c r="D5">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6">
+        <v>1007</v>
+      </c>
+      <c r="D6">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>1008</v>
+      </c>
+      <c r="D7">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8">
+        <v>1009</v>
+      </c>
+      <c r="D8">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>1010</v>
+      </c>
+      <c r="D9">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10">
+        <v>1011</v>
+      </c>
+      <c r="D10">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11">
+        <v>1013</v>
+      </c>
+      <c r="D11">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12">
+        <v>1014</v>
+      </c>
+      <c r="D12">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13">
+        <v>1015</v>
+      </c>
+      <c r="D13">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14">
+        <v>1016</v>
+      </c>
+      <c r="D14">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <v>1017</v>
+      </c>
+      <c r="D15">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16">
+        <v>1018</v>
+      </c>
+      <c r="D16">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <v>1020</v>
+      </c>
+      <c r="D17">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18">
+        <v>1021</v>
+      </c>
+      <c r="D18">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19">
+        <v>1022</v>
+      </c>
+      <c r="D19">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20">
+        <v>1023</v>
+      </c>
+      <c r="D20">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21">
+        <v>1024</v>
+      </c>
+      <c r="D21">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22">
+        <v>1100</v>
+      </c>
+      <c r="D22">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23">
+        <v>1101</v>
+      </c>
+      <c r="D23">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24">
+        <v>1103</v>
+      </c>
+      <c r="D24">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25">
+        <v>1105</v>
+      </c>
+      <c r="D25">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>1106</v>
+      </c>
+      <c r="D26">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <v>1109</v>
+      </c>
+      <c r="D27">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>1110</v>
+      </c>
+      <c r="D28">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>1111</v>
+      </c>
+      <c r="D29">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30">
+        <v>1112</v>
+      </c>
+      <c r="D30">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>1113</v>
+      </c>
+      <c r="D31">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32">
+        <v>1114</v>
+      </c>
+      <c r="D32">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33">
+        <v>1115</v>
+      </c>
+      <c r="D33">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34">
+        <v>1116</v>
+      </c>
+      <c r="D34">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35">
+        <v>1117</v>
+      </c>
+      <c r="D35">
+        <v>4117</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="GameRandomData" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="499">
   <si>
     <t>text</t>
   </si>
@@ -1367,6 +1367,246 @@
   </si>
   <si>
     <t>死神掉落</t>
+  </si>
+  <si>
+    <t>100101</t>
+  </si>
+  <si>
+    <t>100102</t>
+  </si>
+  <si>
+    <t>100111</t>
+  </si>
+  <si>
+    <t>100112</t>
+  </si>
+  <si>
+    <t>100121</t>
+  </si>
+  <si>
+    <t>100122</t>
+  </si>
+  <si>
+    <t>100131</t>
+  </si>
+  <si>
+    <t>100132</t>
+  </si>
+  <si>
+    <t>100141</t>
+  </si>
+  <si>
+    <t>100142</t>
+  </si>
+  <si>
+    <t>100201</t>
+  </si>
+  <si>
+    <t>100202</t>
+  </si>
+  <si>
+    <t>100211</t>
+  </si>
+  <si>
+    <t>100212</t>
+  </si>
+  <si>
+    <t>100221</t>
+  </si>
+  <si>
+    <t>100222</t>
+  </si>
+  <si>
+    <t>100231</t>
+  </si>
+  <si>
+    <t>100232</t>
+  </si>
+  <si>
+    <t>100241</t>
+  </si>
+  <si>
+    <t>100242</t>
+  </si>
+  <si>
+    <t>100301</t>
+  </si>
+  <si>
+    <t>100302</t>
+  </si>
+  <si>
+    <t>100311</t>
+  </si>
+  <si>
+    <t>100312</t>
+  </si>
+  <si>
+    <t>100321</t>
+  </si>
+  <si>
+    <t>100322</t>
+  </si>
+  <si>
+    <t>100331</t>
+  </si>
+  <si>
+    <t>100332</t>
+  </si>
+  <si>
+    <t>100341</t>
+  </si>
+  <si>
+    <t>100342</t>
+  </si>
+  <si>
+    <t>100401</t>
+  </si>
+  <si>
+    <t>100402</t>
+  </si>
+  <si>
+    <t>100411</t>
+  </si>
+  <si>
+    <t>100412</t>
+  </si>
+  <si>
+    <t>100421</t>
+  </si>
+  <si>
+    <t>100422</t>
+  </si>
+  <si>
+    <t>100431</t>
+  </si>
+  <si>
+    <t>100432</t>
+  </si>
+  <si>
+    <t>100441</t>
+  </si>
+  <si>
+    <t>100442</t>
+  </si>
+  <si>
+    <t>100501</t>
+  </si>
+  <si>
+    <t>100502</t>
+  </si>
+  <si>
+    <t>100511</t>
+  </si>
+  <si>
+    <t>100512</t>
+  </si>
+  <si>
+    <t>100521</t>
+  </si>
+  <si>
+    <t>100522</t>
+  </si>
+  <si>
+    <t>100531</t>
+  </si>
+  <si>
+    <t>100532</t>
+  </si>
+  <si>
+    <t>100541</t>
+  </si>
+  <si>
+    <t>100542</t>
+  </si>
+  <si>
+    <t>100601</t>
+  </si>
+  <si>
+    <t>100602</t>
+  </si>
+  <si>
+    <t>100611</t>
+  </si>
+  <si>
+    <t>100612</t>
+  </si>
+  <si>
+    <t>100621</t>
+  </si>
+  <si>
+    <t>100622</t>
+  </si>
+  <si>
+    <t>100631</t>
+  </si>
+  <si>
+    <t>100632</t>
+  </si>
+  <si>
+    <t>100641</t>
+  </si>
+  <si>
+    <t>100642</t>
+  </si>
+  <si>
+    <t>100701</t>
+  </si>
+  <si>
+    <t>100702</t>
+  </si>
+  <si>
+    <t>100711</t>
+  </si>
+  <si>
+    <t>100712</t>
+  </si>
+  <si>
+    <t>100721</t>
+  </si>
+  <si>
+    <t>100722</t>
+  </si>
+  <si>
+    <t>100731</t>
+  </si>
+  <si>
+    <t>100732</t>
+  </si>
+  <si>
+    <t>100741</t>
+  </si>
+  <si>
+    <t>100742</t>
+  </si>
+  <si>
+    <t>100801</t>
+  </si>
+  <si>
+    <t>100802</t>
+  </si>
+  <si>
+    <t>100811</t>
+  </si>
+  <si>
+    <t>100812</t>
+  </si>
+  <si>
+    <t>100821</t>
+  </si>
+  <si>
+    <t>100822</t>
+  </si>
+  <si>
+    <t>100831</t>
+  </si>
+  <si>
+    <t>100832</t>
+  </si>
+  <si>
+    <t>100841</t>
+  </si>
+  <si>
+    <t>100842</t>
   </si>
 </sst>
 </file>
@@ -4915,8 +5155,8 @@
       <c r="F63" s="1">
         <v>0</v>
       </c>
-      <c r="G63" s="1">
-        <v>4100</v>
+      <c r="G63" t="s">
+        <v>419</v>
       </c>
       <c r="H63" s="1">
         <v>100</v>
@@ -4947,8 +5187,8 @@
       <c r="F64" s="1">
         <v>0</v>
       </c>
-      <c r="G64" s="1">
-        <v>4101</v>
+      <c r="G64" t="s">
+        <v>420</v>
       </c>
       <c r="H64" s="1">
         <v>100</v>
@@ -4979,8 +5219,8 @@
       <c r="F65" s="1">
         <v>0</v>
       </c>
-      <c r="G65" s="1">
-        <v>4102</v>
+      <c r="G65" t="s">
+        <v>421</v>
       </c>
       <c r="H65" s="1">
         <v>100</v>
@@ -5011,8 +5251,8 @@
       <c r="F66" s="1">
         <v>0</v>
       </c>
-      <c r="G66" s="1">
-        <v>4103</v>
+      <c r="G66" t="s">
+        <v>422</v>
       </c>
       <c r="H66" s="1">
         <v>100</v>
@@ -5043,8 +5283,8 @@
       <c r="F67" s="1">
         <v>0</v>
       </c>
-      <c r="G67" s="1">
-        <v>4104</v>
+      <c r="G67" t="s">
+        <v>423</v>
       </c>
       <c r="H67" s="1">
         <v>100</v>
@@ -5075,8 +5315,8 @@
       <c r="F68" s="1">
         <v>0</v>
       </c>
-      <c r="G68" s="1">
-        <v>4105</v>
+      <c r="G68" t="s">
+        <v>424</v>
       </c>
       <c r="H68" s="1">
         <v>100</v>
@@ -5107,8 +5347,8 @@
       <c r="F69" s="1">
         <v>0</v>
       </c>
-      <c r="G69" s="1">
-        <v>4106</v>
+      <c r="G69" t="s">
+        <v>425</v>
       </c>
       <c r="H69" s="1">
         <v>100</v>
@@ -5139,8 +5379,8 @@
       <c r="F70" s="1">
         <v>0</v>
       </c>
-      <c r="G70" s="1">
-        <v>4107</v>
+      <c r="G70" t="s">
+        <v>426</v>
       </c>
       <c r="H70" s="1">
         <v>100</v>
@@ -5171,8 +5411,8 @@
       <c r="F71" s="1">
         <v>0</v>
       </c>
-      <c r="G71" s="1">
-        <v>4108</v>
+      <c r="G71" t="s">
+        <v>427</v>
       </c>
       <c r="H71" s="1">
         <v>100</v>
@@ -5203,8 +5443,8 @@
       <c r="F72" s="1">
         <v>0</v>
       </c>
-      <c r="G72" s="1">
-        <v>4109</v>
+      <c r="G72" t="s">
+        <v>428</v>
       </c>
       <c r="H72" s="1">
         <v>100</v>
@@ -5235,8 +5475,8 @@
       <c r="F73" s="1">
         <v>0</v>
       </c>
-      <c r="G73" s="1">
-        <v>4110</v>
+      <c r="G73" t="s">
+        <v>429</v>
       </c>
       <c r="H73" s="1">
         <v>100</v>
@@ -5267,8 +5507,8 @@
       <c r="F74" s="1">
         <v>0</v>
       </c>
-      <c r="G74" s="1">
-        <v>4111</v>
+      <c r="G74" t="s">
+        <v>430</v>
       </c>
       <c r="H74" s="1">
         <v>100</v>
@@ -5299,8 +5539,8 @@
       <c r="F75" s="1">
         <v>0</v>
       </c>
-      <c r="G75" s="1">
-        <v>4112</v>
+      <c r="G75" t="s">
+        <v>431</v>
       </c>
       <c r="H75" s="1">
         <v>100</v>
@@ -5331,8 +5571,8 @@
       <c r="F76" s="1">
         <v>0</v>
       </c>
-      <c r="G76" s="1">
-        <v>4113</v>
+      <c r="G76" t="s">
+        <v>432</v>
       </c>
       <c r="H76" s="1">
         <v>100</v>
@@ -5363,8 +5603,8 @@
       <c r="F77" s="1">
         <v>0</v>
       </c>
-      <c r="G77" s="1">
-        <v>4114</v>
+      <c r="G77" t="s">
+        <v>433</v>
       </c>
       <c r="H77" s="1">
         <v>100</v>
@@ -5395,8 +5635,8 @@
       <c r="F78" s="1">
         <v>0</v>
       </c>
-      <c r="G78" s="1">
-        <v>4115</v>
+      <c r="G78" t="s">
+        <v>434</v>
       </c>
       <c r="H78" s="1">
         <v>100</v>
@@ -5427,8 +5667,8 @@
       <c r="F79" s="1">
         <v>0</v>
       </c>
-      <c r="G79" s="1">
-        <v>4116</v>
+      <c r="G79" t="s">
+        <v>435</v>
       </c>
       <c r="H79" s="1">
         <v>100</v>
@@ -5459,8 +5699,8 @@
       <c r="F80" s="1">
         <v>0</v>
       </c>
-      <c r="G80" s="1">
-        <v>4117</v>
+      <c r="G80" t="s">
+        <v>436</v>
       </c>
       <c r="H80" s="1">
         <v>100</v>
@@ -5491,8 +5731,8 @@
       <c r="F81" s="1">
         <v>0</v>
       </c>
-      <c r="G81" s="1">
-        <v>4118</v>
+      <c r="G81" t="s">
+        <v>437</v>
       </c>
       <c r="H81" s="1">
         <v>100</v>
@@ -5523,8 +5763,8 @@
       <c r="F82" s="1">
         <v>0</v>
       </c>
-      <c r="G82" s="1">
-        <v>4119</v>
+      <c r="G82" t="s">
+        <v>438</v>
       </c>
       <c r="H82" s="1">
         <v>100</v>
@@ -5555,8 +5795,8 @@
       <c r="F83" s="1">
         <v>0</v>
       </c>
-      <c r="G83" s="1">
-        <v>4120</v>
+      <c r="G83" t="s">
+        <v>439</v>
       </c>
       <c r="H83" s="1">
         <v>100</v>
@@ -5587,8 +5827,8 @@
       <c r="F84" s="1">
         <v>0</v>
       </c>
-      <c r="G84" s="1">
-        <v>4121</v>
+      <c r="G84" t="s">
+        <v>440</v>
       </c>
       <c r="H84" s="1">
         <v>100</v>
@@ -5619,8 +5859,8 @@
       <c r="F85" s="1">
         <v>0</v>
       </c>
-      <c r="G85" s="1">
-        <v>4122</v>
+      <c r="G85" t="s">
+        <v>441</v>
       </c>
       <c r="H85" s="1">
         <v>100</v>
@@ -5651,8 +5891,8 @@
       <c r="F86" s="1">
         <v>0</v>
       </c>
-      <c r="G86" s="1">
-        <v>4123</v>
+      <c r="G86" t="s">
+        <v>442</v>
       </c>
       <c r="H86" s="1">
         <v>100</v>
@@ -5683,8 +5923,8 @@
       <c r="F87" s="1">
         <v>0</v>
       </c>
-      <c r="G87" s="1">
-        <v>4124</v>
+      <c r="G87" t="s">
+        <v>443</v>
       </c>
       <c r="H87" s="1">
         <v>100</v>
@@ -5715,8 +5955,8 @@
       <c r="F88" s="1">
         <v>0</v>
       </c>
-      <c r="G88" s="1">
-        <v>4125</v>
+      <c r="G88" t="s">
+        <v>444</v>
       </c>
       <c r="H88" s="1">
         <v>100</v>
@@ -5747,8 +5987,8 @@
       <c r="F89" s="1">
         <v>0</v>
       </c>
-      <c r="G89" s="1">
-        <v>4126</v>
+      <c r="G89" t="s">
+        <v>445</v>
       </c>
       <c r="H89" s="1">
         <v>100</v>
@@ -5779,8 +6019,8 @@
       <c r="F90" s="1">
         <v>0</v>
       </c>
-      <c r="G90" s="1">
-        <v>4127</v>
+      <c r="G90" t="s">
+        <v>446</v>
       </c>
       <c r="H90" s="1">
         <v>100</v>
@@ -5811,8 +6051,8 @@
       <c r="F91" s="1">
         <v>0</v>
       </c>
-      <c r="G91" s="1">
-        <v>4128</v>
+      <c r="G91" t="s">
+        <v>447</v>
       </c>
       <c r="H91" s="1">
         <v>100</v>
@@ -5843,8 +6083,8 @@
       <c r="F92" s="1">
         <v>0</v>
       </c>
-      <c r="G92" s="1">
-        <v>4129</v>
+      <c r="G92" t="s">
+        <v>448</v>
       </c>
       <c r="H92" s="1">
         <v>100</v>
@@ -5875,8 +6115,8 @@
       <c r="F93" s="1">
         <v>0</v>
       </c>
-      <c r="G93" s="1">
-        <v>4130</v>
+      <c r="G93" t="s">
+        <v>449</v>
       </c>
       <c r="H93" s="1">
         <v>100</v>
@@ -5907,8 +6147,8 @@
       <c r="F94" s="1">
         <v>0</v>
       </c>
-      <c r="G94" s="1">
-        <v>4131</v>
+      <c r="G94" t="s">
+        <v>450</v>
       </c>
       <c r="H94" s="1">
         <v>100</v>
@@ -5939,8 +6179,8 @@
       <c r="F95" s="1">
         <v>0</v>
       </c>
-      <c r="G95" s="1">
-        <v>4132</v>
+      <c r="G95" t="s">
+        <v>451</v>
       </c>
       <c r="H95" s="1">
         <v>100</v>
@@ -5971,8 +6211,8 @@
       <c r="F96" s="1">
         <v>0</v>
       </c>
-      <c r="G96" s="1">
-        <v>4133</v>
+      <c r="G96" t="s">
+        <v>452</v>
       </c>
       <c r="H96" s="1">
         <v>100</v>
@@ -6003,8 +6243,8 @@
       <c r="F97" s="1">
         <v>0</v>
       </c>
-      <c r="G97" s="1">
-        <v>4134</v>
+      <c r="G97" t="s">
+        <v>453</v>
       </c>
       <c r="H97" s="1">
         <v>100</v>
@@ -6035,8 +6275,8 @@
       <c r="F98" s="1">
         <v>0</v>
       </c>
-      <c r="G98" s="1">
-        <v>4135</v>
+      <c r="G98" t="s">
+        <v>454</v>
       </c>
       <c r="H98" s="1">
         <v>100</v>
@@ -6067,8 +6307,8 @@
       <c r="F99" s="1">
         <v>0</v>
       </c>
-      <c r="G99" s="1">
-        <v>4136</v>
+      <c r="G99" t="s">
+        <v>455</v>
       </c>
       <c r="H99" s="1">
         <v>100</v>
@@ -6099,8 +6339,8 @@
       <c r="F100" s="1">
         <v>0</v>
       </c>
-      <c r="G100" s="1">
-        <v>4137</v>
+      <c r="G100" t="s">
+        <v>456</v>
       </c>
       <c r="H100" s="1">
         <v>100</v>
@@ -6131,8 +6371,8 @@
       <c r="F101" s="1">
         <v>0</v>
       </c>
-      <c r="G101" s="1">
-        <v>4138</v>
+      <c r="G101" t="s">
+        <v>457</v>
       </c>
       <c r="H101" s="1">
         <v>100</v>
@@ -6163,8 +6403,8 @@
       <c r="F102" s="1">
         <v>0</v>
       </c>
-      <c r="G102" s="1">
-        <v>4139</v>
+      <c r="G102" t="s">
+        <v>458</v>
       </c>
       <c r="H102" s="1">
         <v>100</v>
@@ -6195,8 +6435,8 @@
       <c r="F103" s="1">
         <v>0</v>
       </c>
-      <c r="G103" s="1">
-        <v>4140</v>
+      <c r="G103" t="s">
+        <v>459</v>
       </c>
       <c r="H103" s="1">
         <v>100</v>
@@ -6227,8 +6467,8 @@
       <c r="F104" s="1">
         <v>0</v>
       </c>
-      <c r="G104" s="1">
-        <v>4141</v>
+      <c r="G104" t="s">
+        <v>460</v>
       </c>
       <c r="H104" s="1">
         <v>100</v>
@@ -6259,8 +6499,8 @@
       <c r="F105" s="1">
         <v>0</v>
       </c>
-      <c r="G105" s="1">
-        <v>4142</v>
+      <c r="G105" t="s">
+        <v>461</v>
       </c>
       <c r="H105" s="1">
         <v>100</v>
@@ -6291,8 +6531,8 @@
       <c r="F106" s="1">
         <v>0</v>
       </c>
-      <c r="G106" s="1">
-        <v>4143</v>
+      <c r="G106" t="s">
+        <v>462</v>
       </c>
       <c r="H106" s="1">
         <v>100</v>
@@ -6323,8 +6563,8 @@
       <c r="F107" s="1">
         <v>0</v>
       </c>
-      <c r="G107" s="1">
-        <v>4144</v>
+      <c r="G107" t="s">
+        <v>463</v>
       </c>
       <c r="H107" s="1">
         <v>100</v>
@@ -6355,8 +6595,8 @@
       <c r="F108" s="1">
         <v>0</v>
       </c>
-      <c r="G108" s="1">
-        <v>4145</v>
+      <c r="G108" t="s">
+        <v>464</v>
       </c>
       <c r="H108" s="1">
         <v>100</v>
@@ -6387,8 +6627,8 @@
       <c r="F109" s="1">
         <v>0</v>
       </c>
-      <c r="G109" s="1">
-        <v>4146</v>
+      <c r="G109" t="s">
+        <v>465</v>
       </c>
       <c r="H109" s="1">
         <v>100</v>
@@ -6419,8 +6659,8 @@
       <c r="F110" s="1">
         <v>0</v>
       </c>
-      <c r="G110" s="1">
-        <v>4147</v>
+      <c r="G110" t="s">
+        <v>466</v>
       </c>
       <c r="H110" s="1">
         <v>100</v>
@@ -6451,8 +6691,8 @@
       <c r="F111" s="1">
         <v>0</v>
       </c>
-      <c r="G111" s="1">
-        <v>4148</v>
+      <c r="G111" t="s">
+        <v>467</v>
       </c>
       <c r="H111" s="1">
         <v>100</v>
@@ -6483,8 +6723,8 @@
       <c r="F112" s="1">
         <v>0</v>
       </c>
-      <c r="G112" s="1">
-        <v>4149</v>
+      <c r="G112" t="s">
+        <v>468</v>
       </c>
       <c r="H112" s="1">
         <v>100</v>
@@ -6515,8 +6755,8 @@
       <c r="F113" s="1">
         <v>0</v>
       </c>
-      <c r="G113" s="1">
-        <v>4150</v>
+      <c r="G113" t="s">
+        <v>469</v>
       </c>
       <c r="H113" s="1">
         <v>100</v>
@@ -6547,8 +6787,8 @@
       <c r="F114" s="1">
         <v>0</v>
       </c>
-      <c r="G114" s="1">
-        <v>4151</v>
+      <c r="G114" t="s">
+        <v>470</v>
       </c>
       <c r="H114" s="1">
         <v>100</v>
@@ -6579,8 +6819,8 @@
       <c r="F115" s="1">
         <v>0</v>
       </c>
-      <c r="G115" s="1">
-        <v>4152</v>
+      <c r="G115" t="s">
+        <v>471</v>
       </c>
       <c r="H115" s="1">
         <v>100</v>
@@ -6611,8 +6851,8 @@
       <c r="F116" s="1">
         <v>0</v>
       </c>
-      <c r="G116" s="1">
-        <v>4153</v>
+      <c r="G116" t="s">
+        <v>472</v>
       </c>
       <c r="H116" s="1">
         <v>100</v>
@@ -6643,8 +6883,8 @@
       <c r="F117" s="1">
         <v>0</v>
       </c>
-      <c r="G117" s="1">
-        <v>4154</v>
+      <c r="G117" t="s">
+        <v>473</v>
       </c>
       <c r="H117" s="1">
         <v>100</v>
@@ -6675,8 +6915,8 @@
       <c r="F118" s="1">
         <v>0</v>
       </c>
-      <c r="G118" s="1">
-        <v>4155</v>
+      <c r="G118" t="s">
+        <v>474</v>
       </c>
       <c r="H118" s="1">
         <v>100</v>
@@ -6707,8 +6947,8 @@
       <c r="F119" s="1">
         <v>0</v>
       </c>
-      <c r="G119" s="1">
-        <v>4156</v>
+      <c r="G119" t="s">
+        <v>475</v>
       </c>
       <c r="H119" s="1">
         <v>100</v>
@@ -6739,8 +6979,8 @@
       <c r="F120" s="1">
         <v>0</v>
       </c>
-      <c r="G120" s="1">
-        <v>4157</v>
+      <c r="G120" t="s">
+        <v>476</v>
       </c>
       <c r="H120" s="1">
         <v>100</v>
@@ -6771,8 +7011,8 @@
       <c r="F121" s="1">
         <v>0</v>
       </c>
-      <c r="G121" s="1">
-        <v>4158</v>
+      <c r="G121" t="s">
+        <v>477</v>
       </c>
       <c r="H121" s="1">
         <v>100</v>
@@ -6803,8 +7043,8 @@
       <c r="F122" s="1">
         <v>0</v>
       </c>
-      <c r="G122" s="1">
-        <v>4159</v>
+      <c r="G122" t="s">
+        <v>478</v>
       </c>
       <c r="H122" s="1">
         <v>100</v>
@@ -6835,8 +7075,8 @@
       <c r="F123" s="1">
         <v>0</v>
       </c>
-      <c r="G123" s="1">
-        <v>4160</v>
+      <c r="G123" t="s">
+        <v>479</v>
       </c>
       <c r="H123" s="1">
         <v>100</v>
@@ -6867,8 +7107,8 @@
       <c r="F124" s="1">
         <v>0</v>
       </c>
-      <c r="G124" s="1">
-        <v>4161</v>
+      <c r="G124" t="s">
+        <v>480</v>
       </c>
       <c r="H124" s="1">
         <v>100</v>
@@ -6899,8 +7139,8 @@
       <c r="F125" s="1">
         <v>0</v>
       </c>
-      <c r="G125" s="1">
-        <v>4162</v>
+      <c r="G125" t="s">
+        <v>481</v>
       </c>
       <c r="H125" s="1">
         <v>100</v>
@@ -6931,8 +7171,8 @@
       <c r="F126" s="1">
         <v>0</v>
       </c>
-      <c r="G126" s="1">
-        <v>4163</v>
+      <c r="G126" t="s">
+        <v>482</v>
       </c>
       <c r="H126" s="1">
         <v>100</v>
@@ -6963,8 +7203,8 @@
       <c r="F127" s="1">
         <v>0</v>
       </c>
-      <c r="G127" s="1">
-        <v>4164</v>
+      <c r="G127" t="s">
+        <v>483</v>
       </c>
       <c r="H127" s="1">
         <v>100</v>
@@ -6995,8 +7235,8 @@
       <c r="F128" s="1">
         <v>0</v>
       </c>
-      <c r="G128" s="1">
-        <v>4165</v>
+      <c r="G128" t="s">
+        <v>484</v>
       </c>
       <c r="H128" s="1">
         <v>100</v>
@@ -7027,8 +7267,8 @@
       <c r="F129" s="1">
         <v>0</v>
       </c>
-      <c r="G129" s="1">
-        <v>4166</v>
+      <c r="G129" t="s">
+        <v>485</v>
       </c>
       <c r="H129" s="1">
         <v>100</v>
@@ -7059,8 +7299,8 @@
       <c r="F130" s="1">
         <v>0</v>
       </c>
-      <c r="G130" s="1">
-        <v>4167</v>
+      <c r="G130" t="s">
+        <v>486</v>
       </c>
       <c r="H130" s="1">
         <v>100</v>
@@ -7091,8 +7331,8 @@
       <c r="F131" s="1">
         <v>0</v>
       </c>
-      <c r="G131" s="1">
-        <v>4168</v>
+      <c r="G131" t="s">
+        <v>487</v>
       </c>
       <c r="H131" s="1">
         <v>100</v>
@@ -7123,8 +7363,8 @@
       <c r="F132" s="1">
         <v>0</v>
       </c>
-      <c r="G132" s="1">
-        <v>4169</v>
+      <c r="G132" t="s">
+        <v>488</v>
       </c>
       <c r="H132" s="1">
         <v>100</v>
@@ -7155,8 +7395,8 @@
       <c r="F133" s="1">
         <v>0</v>
       </c>
-      <c r="G133" s="1">
-        <v>4170</v>
+      <c r="G133" t="s">
+        <v>489</v>
       </c>
       <c r="H133" s="1">
         <v>100</v>
@@ -7187,8 +7427,8 @@
       <c r="F134" s="1">
         <v>0</v>
       </c>
-      <c r="G134" s="1">
-        <v>4171</v>
+      <c r="G134" t="s">
+        <v>490</v>
       </c>
       <c r="H134" s="1">
         <v>100</v>
@@ -7219,8 +7459,8 @@
       <c r="F135" s="1">
         <v>0</v>
       </c>
-      <c r="G135" s="1">
-        <v>4172</v>
+      <c r="G135" t="s">
+        <v>491</v>
       </c>
       <c r="H135" s="1">
         <v>100</v>
@@ -7251,8 +7491,8 @@
       <c r="F136" s="1">
         <v>0</v>
       </c>
-      <c r="G136" s="1">
-        <v>4173</v>
+      <c r="G136" t="s">
+        <v>492</v>
       </c>
       <c r="H136" s="1">
         <v>100</v>
@@ -7283,8 +7523,8 @@
       <c r="F137" s="1">
         <v>0</v>
       </c>
-      <c r="G137" s="1">
-        <v>4174</v>
+      <c r="G137" t="s">
+        <v>493</v>
       </c>
       <c r="H137" s="1">
         <v>100</v>
@@ -7315,8 +7555,8 @@
       <c r="F138" s="1">
         <v>0</v>
       </c>
-      <c r="G138" s="1">
-        <v>4175</v>
+      <c r="G138" t="s">
+        <v>494</v>
       </c>
       <c r="H138" s="1">
         <v>100</v>
@@ -7347,8 +7587,8 @@
       <c r="F139" s="1">
         <v>0</v>
       </c>
-      <c r="G139" s="1">
-        <v>4176</v>
+      <c r="G139" t="s">
+        <v>495</v>
       </c>
       <c r="H139" s="1">
         <v>100</v>
@@ -7379,8 +7619,8 @@
       <c r="F140" s="1">
         <v>0</v>
       </c>
-      <c r="G140" s="1">
-        <v>4177</v>
+      <c r="G140" t="s">
+        <v>496</v>
       </c>
       <c r="H140" s="1">
         <v>100</v>
@@ -7411,8 +7651,8 @@
       <c r="F141" s="1">
         <v>0</v>
       </c>
-      <c r="G141" s="1">
-        <v>4178</v>
+      <c r="G141" t="s">
+        <v>497</v>
       </c>
       <c r="H141" s="1">
         <v>100</v>
@@ -7443,8 +7683,8 @@
       <c r="F142" s="1">
         <v>0</v>
       </c>
-      <c r="G142" s="1">
-        <v>4179</v>
+      <c r="G142" t="s">
+        <v>498</v>
       </c>
       <c r="H142" s="1">
         <v>100</v>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="585">
   <si>
     <t>text</t>
   </si>
@@ -1734,6 +1734,180 @@
   <si>
     <t>曲谱</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清晨住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>清晨住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白天住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>傍晚住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小丑</t>
+  </si>
+  <si>
+    <t>兔女郎</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深夜住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌晨住宅区路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>轻战士</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>制服小孩</t>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>魔族大将</t>
+  </si>
+  <si>
+    <t>魔族法师</t>
+  </si>
+  <si>
+    <t>魔族娃娃</t>
+  </si>
+  <si>
+    <t>女鬼</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>小精灵黄</t>
+  </si>
+  <si>
+    <t>邪恶法师</t>
+  </si>
+  <si>
+    <t>幽灵战士</t>
   </si>
 </sst>
 </file>
@@ -3310,7 +3484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I389"/>
+  <dimension ref="A1:I450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -12004,22 +12178,25 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B301" s="1">
-        <v>30000</v>
+        <v>20001</v>
       </c>
       <c r="C301" s="1">
         <v>1</v>
       </c>
+      <c r="D301" t="s">
+        <v>499</v>
+      </c>
       <c r="E301" s="1">
         <v>0</v>
       </c>
-      <c r="F301" s="2">
-        <v>6000</v>
+      <c r="F301">
+        <v>42</v>
       </c>
       <c r="G301" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H301" s="1">
         <v>1</v>
@@ -12030,22 +12207,25 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B302" s="1">
-        <v>30000</v>
+        <v>20001</v>
       </c>
       <c r="C302" s="1">
         <v>1</v>
       </c>
+      <c r="D302" t="s">
+        <v>500</v>
+      </c>
       <c r="E302" s="1">
         <v>0</v>
       </c>
-      <c r="F302" s="2">
-        <v>6001</v>
+      <c r="F302">
+        <v>48</v>
       </c>
       <c r="G302" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H302" s="1">
         <v>1</v>
@@ -12056,22 +12236,25 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B303" s="1">
-        <v>30000</v>
+        <v>20001</v>
       </c>
       <c r="C303" s="1">
         <v>1</v>
       </c>
+      <c r="D303" t="s">
+        <v>502</v>
+      </c>
       <c r="E303" s="1">
         <v>0</v>
       </c>
-      <c r="F303" s="2">
-        <v>6002</v>
+      <c r="F303">
+        <v>17</v>
       </c>
       <c r="G303" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H303" s="1">
         <v>1</v>
@@ -12082,22 +12265,25 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B304" s="1">
-        <v>30000</v>
+        <v>20001</v>
       </c>
       <c r="C304" s="1">
         <v>1</v>
       </c>
+      <c r="D304" t="s">
+        <v>503</v>
+      </c>
       <c r="E304" s="1">
         <v>0</v>
       </c>
-      <c r="F304" s="2">
-        <v>6003</v>
+      <c r="F304">
+        <v>18</v>
       </c>
       <c r="G304" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H304" s="1">
         <v>1</v>
@@ -12108,22 +12294,25 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>16</v>
+        <v>498</v>
       </c>
       <c r="B305" s="1">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="C305" s="1">
         <v>1</v>
       </c>
+      <c r="D305" s="1" t="s">
+        <v>504</v>
+      </c>
       <c r="E305" s="1">
         <v>0</v>
       </c>
-      <c r="F305" s="2">
-        <v>6004</v>
+      <c r="F305" s="1">
+        <v>1</v>
       </c>
       <c r="G305" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H305" s="1">
         <v>1</v>
@@ -12134,22 +12323,25 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>16</v>
+        <v>506</v>
       </c>
       <c r="B306" s="1">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="C306" s="1">
         <v>1</v>
       </c>
+      <c r="D306" s="1" t="s">
+        <v>505</v>
+      </c>
       <c r="E306" s="1">
         <v>0</v>
       </c>
-      <c r="F306" s="2">
-        <v>6005</v>
+      <c r="F306" s="1">
+        <v>24</v>
       </c>
       <c r="G306" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H306" s="1">
         <v>1</v>
@@ -12160,22 +12352,25 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="B307" s="1">
-        <v>30001</v>
+        <v>20002</v>
       </c>
       <c r="C307" s="1">
         <v>1</v>
       </c>
+      <c r="D307" t="s">
+        <v>512</v>
+      </c>
       <c r="E307" s="1">
         <v>0</v>
       </c>
-      <c r="F307" s="2">
-        <v>6006</v>
+      <c r="F307">
+        <v>61</v>
       </c>
       <c r="G307" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H307" s="1">
         <v>1</v>
@@ -12186,22 +12381,25 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="B308" s="1">
-        <v>30002</v>
+        <v>20002</v>
       </c>
       <c r="C308" s="1">
         <v>1</v>
       </c>
+      <c r="D308" t="s">
+        <v>513</v>
+      </c>
       <c r="E308" s="1">
         <v>0</v>
       </c>
-      <c r="F308" s="1">
-        <v>30</v>
+      <c r="F308">
+        <v>16</v>
       </c>
       <c r="G308" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H308" s="1">
         <v>1</v>
@@ -12212,22 +12410,25 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="B309" s="1">
-        <v>30002</v>
+        <v>20002</v>
       </c>
       <c r="C309" s="1">
         <v>1</v>
       </c>
+      <c r="D309" t="s">
+        <v>515</v>
+      </c>
       <c r="E309" s="1">
         <v>0</v>
       </c>
-      <c r="F309" s="1">
-        <v>8</v>
+      <c r="F309">
+        <v>31</v>
       </c>
       <c r="G309" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H309" s="1">
         <v>1</v>
@@ -12238,22 +12439,25 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="B310" s="1">
-        <v>30002</v>
+        <v>20002</v>
       </c>
       <c r="C310" s="1">
         <v>1</v>
       </c>
+      <c r="D310" t="s">
+        <v>503</v>
+      </c>
       <c r="E310" s="1">
         <v>0</v>
       </c>
-      <c r="F310" s="1">
-        <v>5</v>
+      <c r="F310">
+        <v>18</v>
       </c>
       <c r="G310" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H310" s="1">
         <v>1</v>
@@ -12264,22 +12468,25 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="B311" s="1">
-        <v>30002</v>
+        <v>20002</v>
       </c>
       <c r="C311" s="1">
         <v>1</v>
       </c>
+      <c r="D311" s="1" t="s">
+        <v>504</v>
+      </c>
       <c r="E311" s="1">
         <v>0</v>
       </c>
       <c r="F311" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G311" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H311" s="1">
         <v>1</v>
@@ -12290,22 +12497,25 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>19</v>
+        <v>508</v>
       </c>
       <c r="B312" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="C312" s="1">
         <v>1</v>
       </c>
+      <c r="D312" t="s">
+        <v>518</v>
+      </c>
       <c r="E312" s="1">
         <v>0</v>
       </c>
-      <c r="F312" s="1">
-        <v>24</v>
+      <c r="F312">
+        <v>14</v>
       </c>
       <c r="G312" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H312" s="1">
         <v>1</v>
@@ -12316,22 +12526,25 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>19</v>
+        <v>508</v>
       </c>
       <c r="B313" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="C313" s="1">
         <v>1</v>
       </c>
+      <c r="D313" t="s">
+        <v>519</v>
+      </c>
       <c r="E313" s="1">
         <v>0</v>
       </c>
-      <c r="F313" s="1">
-        <v>25</v>
+      <c r="F313">
+        <v>16</v>
       </c>
       <c r="G313" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H313" s="1">
         <v>1</v>
@@ -12342,22 +12555,25 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>19</v>
+        <v>508</v>
       </c>
       <c r="B314" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="C314" s="1">
         <v>1</v>
       </c>
+      <c r="D314" t="s">
+        <v>520</v>
+      </c>
       <c r="E314" s="1">
         <v>0</v>
       </c>
-      <c r="F314" s="1">
-        <v>2</v>
+      <c r="F314">
+        <v>17</v>
       </c>
       <c r="G314" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H314" s="1">
         <v>1</v>
@@ -12368,22 +12584,25 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="B315" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="C315" s="1">
         <v>1</v>
       </c>
+      <c r="D315" t="s">
+        <v>521</v>
+      </c>
       <c r="E315" s="1">
         <v>0</v>
       </c>
-      <c r="F315" s="1">
-        <v>19</v>
+      <c r="F315">
+        <v>18</v>
       </c>
       <c r="G315" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H315" s="1">
         <v>1</v>
@@ -12394,22 +12613,25 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>20</v>
+        <v>508</v>
       </c>
       <c r="B316" s="1">
-        <v>30004</v>
+        <v>20003</v>
       </c>
       <c r="C316" s="1">
         <v>1</v>
       </c>
+      <c r="D316" t="s">
+        <v>523</v>
+      </c>
       <c r="E316" s="1">
         <v>0</v>
       </c>
-      <c r="F316" s="1">
-        <v>6007</v>
+      <c r="F316">
+        <v>25</v>
       </c>
       <c r="G316" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H316" s="1">
         <v>1</v>
@@ -12420,22 +12642,25 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>22</v>
+        <v>509</v>
       </c>
       <c r="B317" s="1">
-        <v>30005</v>
+        <v>20004</v>
       </c>
       <c r="C317" s="1">
         <v>1</v>
       </c>
+      <c r="D317" t="s">
+        <v>524</v>
+      </c>
       <c r="E317" s="1">
         <v>0</v>
       </c>
-      <c r="F317" s="1">
-        <v>4</v>
+      <c r="F317">
+        <v>12</v>
       </c>
       <c r="G317" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H317" s="1">
         <v>1</v>
@@ -12446,22 +12671,25 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>23</v>
+        <v>509</v>
       </c>
       <c r="B318" s="1">
-        <v>30005</v>
+        <v>20004</v>
       </c>
       <c r="C318" s="1">
         <v>1</v>
       </c>
+      <c r="D318" t="s">
+        <v>516</v>
+      </c>
       <c r="E318" s="1">
         <v>0</v>
       </c>
-      <c r="F318" s="1">
-        <v>1</v>
+      <c r="F318">
+        <v>13</v>
       </c>
       <c r="G318" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H318" s="1">
         <v>1</v>
@@ -12472,2103 +12700,3879 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B319" s="1">
+        <v>20004</v>
+      </c>
+      <c r="C319" s="1">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>525</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>8</v>
+      </c>
+      <c r="G319" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H319" s="1">
+        <v>1</v>
+      </c>
+      <c r="I319" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A320" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B320" s="1">
+        <v>20004</v>
+      </c>
+      <c r="C320" s="1">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>526</v>
+      </c>
+      <c r="E320" s="1">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>76</v>
+      </c>
+      <c r="G320" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H320" s="1">
+        <v>1</v>
+      </c>
+      <c r="I320" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A321" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B321" s="1">
+        <v>20004</v>
+      </c>
+      <c r="C321" s="1">
+        <v>1</v>
+      </c>
+      <c r="D321" t="s">
+        <v>512</v>
+      </c>
+      <c r="E321" s="1">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>61</v>
+      </c>
+      <c r="G321" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H321" s="1">
+        <v>1</v>
+      </c>
+      <c r="I321" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A322" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B322" s="1">
+        <v>20005</v>
+      </c>
+      <c r="C322" s="1">
+        <v>1</v>
+      </c>
+      <c r="D322" t="s">
+        <v>517</v>
+      </c>
+      <c r="E322" s="1">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>14</v>
+      </c>
+      <c r="G322" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H322" s="1">
+        <v>1</v>
+      </c>
+      <c r="I322" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A323" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B323" s="1">
+        <v>20005</v>
+      </c>
+      <c r="C323" s="1">
+        <v>1</v>
+      </c>
+      <c r="D323" t="s">
+        <v>522</v>
+      </c>
+      <c r="E323" s="1">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>19</v>
+      </c>
+      <c r="G323" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H323" s="1">
+        <v>1</v>
+      </c>
+      <c r="I323" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A324" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B324" s="1">
+        <v>20005</v>
+      </c>
+      <c r="C324" s="1">
+        <v>1</v>
+      </c>
+      <c r="D324" t="s">
+        <v>516</v>
+      </c>
+      <c r="E324" s="1">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>13</v>
+      </c>
+      <c r="G324" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H324" s="1">
+        <v>1</v>
+      </c>
+      <c r="I324" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A325" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B325" s="1">
+        <v>20005</v>
+      </c>
+      <c r="C325" s="1">
+        <v>1</v>
+      </c>
+      <c r="D325" t="s">
+        <v>514</v>
+      </c>
+      <c r="E325" s="1">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>10</v>
+      </c>
+      <c r="G325" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H325" s="1">
+        <v>1</v>
+      </c>
+      <c r="I325" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A326" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B326" s="1">
+        <v>20006</v>
+      </c>
+      <c r="C326" s="1">
+        <v>1</v>
+      </c>
+      <c r="D326" t="s">
+        <v>501</v>
+      </c>
+      <c r="E326" s="1">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>17</v>
+      </c>
+      <c r="G326" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H326" s="1">
+        <v>1</v>
+      </c>
+      <c r="I326" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A327" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B327" s="1">
+        <v>20006</v>
+      </c>
+      <c r="C327" s="1">
+        <v>1</v>
+      </c>
+      <c r="D327" t="s">
+        <v>527</v>
+      </c>
+      <c r="E327" s="1">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>4</v>
+      </c>
+      <c r="G327" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H327" s="1">
+        <v>1</v>
+      </c>
+      <c r="I327" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A328" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B328" s="1">
+        <v>20006</v>
+      </c>
+      <c r="C328" s="1">
+        <v>1</v>
+      </c>
+      <c r="D328" t="s">
+        <v>528</v>
+      </c>
+      <c r="E328" s="1">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>3</v>
+      </c>
+      <c r="G328" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H328" s="1">
+        <v>1</v>
+      </c>
+      <c r="I328" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A329" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B329" s="1">
+        <v>20006</v>
+      </c>
+      <c r="C329" s="1">
+        <v>1</v>
+      </c>
+      <c r="D329" t="s">
+        <v>529</v>
+      </c>
+      <c r="E329" s="1">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>15</v>
+      </c>
+      <c r="G329" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H329" s="1">
+        <v>1</v>
+      </c>
+      <c r="I329" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A330" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B330" s="1">
+        <v>20006</v>
+      </c>
+      <c r="C330" s="1">
+        <v>1</v>
+      </c>
+      <c r="D330" t="s">
+        <v>530</v>
+      </c>
+      <c r="E330" s="1">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>49</v>
+      </c>
+      <c r="G330" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H330" s="1">
+        <v>1</v>
+      </c>
+      <c r="I330" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A331" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B331" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C331" s="1">
+        <v>1</v>
+      </c>
+      <c r="E331" s="1">
+        <v>0</v>
+      </c>
+      <c r="F331" s="2">
+        <v>6000</v>
+      </c>
+      <c r="G331" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H331" s="1">
+        <v>1</v>
+      </c>
+      <c r="I331" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A332" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B332" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C332" s="1">
+        <v>1</v>
+      </c>
+      <c r="E332" s="1">
+        <v>0</v>
+      </c>
+      <c r="F332" s="2">
+        <v>6001</v>
+      </c>
+      <c r="G332" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H332" s="1">
+        <v>1</v>
+      </c>
+      <c r="I332" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A333" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B333" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C333" s="1">
+        <v>1</v>
+      </c>
+      <c r="E333" s="1">
+        <v>0</v>
+      </c>
+      <c r="F333" s="2">
+        <v>6002</v>
+      </c>
+      <c r="G333" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H333" s="1">
+        <v>1</v>
+      </c>
+      <c r="I333" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A334" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B334" s="1">
+        <v>30000</v>
+      </c>
+      <c r="C334" s="1">
+        <v>1</v>
+      </c>
+      <c r="E334" s="1">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2">
+        <v>6003</v>
+      </c>
+      <c r="G334" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H334" s="1">
+        <v>1</v>
+      </c>
+      <c r="I334" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A335" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B335" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C335" s="1">
+        <v>1</v>
+      </c>
+      <c r="E335" s="1">
+        <v>0</v>
+      </c>
+      <c r="F335" s="2">
+        <v>6004</v>
+      </c>
+      <c r="G335" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H335" s="1">
+        <v>1</v>
+      </c>
+      <c r="I335" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A336" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B336" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C336" s="1">
+        <v>1</v>
+      </c>
+      <c r="E336" s="1">
+        <v>0</v>
+      </c>
+      <c r="F336" s="2">
+        <v>6005</v>
+      </c>
+      <c r="G336" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H336" s="1">
+        <v>1</v>
+      </c>
+      <c r="I336" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A337" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B337" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C337" s="1">
+        <v>1</v>
+      </c>
+      <c r="E337" s="1">
+        <v>0</v>
+      </c>
+      <c r="F337" s="2">
+        <v>6006</v>
+      </c>
+      <c r="G337" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H337" s="1">
+        <v>1</v>
+      </c>
+      <c r="I337" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A338" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B338" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C338" s="1">
+        <v>1</v>
+      </c>
+      <c r="E338" s="1">
+        <v>0</v>
+      </c>
+      <c r="F338" s="1">
+        <v>30</v>
+      </c>
+      <c r="G338" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H338" s="1">
+        <v>1</v>
+      </c>
+      <c r="I338" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A339" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B339" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C339" s="1">
+        <v>1</v>
+      </c>
+      <c r="E339" s="1">
+        <v>0</v>
+      </c>
+      <c r="F339" s="1">
+        <v>8</v>
+      </c>
+      <c r="G339" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H339" s="1">
+        <v>1</v>
+      </c>
+      <c r="I339" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A340" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B340" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C340" s="1">
+        <v>1</v>
+      </c>
+      <c r="E340" s="1">
+        <v>0</v>
+      </c>
+      <c r="F340" s="1">
+        <v>5</v>
+      </c>
+      <c r="G340" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H340" s="1">
+        <v>1</v>
+      </c>
+      <c r="I340" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A341" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B341" s="1">
+        <v>30002</v>
+      </c>
+      <c r="C341" s="1">
+        <v>1</v>
+      </c>
+      <c r="E341" s="1">
+        <v>0</v>
+      </c>
+      <c r="F341" s="1">
+        <v>12</v>
+      </c>
+      <c r="G341" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H341" s="1">
+        <v>1</v>
+      </c>
+      <c r="I341" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A342" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B342" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C342" s="1">
+        <v>1</v>
+      </c>
+      <c r="E342" s="1">
+        <v>0</v>
+      </c>
+      <c r="F342" s="1">
+        <v>24</v>
+      </c>
+      <c r="G342" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H342" s="1">
+        <v>1</v>
+      </c>
+      <c r="I342" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A343" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B343" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C343" s="1">
+        <v>1</v>
+      </c>
+      <c r="E343" s="1">
+        <v>0</v>
+      </c>
+      <c r="F343" s="1">
+        <v>25</v>
+      </c>
+      <c r="G343" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H343" s="1">
+        <v>1</v>
+      </c>
+      <c r="I343" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A344" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B344" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C344" s="1">
+        <v>1</v>
+      </c>
+      <c r="E344" s="1">
+        <v>0</v>
+      </c>
+      <c r="F344" s="1">
+        <v>2</v>
+      </c>
+      <c r="G344" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H344" s="1">
+        <v>1</v>
+      </c>
+      <c r="I344" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A345" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B345" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C345" s="1">
+        <v>1</v>
+      </c>
+      <c r="E345" s="1">
+        <v>0</v>
+      </c>
+      <c r="F345" s="1">
+        <v>19</v>
+      </c>
+      <c r="G345" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H345" s="1">
+        <v>1</v>
+      </c>
+      <c r="I345" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A346" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B346" s="1">
+        <v>30004</v>
+      </c>
+      <c r="C346" s="1">
+        <v>1</v>
+      </c>
+      <c r="E346" s="1">
+        <v>0</v>
+      </c>
+      <c r="F346" s="1">
+        <v>6007</v>
+      </c>
+      <c r="G346" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H346" s="1">
+        <v>1</v>
+      </c>
+      <c r="I346" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A347" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B319" s="1">
+      <c r="B347" s="1">
         <v>30005</v>
       </c>
-      <c r="C319" s="1">
-        <v>1</v>
-      </c>
-      <c r="E319" s="1">
-        <v>0</v>
-      </c>
-      <c r="F319" s="1">
+      <c r="C347" s="1">
+        <v>1</v>
+      </c>
+      <c r="E347" s="1">
+        <v>0</v>
+      </c>
+      <c r="F347" s="1">
+        <v>4</v>
+      </c>
+      <c r="G347" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H347" s="1">
+        <v>1</v>
+      </c>
+      <c r="I347" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A348" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B348" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C348" s="1">
+        <v>1</v>
+      </c>
+      <c r="E348" s="1">
+        <v>0</v>
+      </c>
+      <c r="F348" s="1">
+        <v>1</v>
+      </c>
+      <c r="G348" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H348" s="1">
+        <v>1</v>
+      </c>
+      <c r="I348" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A349" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B349" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C349" s="1">
+        <v>1</v>
+      </c>
+      <c r="E349" s="1">
+        <v>0</v>
+      </c>
+      <c r="F349" s="1">
         <v>17</v>
       </c>
-      <c r="G319" s="1">
+      <c r="G349" s="1">
         <v>5000</v>
       </c>
-      <c r="H319" s="1">
-        <v>1</v>
-      </c>
-      <c r="I319" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A320" s="6" t="s">
+      <c r="H349" s="1">
+        <v>1</v>
+      </c>
+      <c r="I349" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A350" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B320" s="6">
+      <c r="B350" s="6">
         <v>40000</v>
       </c>
-      <c r="C320" s="6">
-        <v>1</v>
-      </c>
-      <c r="D320" s="6" t="s">
+      <c r="C350" s="6">
+        <v>1</v>
+      </c>
+      <c r="D350" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E320" s="6">
-        <v>0</v>
-      </c>
-      <c r="F320" s="7">
-        <f>VLOOKUP(D320,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E350" s="6">
+        <v>0</v>
+      </c>
+      <c r="F350" s="7">
+        <f>VLOOKUP(D350,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1100</v>
       </c>
-      <c r="G320" s="6">
+      <c r="G350" s="6">
         <v>10000</v>
       </c>
-      <c r="H320" s="6">
+      <c r="H350" s="6">
         <v>10</v>
       </c>
-      <c r="I320" s="6">
+      <c r="I350" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A321" s="6" t="s">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A351" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B321" s="6">
+      <c r="B351" s="6">
         <v>40000</v>
       </c>
-      <c r="C321" s="6">
-        <v>1</v>
-      </c>
-      <c r="D321" s="6" t="s">
+      <c r="C351" s="6">
+        <v>1</v>
+      </c>
+      <c r="D351" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E321" s="6">
-        <v>0</v>
-      </c>
-      <c r="F321" s="7">
-        <f>VLOOKUP(D321,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E351" s="6">
+        <v>0</v>
+      </c>
+      <c r="F351" s="7">
+        <f>VLOOKUP(D351,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1101</v>
       </c>
-      <c r="G321" s="6">
+      <c r="G351" s="6">
         <v>9400</v>
       </c>
-      <c r="H321" s="6">
+      <c r="H351" s="6">
         <v>10</v>
       </c>
-      <c r="I321" s="6">
+      <c r="I351" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A322" s="6" t="s">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A352" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B322" s="6">
+      <c r="B352" s="6">
         <v>40000</v>
       </c>
-      <c r="C322" s="6">
-        <v>1</v>
-      </c>
-      <c r="D322" s="6" t="s">
+      <c r="C352" s="6">
+        <v>1</v>
+      </c>
+      <c r="D352" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E322" s="6">
-        <v>0</v>
-      </c>
-      <c r="F322" s="7">
-        <f>VLOOKUP(D322,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E352" s="6">
+        <v>0</v>
+      </c>
+      <c r="F352" s="7">
+        <f>VLOOKUP(D352,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1103</v>
       </c>
-      <c r="G322" s="6">
+      <c r="G352" s="6">
         <v>8800</v>
       </c>
-      <c r="H322" s="6">
+      <c r="H352" s="6">
         <v>10</v>
       </c>
-      <c r="I322" s="6">
+      <c r="I352" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A323" s="6" t="s">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A353" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B323" s="6">
+      <c r="B353" s="6">
         <v>40000</v>
       </c>
-      <c r="C323" s="6">
-        <v>1</v>
-      </c>
-      <c r="D323" s="6" t="s">
+      <c r="C353" s="6">
+        <v>1</v>
+      </c>
+      <c r="D353" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E323" s="6">
-        <v>0</v>
-      </c>
-      <c r="F323" s="7">
-        <f>VLOOKUP(D323,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E353" s="6">
+        <v>0</v>
+      </c>
+      <c r="F353" s="7">
+        <f>VLOOKUP(D353,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1105</v>
       </c>
-      <c r="G323" s="6">
+      <c r="G353" s="6">
         <v>8200</v>
       </c>
-      <c r="H323" s="6">
+      <c r="H353" s="6">
         <v>10</v>
       </c>
-      <c r="I323" s="6">
+      <c r="I353" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A324" s="6" t="s">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A354" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B324" s="6">
+      <c r="B354" s="6">
         <v>40000</v>
       </c>
-      <c r="C324" s="6">
-        <v>1</v>
-      </c>
-      <c r="D324" s="6" t="s">
+      <c r="C354" s="6">
+        <v>1</v>
+      </c>
+      <c r="D354" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E324" s="6">
-        <v>0</v>
-      </c>
-      <c r="F324" s="7">
-        <f>VLOOKUP(D324,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E354" s="6">
+        <v>0</v>
+      </c>
+      <c r="F354" s="7">
+        <f>VLOOKUP(D354,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1106</v>
       </c>
-      <c r="G324" s="6">
+      <c r="G354" s="6">
         <v>7600</v>
       </c>
-      <c r="H324" s="6">
+      <c r="H354" s="6">
         <v>10</v>
       </c>
-      <c r="I324" s="6">
+      <c r="I354" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A325" s="6" t="s">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A355" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B325" s="6">
+      <c r="B355" s="6">
         <v>40000</v>
       </c>
-      <c r="C325" s="6">
-        <v>1</v>
-      </c>
-      <c r="D325" s="6" t="s">
+      <c r="C355" s="6">
+        <v>1</v>
+      </c>
+      <c r="D355" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E325" s="6">
-        <v>0</v>
-      </c>
-      <c r="F325" s="7">
-        <f>VLOOKUP(D325,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E355" s="6">
+        <v>0</v>
+      </c>
+      <c r="F355" s="7">
+        <f>VLOOKUP(D355,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1109</v>
       </c>
-      <c r="G325" s="6">
+      <c r="G355" s="6">
         <v>7000</v>
       </c>
-      <c r="H325" s="6">
+      <c r="H355" s="6">
         <v>10</v>
       </c>
-      <c r="I325" s="6">
+      <c r="I355" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A326" s="6" t="s">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A356" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B326" s="6">
+      <c r="B356" s="6">
         <v>40000</v>
       </c>
-      <c r="C326" s="6">
-        <v>1</v>
-      </c>
-      <c r="D326" s="6" t="s">
+      <c r="C356" s="6">
+        <v>1</v>
+      </c>
+      <c r="D356" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E326" s="6">
-        <v>0</v>
-      </c>
-      <c r="F326" s="7">
-        <f>VLOOKUP(D326,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E356" s="6">
+        <v>0</v>
+      </c>
+      <c r="F356" s="7">
+        <f>VLOOKUP(D356,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1110</v>
       </c>
-      <c r="G326" s="6">
+      <c r="G356" s="6">
         <v>6400</v>
       </c>
-      <c r="H326" s="6">
+      <c r="H356" s="6">
         <v>10</v>
       </c>
-      <c r="I326" s="6">
+      <c r="I356" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A327" s="6" t="s">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A357" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B327" s="6">
+      <c r="B357" s="6">
         <v>40000</v>
       </c>
-      <c r="C327" s="6">
-        <v>1</v>
-      </c>
-      <c r="D327" s="6" t="s">
+      <c r="C357" s="6">
+        <v>1</v>
+      </c>
+      <c r="D357" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E327" s="6">
-        <v>0</v>
-      </c>
-      <c r="F327" s="7">
-        <f>VLOOKUP(D327,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E357" s="6">
+        <v>0</v>
+      </c>
+      <c r="F357" s="7">
+        <f>VLOOKUP(D357,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1111</v>
       </c>
-      <c r="G327" s="6">
+      <c r="G357" s="6">
         <v>5800</v>
       </c>
-      <c r="H327" s="6">
+      <c r="H357" s="6">
         <v>10</v>
       </c>
-      <c r="I327" s="6">
+      <c r="I357" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A328" s="6" t="s">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A358" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B328" s="6">
+      <c r="B358" s="6">
         <v>40000</v>
       </c>
-      <c r="C328" s="6">
-        <v>1</v>
-      </c>
-      <c r="D328" s="6" t="s">
+      <c r="C358" s="6">
+        <v>1</v>
+      </c>
+      <c r="D358" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E328" s="6">
-        <v>0</v>
-      </c>
-      <c r="F328" s="7">
-        <f>VLOOKUP(D328,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E358" s="6">
+        <v>0</v>
+      </c>
+      <c r="F358" s="7">
+        <f>VLOOKUP(D358,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1112</v>
       </c>
-      <c r="G328" s="6">
+      <c r="G358" s="6">
         <v>5200</v>
       </c>
-      <c r="H328" s="6">
+      <c r="H358" s="6">
         <v>10</v>
       </c>
-      <c r="I328" s="6">
+      <c r="I358" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A329" s="6" t="s">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A359" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B329" s="6">
+      <c r="B359" s="6">
         <v>40000</v>
       </c>
-      <c r="C329" s="6">
-        <v>1</v>
-      </c>
-      <c r="D329" s="6" t="s">
+      <c r="C359" s="6">
+        <v>1</v>
+      </c>
+      <c r="D359" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E329" s="6">
-        <v>0</v>
-      </c>
-      <c r="F329" s="7">
-        <f>VLOOKUP(D329,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E359" s="6">
+        <v>0</v>
+      </c>
+      <c r="F359" s="7">
+        <f>VLOOKUP(D359,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1113</v>
       </c>
-      <c r="G329" s="6">
+      <c r="G359" s="6">
         <v>4600</v>
       </c>
-      <c r="H329" s="6">
+      <c r="H359" s="6">
         <v>10</v>
       </c>
-      <c r="I329" s="6">
+      <c r="I359" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A330" s="6" t="s">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A360" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B330" s="6">
+      <c r="B360" s="6">
         <v>40000</v>
       </c>
-      <c r="C330" s="6">
-        <v>1</v>
-      </c>
-      <c r="D330" s="6" t="s">
+      <c r="C360" s="6">
+        <v>1</v>
+      </c>
+      <c r="D360" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E330" s="6">
-        <v>0</v>
-      </c>
-      <c r="F330" s="7">
-        <f>VLOOKUP(D330,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E360" s="6">
+        <v>0</v>
+      </c>
+      <c r="F360" s="7">
+        <f>VLOOKUP(D360,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1114</v>
       </c>
-      <c r="G330" s="6">
+      <c r="G360" s="6">
         <v>4000</v>
       </c>
-      <c r="H330" s="6">
+      <c r="H360" s="6">
         <v>10</v>
       </c>
-      <c r="I330" s="6">
+      <c r="I360" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A331" s="6" t="s">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A361" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B331" s="6">
+      <c r="B361" s="6">
         <v>40000</v>
       </c>
-      <c r="C331" s="6">
-        <v>1</v>
-      </c>
-      <c r="D331" s="6" t="s">
+      <c r="C361" s="6">
+        <v>1</v>
+      </c>
+      <c r="D361" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E331" s="6">
-        <v>0</v>
-      </c>
-      <c r="F331" s="7">
-        <f>VLOOKUP(D331,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E361" s="6">
+        <v>0</v>
+      </c>
+      <c r="F361" s="7">
+        <f>VLOOKUP(D361,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1115</v>
       </c>
-      <c r="G331" s="6">
+      <c r="G361" s="6">
         <v>3400</v>
       </c>
-      <c r="H331" s="6">
+      <c r="H361" s="6">
         <v>10</v>
       </c>
-      <c r="I331" s="6">
+      <c r="I361" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A332" s="6" t="s">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A362" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B332" s="6">
+      <c r="B362" s="6">
         <v>40000</v>
       </c>
-      <c r="C332" s="6">
-        <v>1</v>
-      </c>
-      <c r="D332" s="6" t="s">
+      <c r="C362" s="6">
+        <v>1</v>
+      </c>
+      <c r="D362" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E332" s="6">
-        <v>0</v>
-      </c>
-      <c r="F332" s="7">
-        <f>VLOOKUP(D332,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E362" s="6">
+        <v>0</v>
+      </c>
+      <c r="F362" s="7">
+        <f>VLOOKUP(D362,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1116</v>
       </c>
-      <c r="G332" s="6">
+      <c r="G362" s="6">
         <v>2800</v>
       </c>
-      <c r="H332" s="6">
+      <c r="H362" s="6">
         <v>10</v>
       </c>
-      <c r="I332" s="6">
+      <c r="I362" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A333" s="6" t="s">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A363" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B333" s="6">
+      <c r="B363" s="6">
         <v>40000</v>
       </c>
-      <c r="C333" s="6">
-        <v>1</v>
-      </c>
-      <c r="D333" s="6" t="s">
+      <c r="C363" s="6">
+        <v>1</v>
+      </c>
+      <c r="D363" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E333" s="6">
-        <v>0</v>
-      </c>
-      <c r="F333" s="7">
-        <f>VLOOKUP(D333,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E363" s="6">
+        <v>0</v>
+      </c>
+      <c r="F363" s="7">
+        <f>VLOOKUP(D363,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1117</v>
       </c>
-      <c r="G333" s="6">
+      <c r="G363" s="6">
         <v>2200</v>
       </c>
-      <c r="H333" s="6">
+      <c r="H363" s="6">
         <v>10</v>
       </c>
-      <c r="I333" s="6">
+      <c r="I363" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A334" s="8" t="s">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A364" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B334" s="8">
+      <c r="B364" s="8">
         <v>40001</v>
       </c>
-      <c r="C334" s="8">
-        <v>1</v>
-      </c>
-      <c r="D334" s="8" t="s">
+      <c r="C364" s="8">
+        <v>1</v>
+      </c>
+      <c r="D364" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E334" s="8">
-        <v>0</v>
-      </c>
-      <c r="F334" s="9">
-        <f>VLOOKUP(D334,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E364" s="8">
+        <v>0</v>
+      </c>
+      <c r="F364" s="9">
+        <f>VLOOKUP(D364,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1009</v>
       </c>
-      <c r="G334" s="8">
+      <c r="G364" s="8">
         <v>8800</v>
       </c>
-      <c r="H334" s="8">
+      <c r="H364" s="8">
         <v>10</v>
       </c>
-      <c r="I334" s="8">
+      <c r="I364" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A335" s="8" t="s">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A365" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B335" s="8">
+      <c r="B365" s="8">
         <v>40001</v>
       </c>
-      <c r="C335" s="8">
-        <v>1</v>
-      </c>
-      <c r="D335" s="8" t="s">
+      <c r="C365" s="8">
+        <v>1</v>
+      </c>
+      <c r="D365" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E335" s="8">
-        <v>0</v>
-      </c>
-      <c r="F335" s="9">
-        <f>VLOOKUP(D335,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E365" s="8">
+        <v>0</v>
+      </c>
+      <c r="F365" s="9">
+        <f>VLOOKUP(D365,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1011</v>
       </c>
-      <c r="G335" s="8">
+      <c r="G365" s="8">
         <v>7600</v>
       </c>
-      <c r="H335" s="8">
+      <c r="H365" s="8">
         <v>10</v>
       </c>
-      <c r="I335" s="8">
+      <c r="I365" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A336" s="8" t="s">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A366" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B336" s="8">
+      <c r="B366" s="8">
         <v>40001</v>
       </c>
-      <c r="C336" s="8">
-        <v>1</v>
-      </c>
-      <c r="D336" s="8" t="s">
+      <c r="C366" s="8">
+        <v>1</v>
+      </c>
+      <c r="D366" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E336" s="8">
-        <v>0</v>
-      </c>
-      <c r="F336" s="9">
-        <f>VLOOKUP(D336,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E366" s="8">
+        <v>0</v>
+      </c>
+      <c r="F366" s="9">
+        <f>VLOOKUP(D366,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1014</v>
       </c>
-      <c r="G336" s="8">
+      <c r="G366" s="8">
         <v>6400</v>
       </c>
-      <c r="H336" s="8">
+      <c r="H366" s="8">
         <v>10</v>
       </c>
-      <c r="I336" s="8">
+      <c r="I366" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A337" s="8" t="s">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A367" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B337" s="8">
+      <c r="B367" s="8">
         <v>40001</v>
       </c>
-      <c r="C337" s="8">
-        <v>1</v>
-      </c>
-      <c r="D337" s="8" t="s">
+      <c r="C367" s="8">
+        <v>1</v>
+      </c>
+      <c r="D367" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E337" s="8">
-        <v>0</v>
-      </c>
-      <c r="F337" s="9">
-        <f>VLOOKUP(D337,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E367" s="8">
+        <v>0</v>
+      </c>
+      <c r="F367" s="9">
+        <f>VLOOKUP(D367,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1016</v>
       </c>
-      <c r="G337" s="8">
+      <c r="G367" s="8">
         <v>5200</v>
       </c>
-      <c r="H337" s="8">
+      <c r="H367" s="8">
         <v>10</v>
       </c>
-      <c r="I337" s="8">
+      <c r="I367" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A338" s="8" t="s">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A368" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B338" s="8">
+      <c r="B368" s="8">
         <v>40001</v>
       </c>
-      <c r="C338" s="8">
-        <v>1</v>
-      </c>
-      <c r="D338" s="8" t="s">
+      <c r="C368" s="8">
+        <v>1</v>
+      </c>
+      <c r="D368" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E338" s="8">
-        <v>0</v>
-      </c>
-      <c r="F338" s="9">
-        <f>VLOOKUP(D338,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E368" s="8">
+        <v>0</v>
+      </c>
+      <c r="F368" s="9">
+        <f>VLOOKUP(D368,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1017</v>
       </c>
-      <c r="G338" s="8">
+      <c r="G368" s="8">
         <v>4000</v>
       </c>
-      <c r="H338" s="8">
+      <c r="H368" s="8">
         <v>10</v>
       </c>
-      <c r="I338" s="8">
+      <c r="I368" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A339" s="8" t="s">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A369" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B339" s="8">
+      <c r="B369" s="8">
         <v>40001</v>
       </c>
-      <c r="C339" s="8">
-        <v>1</v>
-      </c>
-      <c r="D339" s="8" t="s">
+      <c r="C369" s="8">
+        <v>1</v>
+      </c>
+      <c r="D369" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E339" s="8">
-        <v>0</v>
-      </c>
-      <c r="F339" s="9">
-        <f>VLOOKUP(D339,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E369" s="8">
+        <v>0</v>
+      </c>
+      <c r="F369" s="9">
+        <f>VLOOKUP(D369,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1022</v>
       </c>
-      <c r="G339" s="8">
+      <c r="G369" s="8">
         <v>2800</v>
       </c>
-      <c r="H339" s="8">
+      <c r="H369" s="8">
         <v>10</v>
       </c>
-      <c r="I339" s="8">
+      <c r="I369" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A340" s="8" t="s">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A370" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B340" s="8">
+      <c r="B370" s="8">
         <v>40001</v>
       </c>
-      <c r="C340" s="8">
-        <v>1</v>
-      </c>
-      <c r="D340" s="8" t="s">
+      <c r="C370" s="8">
+        <v>1</v>
+      </c>
+      <c r="D370" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E340" s="8">
-        <v>0</v>
-      </c>
-      <c r="F340" s="9">
-        <f>VLOOKUP(D340,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E370" s="8">
+        <v>0</v>
+      </c>
+      <c r="F370" s="9">
+        <f>VLOOKUP(D370,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1024</v>
       </c>
-      <c r="G340" s="8">
+      <c r="G370" s="8">
         <v>1600</v>
       </c>
-      <c r="H340" s="8">
+      <c r="H370" s="8">
         <v>10</v>
       </c>
-      <c r="I340" s="8">
+      <c r="I370" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A341" s="4" t="s">
+    <row r="371" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A371" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B341" s="4">
+      <c r="B371" s="4">
         <v>40002</v>
       </c>
-      <c r="C341" s="4">
-        <v>1</v>
-      </c>
-      <c r="D341" s="10" t="s">
+      <c r="C371" s="4">
+        <v>1</v>
+      </c>
+      <c r="D371" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E341" s="4">
-        <v>0</v>
-      </c>
-      <c r="F341" s="5">
-        <f>VLOOKUP(D341,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E371" s="4">
+        <v>0</v>
+      </c>
+      <c r="F371" s="5">
+        <f>VLOOKUP(D371,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="G341" s="4">
+      <c r="G371" s="4">
         <v>10000</v>
       </c>
-      <c r="H341" s="4">
+      <c r="H371" s="4">
         <v>10</v>
       </c>
-      <c r="I341" s="4">
+      <c r="I371" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A342" s="4" t="s">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A372" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B342" s="4">
+      <c r="B372" s="4">
         <v>40002</v>
       </c>
-      <c r="C342" s="4">
-        <v>1</v>
-      </c>
-      <c r="D342" s="4" t="s">
+      <c r="C372" s="4">
+        <v>1</v>
+      </c>
+      <c r="D372" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E342" s="4">
-        <v>0</v>
-      </c>
-      <c r="F342" s="5">
-        <f>VLOOKUP(D342,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E372" s="4">
+        <v>0</v>
+      </c>
+      <c r="F372" s="5">
+        <f>VLOOKUP(D372,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1010</v>
       </c>
-      <c r="G342" s="4">
+      <c r="G372" s="4">
         <v>7200</v>
       </c>
-      <c r="H342" s="4">
+      <c r="H372" s="4">
         <v>10</v>
       </c>
-      <c r="I342" s="4">
+      <c r="I372" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A343" s="4" t="s">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A373" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B343" s="4">
+      <c r="B373" s="4">
         <v>40002</v>
       </c>
-      <c r="C343" s="4">
-        <v>1</v>
-      </c>
-      <c r="D343" s="4" t="s">
+      <c r="C373" s="4">
+        <v>1</v>
+      </c>
+      <c r="D373" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E343" s="4">
-        <v>0</v>
-      </c>
-      <c r="F343" s="5">
-        <f>VLOOKUP(D343,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E373" s="4">
+        <v>0</v>
+      </c>
+      <c r="F373" s="5">
+        <f>VLOOKUP(D373,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1013</v>
       </c>
-      <c r="G343" s="4">
+      <c r="G373" s="4">
         <v>5800</v>
       </c>
-      <c r="H343" s="4">
+      <c r="H373" s="4">
         <v>10</v>
       </c>
-      <c r="I343" s="4">
+      <c r="I373" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A344" s="4" t="s">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A374" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B374" s="4">
         <v>40002</v>
       </c>
-      <c r="C344" s="4">
-        <v>1</v>
-      </c>
-      <c r="D344" s="4" t="s">
+      <c r="C374" s="4">
+        <v>1</v>
+      </c>
+      <c r="D374" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E344" s="4">
-        <v>0</v>
-      </c>
-      <c r="F344" s="5">
-        <f>VLOOKUP(D344,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E374" s="4">
+        <v>0</v>
+      </c>
+      <c r="F374" s="5">
+        <f>VLOOKUP(D374,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1018</v>
       </c>
-      <c r="G344" s="4">
+      <c r="G374" s="4">
         <v>4400</v>
       </c>
-      <c r="H344" s="4">
+      <c r="H374" s="4">
         <v>10</v>
       </c>
-      <c r="I344" s="4">
+      <c r="I374" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A345" s="4" t="s">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A375" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B375" s="4">
         <v>40002</v>
       </c>
-      <c r="C345" s="4">
-        <v>1</v>
-      </c>
-      <c r="D345" s="4" t="s">
+      <c r="C375" s="4">
+        <v>1</v>
+      </c>
+      <c r="D375" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E345" s="4">
-        <v>0</v>
-      </c>
-      <c r="F345" s="5">
-        <f>VLOOKUP(D345,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E375" s="4">
+        <v>0</v>
+      </c>
+      <c r="F375" s="5">
+        <f>VLOOKUP(D375,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1020</v>
       </c>
-      <c r="G345" s="4">
+      <c r="G375" s="4">
         <v>3000</v>
       </c>
-      <c r="H345" s="4">
+      <c r="H375" s="4">
         <v>10</v>
       </c>
-      <c r="I345" s="4">
+      <c r="I375" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A346" s="4" t="s">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A376" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B346" s="4">
+      <c r="B376" s="4">
         <v>40002</v>
       </c>
-      <c r="C346" s="4">
-        <v>1</v>
-      </c>
-      <c r="D346" s="4" t="s">
+      <c r="C376" s="4">
+        <v>1</v>
+      </c>
+      <c r="D376" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E346" s="4">
-        <v>0</v>
-      </c>
-      <c r="F346" s="5">
-        <f>VLOOKUP(D346,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E376" s="4">
+        <v>0</v>
+      </c>
+      <c r="F376" s="5">
+        <f>VLOOKUP(D376,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1023</v>
       </c>
-      <c r="G346" s="4">
+      <c r="G376" s="4">
         <v>1600</v>
       </c>
-      <c r="H346" s="4">
+      <c r="H376" s="4">
         <v>10</v>
       </c>
-      <c r="I346" s="4">
+      <c r="I376" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A347" s="8" t="s">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A377" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B347" s="8">
+      <c r="B377" s="8">
         <v>40003</v>
       </c>
-      <c r="C347" s="8">
-        <v>1</v>
-      </c>
-      <c r="D347" s="8" t="s">
+      <c r="C377" s="8">
+        <v>1</v>
+      </c>
+      <c r="D377" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E347" s="8">
-        <v>0</v>
-      </c>
-      <c r="F347" s="9">
-        <f>VLOOKUP(D347,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E377" s="8">
+        <v>0</v>
+      </c>
+      <c r="F377" s="9">
+        <f>VLOOKUP(D377,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="G347" s="8">
+      <c r="G377" s="8">
         <v>10000</v>
       </c>
-      <c r="H347" s="8">
+      <c r="H377" s="8">
         <v>10</v>
       </c>
-      <c r="I347" s="8">
+      <c r="I377" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A348" s="8" t="s">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A378" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B348" s="8">
+      <c r="B378" s="8">
         <v>40003</v>
       </c>
-      <c r="C348" s="8">
-        <v>1</v>
-      </c>
-      <c r="D348" s="8" t="s">
+      <c r="C378" s="8">
+        <v>1</v>
+      </c>
+      <c r="D378" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E348" s="8">
-        <v>0</v>
-      </c>
-      <c r="F348" s="9">
-        <f>VLOOKUP(D348,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E378" s="8">
+        <v>0</v>
+      </c>
+      <c r="F378" s="9">
+        <f>VLOOKUP(D378,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1009</v>
       </c>
-      <c r="G348" s="8">
+      <c r="G378" s="8">
         <v>8600</v>
       </c>
-      <c r="H348" s="8">
+      <c r="H378" s="8">
         <v>10</v>
       </c>
-      <c r="I348" s="8">
+      <c r="I378" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A349" s="8" t="s">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A379" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B349" s="8">
+      <c r="B379" s="8">
         <v>40003</v>
       </c>
-      <c r="C349" s="8">
-        <v>1</v>
-      </c>
-      <c r="D349" s="8" t="s">
+      <c r="C379" s="8">
+        <v>1</v>
+      </c>
+      <c r="D379" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E349" s="8">
-        <v>0</v>
-      </c>
-      <c r="F349" s="9">
-        <f>VLOOKUP(D349,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E379" s="8">
+        <v>0</v>
+      </c>
+      <c r="F379" s="9">
+        <f>VLOOKUP(D379,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1006</v>
       </c>
-      <c r="G349" s="8">
+      <c r="G379" s="8">
         <v>7200</v>
       </c>
-      <c r="H349" s="8">
+      <c r="H379" s="8">
         <v>10</v>
       </c>
-      <c r="I349" s="8">
+      <c r="I379" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A350" s="8" t="s">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A380" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B350" s="8">
+      <c r="B380" s="8">
         <v>40003</v>
       </c>
-      <c r="C350" s="8">
-        <v>1</v>
-      </c>
-      <c r="D350" s="8" t="s">
+      <c r="C380" s="8">
+        <v>1</v>
+      </c>
+      <c r="D380" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E350" s="8">
-        <v>0</v>
-      </c>
-      <c r="F350" s="9">
-        <f>VLOOKUP(D350,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E380" s="8">
+        <v>0</v>
+      </c>
+      <c r="F380" s="9">
+        <f>VLOOKUP(D380,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1007</v>
       </c>
-      <c r="G350" s="8">
+      <c r="G380" s="8">
         <v>5800</v>
       </c>
-      <c r="H350" s="8">
+      <c r="H380" s="8">
         <v>10</v>
       </c>
-      <c r="I350" s="8">
+      <c r="I380" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A351" s="8" t="s">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A381" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B351" s="8">
+      <c r="B381" s="8">
         <v>40003</v>
       </c>
-      <c r="C351" s="8">
-        <v>1</v>
-      </c>
-      <c r="D351" s="8" t="s">
+      <c r="C381" s="8">
+        <v>1</v>
+      </c>
+      <c r="D381" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E351" s="8">
-        <v>0</v>
-      </c>
-      <c r="F351" s="9">
-        <f>VLOOKUP(D351,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E381" s="8">
+        <v>0</v>
+      </c>
+      <c r="F381" s="9">
+        <f>VLOOKUP(D381,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1014</v>
       </c>
-      <c r="G351" s="8">
+      <c r="G381" s="8">
         <v>4400</v>
       </c>
-      <c r="H351" s="8">
+      <c r="H381" s="8">
         <v>10</v>
       </c>
-      <c r="I351" s="8">
+      <c r="I381" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A352" s="8" t="s">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A382" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B352" s="8">
+      <c r="B382" s="8">
         <v>40003</v>
       </c>
-      <c r="C352" s="8">
-        <v>1</v>
-      </c>
-      <c r="D352" s="8" t="s">
+      <c r="C382" s="8">
+        <v>1</v>
+      </c>
+      <c r="D382" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E352" s="8">
-        <v>0</v>
-      </c>
-      <c r="F352" s="9">
-        <f>VLOOKUP(D352,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E382" s="8">
+        <v>0</v>
+      </c>
+      <c r="F382" s="9">
+        <f>VLOOKUP(D382,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1017</v>
       </c>
-      <c r="G352" s="8">
+      <c r="G382" s="8">
         <v>3000</v>
       </c>
-      <c r="H352" s="8">
+      <c r="H382" s="8">
         <v>10</v>
       </c>
-      <c r="I352" s="8">
+      <c r="I382" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A353" s="8" t="s">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A383" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B353" s="8">
+      <c r="B383" s="8">
         <v>40003</v>
       </c>
-      <c r="C353" s="8">
-        <v>1</v>
-      </c>
-      <c r="D353" s="8" t="s">
+      <c r="C383" s="8">
+        <v>1</v>
+      </c>
+      <c r="D383" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E353" s="8">
-        <v>0</v>
-      </c>
-      <c r="F353" s="9">
-        <f>VLOOKUP(D353,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E383" s="8">
+        <v>0</v>
+      </c>
+      <c r="F383" s="9">
+        <f>VLOOKUP(D383,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1020</v>
       </c>
-      <c r="G353" s="8">
+      <c r="G383" s="8">
         <v>1600</v>
       </c>
-      <c r="H353" s="8">
+      <c r="H383" s="8">
         <v>10</v>
       </c>
-      <c r="I353" s="8">
+      <c r="I383" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A354" s="1" t="s">
+    <row r="384" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A384" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B354" s="1">
+      <c r="B384" s="1">
         <v>40004</v>
       </c>
-      <c r="C354" s="1">
-        <v>1</v>
-      </c>
-      <c r="D354" s="3" t="s">
+      <c r="C384" s="1">
+        <v>1</v>
+      </c>
+      <c r="D384" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E354" s="1">
-        <v>0</v>
-      </c>
-      <c r="F354">
-        <f>VLOOKUP(D354,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E384" s="1">
+        <v>0</v>
+      </c>
+      <c r="F384">
+        <f>VLOOKUP(D384,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="G354" s="1">
+      <c r="G384" s="1">
         <v>10000</v>
       </c>
-      <c r="H354" s="1">
+      <c r="H384" s="1">
         <v>10</v>
       </c>
-      <c r="I354" s="1">
+      <c r="I384" s="1">
         <v>30</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A355" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B355" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C355" s="1">
-        <v>1</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E355" s="1">
-        <v>0</v>
-      </c>
-      <c r="F355">
-        <f>VLOOKUP(D355,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1006</v>
-      </c>
-      <c r="G355" s="1">
-        <v>7200</v>
-      </c>
-      <c r="H355" s="1">
-        <v>10</v>
-      </c>
-      <c r="I355" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A356" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B356" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C356" s="1">
-        <v>1</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E356" s="1">
-        <v>0</v>
-      </c>
-      <c r="F356">
-        <f>VLOOKUP(D356,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1007</v>
-      </c>
-      <c r="G356" s="1">
-        <v>5800</v>
-      </c>
-      <c r="H356" s="1">
-        <v>10</v>
-      </c>
-      <c r="I356" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A357" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B357" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C357" s="1">
-        <v>1</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E357" s="1">
-        <v>0</v>
-      </c>
-      <c r="F357">
-        <f>VLOOKUP(D357,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1010</v>
-      </c>
-      <c r="G357" s="1">
-        <v>4400</v>
-      </c>
-      <c r="H357" s="1">
-        <v>10</v>
-      </c>
-      <c r="I357" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A358" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B358" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C358" s="1">
-        <v>1</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E358" s="1">
-        <v>0</v>
-      </c>
-      <c r="F358">
-        <f>VLOOKUP(D358,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1015</v>
-      </c>
-      <c r="G358" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H358" s="1">
-        <v>10</v>
-      </c>
-      <c r="I358" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A359" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B359" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C359" s="1">
-        <v>1</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E359" s="1">
-        <v>0</v>
-      </c>
-      <c r="F359">
-        <f>VLOOKUP(D359,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1021</v>
-      </c>
-      <c r="G359" s="1">
-        <v>1600</v>
-      </c>
-      <c r="H359" s="1">
-        <v>10</v>
-      </c>
-      <c r="I359" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A360" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B360" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C360" s="1">
-        <v>1</v>
-      </c>
-      <c r="D360" t="s">
-        <v>499</v>
-      </c>
-      <c r="E360" s="1">
-        <v>0</v>
-      </c>
-      <c r="F360">
-        <v>42</v>
-      </c>
-      <c r="G360" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H360" s="1">
-        <v>1</v>
-      </c>
-      <c r="I360" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A361" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B361" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C361" s="1">
-        <v>1</v>
-      </c>
-      <c r="D361" t="s">
-        <v>500</v>
-      </c>
-      <c r="E361" s="1">
-        <v>0</v>
-      </c>
-      <c r="F361">
-        <v>48</v>
-      </c>
-      <c r="G361" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H361" s="1">
-        <v>1</v>
-      </c>
-      <c r="I361" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A362" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B362" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C362" s="1">
-        <v>1</v>
-      </c>
-      <c r="D362" t="s">
-        <v>502</v>
-      </c>
-      <c r="E362" s="1">
-        <v>0</v>
-      </c>
-      <c r="F362">
-        <v>17</v>
-      </c>
-      <c r="G362" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H362" s="1">
-        <v>1</v>
-      </c>
-      <c r="I362" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A363" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B363" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C363" s="1">
-        <v>1</v>
-      </c>
-      <c r="D363" t="s">
-        <v>503</v>
-      </c>
-      <c r="E363" s="1">
-        <v>0</v>
-      </c>
-      <c r="F363">
-        <v>18</v>
-      </c>
-      <c r="G363" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H363" s="1">
-        <v>1</v>
-      </c>
-      <c r="I363" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A364" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B364" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C364" s="1">
-        <v>1</v>
-      </c>
-      <c r="D364" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E364" s="1">
-        <v>0</v>
-      </c>
-      <c r="F364" s="1">
-        <v>1</v>
-      </c>
-      <c r="G364" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H364" s="1">
-        <v>1</v>
-      </c>
-      <c r="I364" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A365" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="B365" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C365" s="1">
-        <v>1</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="E365" s="1">
-        <v>0</v>
-      </c>
-      <c r="F365" s="1">
-        <v>24</v>
-      </c>
-      <c r="G365" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H365" s="1">
-        <v>1</v>
-      </c>
-      <c r="I365" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A366" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B366" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C366" s="1">
-        <v>1</v>
-      </c>
-      <c r="D366" t="s">
-        <v>512</v>
-      </c>
-      <c r="E366" s="1">
-        <v>0</v>
-      </c>
-      <c r="F366">
-        <v>61</v>
-      </c>
-      <c r="G366" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H366" s="1">
-        <v>1</v>
-      </c>
-      <c r="I366" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A367" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B367" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C367" s="1">
-        <v>1</v>
-      </c>
-      <c r="D367" t="s">
-        <v>513</v>
-      </c>
-      <c r="E367" s="1">
-        <v>0</v>
-      </c>
-      <c r="F367">
-        <v>16</v>
-      </c>
-      <c r="G367" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H367" s="1">
-        <v>1</v>
-      </c>
-      <c r="I367" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A368" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B368" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C368" s="1">
-        <v>1</v>
-      </c>
-      <c r="D368" t="s">
-        <v>515</v>
-      </c>
-      <c r="E368" s="1">
-        <v>0</v>
-      </c>
-      <c r="F368">
-        <v>31</v>
-      </c>
-      <c r="G368" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H368" s="1">
-        <v>1</v>
-      </c>
-      <c r="I368" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A369" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B369" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C369" s="1">
-        <v>1</v>
-      </c>
-      <c r="D369" t="s">
-        <v>503</v>
-      </c>
-      <c r="E369" s="1">
-        <v>0</v>
-      </c>
-      <c r="F369">
-        <v>18</v>
-      </c>
-      <c r="G369" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H369" s="1">
-        <v>1</v>
-      </c>
-      <c r="I369" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A370" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B370" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C370" s="1">
-        <v>1</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E370" s="1">
-        <v>0</v>
-      </c>
-      <c r="F370" s="1">
-        <v>1</v>
-      </c>
-      <c r="G370" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H370" s="1">
-        <v>1</v>
-      </c>
-      <c r="I370" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A371" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B371" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C371" s="1">
-        <v>1</v>
-      </c>
-      <c r="D371" t="s">
-        <v>518</v>
-      </c>
-      <c r="E371" s="1">
-        <v>0</v>
-      </c>
-      <c r="F371">
-        <v>14</v>
-      </c>
-      <c r="G371" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H371" s="1">
-        <v>1</v>
-      </c>
-      <c r="I371" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A372" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B372" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C372" s="1">
-        <v>1</v>
-      </c>
-      <c r="D372" t="s">
-        <v>519</v>
-      </c>
-      <c r="E372" s="1">
-        <v>0</v>
-      </c>
-      <c r="F372">
-        <v>16</v>
-      </c>
-      <c r="G372" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H372" s="1">
-        <v>1</v>
-      </c>
-      <c r="I372" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A373" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B373" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C373" s="1">
-        <v>1</v>
-      </c>
-      <c r="D373" t="s">
-        <v>520</v>
-      </c>
-      <c r="E373" s="1">
-        <v>0</v>
-      </c>
-      <c r="F373">
-        <v>17</v>
-      </c>
-      <c r="G373" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H373" s="1">
-        <v>1</v>
-      </c>
-      <c r="I373" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A374" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B374" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C374" s="1">
-        <v>1</v>
-      </c>
-      <c r="D374" t="s">
-        <v>521</v>
-      </c>
-      <c r="E374" s="1">
-        <v>0</v>
-      </c>
-      <c r="F374">
-        <v>18</v>
-      </c>
-      <c r="G374" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H374" s="1">
-        <v>1</v>
-      </c>
-      <c r="I374" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A375" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B375" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C375" s="1">
-        <v>1</v>
-      </c>
-      <c r="D375" t="s">
-        <v>523</v>
-      </c>
-      <c r="E375" s="1">
-        <v>0</v>
-      </c>
-      <c r="F375">
-        <v>25</v>
-      </c>
-      <c r="G375" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H375" s="1">
-        <v>1</v>
-      </c>
-      <c r="I375" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A376" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B376" s="1">
-        <v>20004</v>
-      </c>
-      <c r="C376" s="1">
-        <v>1</v>
-      </c>
-      <c r="D376" t="s">
-        <v>524</v>
-      </c>
-      <c r="E376" s="1">
-        <v>0</v>
-      </c>
-      <c r="F376">
-        <v>12</v>
-      </c>
-      <c r="G376" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H376" s="1">
-        <v>1</v>
-      </c>
-      <c r="I376" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A377" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B377" s="1">
-        <v>20004</v>
-      </c>
-      <c r="C377" s="1">
-        <v>1</v>
-      </c>
-      <c r="D377" t="s">
-        <v>516</v>
-      </c>
-      <c r="E377" s="1">
-        <v>0</v>
-      </c>
-      <c r="F377">
-        <v>13</v>
-      </c>
-      <c r="G377" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H377" s="1">
-        <v>1</v>
-      </c>
-      <c r="I377" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A378" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B378" s="1">
-        <v>20004</v>
-      </c>
-      <c r="C378" s="1">
-        <v>1</v>
-      </c>
-      <c r="D378" t="s">
-        <v>525</v>
-      </c>
-      <c r="E378" s="1">
-        <v>0</v>
-      </c>
-      <c r="F378">
-        <v>8</v>
-      </c>
-      <c r="G378" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H378" s="1">
-        <v>1</v>
-      </c>
-      <c r="I378" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A379" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B379" s="1">
-        <v>20004</v>
-      </c>
-      <c r="C379" s="1">
-        <v>1</v>
-      </c>
-      <c r="D379" t="s">
-        <v>526</v>
-      </c>
-      <c r="E379" s="1">
-        <v>0</v>
-      </c>
-      <c r="F379">
-        <v>76</v>
-      </c>
-      <c r="G379" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H379" s="1">
-        <v>1</v>
-      </c>
-      <c r="I379" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A380" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B380" s="1">
-        <v>20004</v>
-      </c>
-      <c r="C380" s="1">
-        <v>1</v>
-      </c>
-      <c r="D380" t="s">
-        <v>512</v>
-      </c>
-      <c r="E380" s="1">
-        <v>0</v>
-      </c>
-      <c r="F380">
-        <v>61</v>
-      </c>
-      <c r="G380" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H380" s="1">
-        <v>1</v>
-      </c>
-      <c r="I380" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A381" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B381" s="1">
-        <v>20005</v>
-      </c>
-      <c r="C381" s="1">
-        <v>1</v>
-      </c>
-      <c r="D381" t="s">
-        <v>517</v>
-      </c>
-      <c r="E381" s="1">
-        <v>0</v>
-      </c>
-      <c r="F381">
-        <v>14</v>
-      </c>
-      <c r="G381" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H381" s="1">
-        <v>1</v>
-      </c>
-      <c r="I381" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A382" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B382" s="1">
-        <v>20005</v>
-      </c>
-      <c r="C382" s="1">
-        <v>1</v>
-      </c>
-      <c r="D382" t="s">
-        <v>522</v>
-      </c>
-      <c r="E382" s="1">
-        <v>0</v>
-      </c>
-      <c r="F382">
-        <v>19</v>
-      </c>
-      <c r="G382" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H382" s="1">
-        <v>1</v>
-      </c>
-      <c r="I382" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A383" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B383" s="1">
-        <v>20005</v>
-      </c>
-      <c r="C383" s="1">
-        <v>1</v>
-      </c>
-      <c r="D383" t="s">
-        <v>516</v>
-      </c>
-      <c r="E383" s="1">
-        <v>0</v>
-      </c>
-      <c r="F383">
-        <v>13</v>
-      </c>
-      <c r="G383" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H383" s="1">
-        <v>1</v>
-      </c>
-      <c r="I383" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A384" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B384" s="1">
-        <v>20005</v>
-      </c>
-      <c r="C384" s="1">
-        <v>1</v>
-      </c>
-      <c r="D384" t="s">
-        <v>514</v>
-      </c>
-      <c r="E384" s="1">
-        <v>0</v>
-      </c>
-      <c r="F384">
-        <v>10</v>
-      </c>
-      <c r="G384" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H384" s="1">
-        <v>1</v>
-      </c>
-      <c r="I384" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
-        <v>511</v>
+        <v>28</v>
       </c>
       <c r="B385" s="1">
-        <v>20006</v>
+        <v>40004</v>
       </c>
       <c r="C385" s="1">
         <v>1</v>
       </c>
-      <c r="D385" t="s">
-        <v>501</v>
+      <c r="D385" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E385" s="1">
         <v>0</v>
       </c>
       <c r="F385">
-        <v>17</v>
+        <f>VLOOKUP(D385,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
       </c>
       <c r="G385" s="1">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="H385" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I385" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
-        <v>511</v>
+        <v>28</v>
       </c>
       <c r="B386" s="1">
-        <v>20006</v>
+        <v>40004</v>
       </c>
       <c r="C386" s="1">
         <v>1</v>
       </c>
-      <c r="D386" t="s">
-        <v>527</v>
+      <c r="D386" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E386" s="1">
         <v>0</v>
       </c>
       <c r="F386">
-        <v>4</v>
+        <f>VLOOKUP(D386,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
       </c>
       <c r="G386" s="1">
-        <v>1000</v>
+        <v>5800</v>
       </c>
       <c r="H386" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I386" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
-        <v>511</v>
+        <v>28</v>
       </c>
       <c r="B387" s="1">
-        <v>20006</v>
+        <v>40004</v>
       </c>
       <c r="C387" s="1">
         <v>1</v>
       </c>
-      <c r="D387" t="s">
-        <v>528</v>
+      <c r="D387" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E387" s="1">
         <v>0</v>
       </c>
       <c r="F387">
-        <v>3</v>
+        <f>VLOOKUP(D387,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
       </c>
       <c r="G387" s="1">
-        <v>1000</v>
+        <v>4400</v>
       </c>
       <c r="H387" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I387" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
-        <v>511</v>
+        <v>28</v>
       </c>
       <c r="B388" s="1">
-        <v>20006</v>
+        <v>40004</v>
       </c>
       <c r="C388" s="1">
         <v>1</v>
       </c>
-      <c r="D388" t="s">
-        <v>529</v>
+      <c r="D388" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E388" s="1">
         <v>0</v>
       </c>
       <c r="F388">
-        <v>15</v>
+        <f>VLOOKUP(D388,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1015</v>
       </c>
       <c r="G388" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H388" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I388" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
-        <v>511</v>
+        <v>28</v>
       </c>
       <c r="B389" s="1">
-        <v>20006</v>
+        <v>40004</v>
       </c>
       <c r="C389" s="1">
         <v>1</v>
       </c>
-      <c r="D389" t="s">
-        <v>530</v>
+      <c r="D389" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
       </c>
       <c r="F389">
-        <v>49</v>
+        <f>VLOOKUP(D389,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1021</v>
       </c>
       <c r="G389" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H389" s="1">
+        <v>10</v>
+      </c>
+      <c r="I389" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A390" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B390" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C390" s="1">
+        <v>1</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E390" s="1">
+        <v>0</v>
+      </c>
+      <c r="F390" s="1">
+        <f>VLOOKUP(D390,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5006</v>
+      </c>
+      <c r="G390" s="1">
         <v>1000</v>
       </c>
-      <c r="H389" s="1">
-        <v>1</v>
-      </c>
-      <c r="I389" s="1">
+      <c r="H390" s="1">
+        <v>1</v>
+      </c>
+      <c r="I390" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A391" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B391" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C391" s="1">
+        <v>1</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E391" s="1">
+        <v>0</v>
+      </c>
+      <c r="F391" s="1">
+        <f>VLOOKUP(D391,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5007</v>
+      </c>
+      <c r="G391" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H391" s="1">
+        <v>1</v>
+      </c>
+      <c r="I391" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A392" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B392" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C392" s="1">
+        <v>1</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E392" s="1">
+        <v>0</v>
+      </c>
+      <c r="F392" s="1">
+        <f>VLOOKUP(D392,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5016</v>
+      </c>
+      <c r="G392" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H392" s="1">
+        <v>1</v>
+      </c>
+      <c r="I392" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A393" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B393" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C393" s="1">
+        <v>1</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E393" s="1">
+        <v>0</v>
+      </c>
+      <c r="F393" s="1">
+        <f>VLOOKUP(D393,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5017</v>
+      </c>
+      <c r="G393" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H393" s="1">
+        <v>1</v>
+      </c>
+      <c r="I393" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A394" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B394" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C394" s="1">
+        <v>1</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E394" s="1">
+        <v>0</v>
+      </c>
+      <c r="F394" s="1">
+        <f>VLOOKUP(D394,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5020</v>
+      </c>
+      <c r="G394" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H394" s="1">
+        <v>1</v>
+      </c>
+      <c r="I394" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A395" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B395" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C395" s="1">
+        <v>1</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E395" s="1">
+        <v>0</v>
+      </c>
+      <c r="F395" s="1">
+        <f>VLOOKUP(D395,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5022</v>
+      </c>
+      <c r="G395" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H395" s="1">
+        <v>1</v>
+      </c>
+      <c r="I395" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A396" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B396" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C396" s="1">
+        <v>1</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E396" s="1">
+        <v>0</v>
+      </c>
+      <c r="F396" s="1">
+        <f>VLOOKUP(D396,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5019</v>
+      </c>
+      <c r="G396" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H396" s="1">
+        <v>1</v>
+      </c>
+      <c r="I396" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A397" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B397" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C397" s="1">
+        <v>1</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E397" s="1">
+        <v>0</v>
+      </c>
+      <c r="F397" s="1">
+        <f>VLOOKUP(D397,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5015</v>
+      </c>
+      <c r="G397" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H397" s="1">
+        <v>1</v>
+      </c>
+      <c r="I397" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A398" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B398" s="1">
+        <v>50000</v>
+      </c>
+      <c r="C398" s="1">
+        <v>1</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E398" s="1">
+        <v>0</v>
+      </c>
+      <c r="F398" s="1">
+        <f>VLOOKUP(D398,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5024</v>
+      </c>
+      <c r="G398" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H398" s="1">
+        <v>1</v>
+      </c>
+      <c r="I398" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A399" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B399" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C399" s="1">
+        <v>1</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E399" s="1">
+        <v>0</v>
+      </c>
+      <c r="F399" s="1">
+        <f>VLOOKUP(D399,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5006</v>
+      </c>
+      <c r="G399" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H399" s="1">
+        <v>1</v>
+      </c>
+      <c r="I399" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A400" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B400" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C400" s="1">
+        <v>1</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E400" s="1">
+        <v>0</v>
+      </c>
+      <c r="F400" s="1">
+        <f>VLOOKUP(D400,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5016</v>
+      </c>
+      <c r="G400" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H400" s="1">
+        <v>1</v>
+      </c>
+      <c r="I400" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A401" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B401" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C401" s="1">
+        <v>1</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E401" s="1">
+        <v>0</v>
+      </c>
+      <c r="F401" s="1">
+        <f>VLOOKUP(D401,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5017</v>
+      </c>
+      <c r="G401" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H401" s="1">
+        <v>1</v>
+      </c>
+      <c r="I401" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A402" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B402" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C402" s="1">
+        <v>1</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E402" s="1">
+        <v>0</v>
+      </c>
+      <c r="F402" s="1">
+        <f>VLOOKUP(D402,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5020</v>
+      </c>
+      <c r="G402" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H402" s="1">
+        <v>1</v>
+      </c>
+      <c r="I402" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A403" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B403" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C403" s="1">
+        <v>1</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E403" s="1">
+        <v>0</v>
+      </c>
+      <c r="F403" s="1">
+        <f>VLOOKUP(D403,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5022</v>
+      </c>
+      <c r="G403" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H403" s="1">
+        <v>1</v>
+      </c>
+      <c r="I403" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A404" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B404" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C404" s="1">
+        <v>1</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E404" s="1">
+        <v>0</v>
+      </c>
+      <c r="F404" s="1">
+        <f>VLOOKUP(D404,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5015</v>
+      </c>
+      <c r="G404" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H404" s="1">
+        <v>1</v>
+      </c>
+      <c r="I404" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A405" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B405" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C405" s="1">
+        <v>1</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E405" s="1">
+        <v>0</v>
+      </c>
+      <c r="F405" s="1">
+        <f>VLOOKUP(D405,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5024</v>
+      </c>
+      <c r="G405" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H405" s="1">
+        <v>1</v>
+      </c>
+      <c r="I405" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A406" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B406" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C406" s="1">
+        <v>1</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E406" s="1">
+        <v>0</v>
+      </c>
+      <c r="F406" s="1">
+        <f>VLOOKUP(D406,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5008</v>
+      </c>
+      <c r="G406" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H406" s="1">
+        <v>1</v>
+      </c>
+      <c r="I406" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A407" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B407" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C407" s="1">
+        <v>1</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E407" s="1">
+        <v>0</v>
+      </c>
+      <c r="F407" s="1">
+        <f>VLOOKUP(D407,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5009</v>
+      </c>
+      <c r="G407" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H407" s="1">
+        <v>1</v>
+      </c>
+      <c r="I407" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A408" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B408" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C408" s="1">
+        <v>1</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E408" s="1">
+        <v>0</v>
+      </c>
+      <c r="F408" s="1">
+        <f>VLOOKUP(D408,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5025</v>
+      </c>
+      <c r="G408" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H408" s="1">
+        <v>1</v>
+      </c>
+      <c r="I408" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A409" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B409" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C409" s="1">
+        <v>1</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E409" s="1">
+        <v>0</v>
+      </c>
+      <c r="F409" s="1">
+        <f>VLOOKUP(D409,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5026</v>
+      </c>
+      <c r="G409" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H409" s="1">
+        <v>1</v>
+      </c>
+      <c r="I409" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A410" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B410" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C410" s="1">
+        <v>1</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E410" s="1">
+        <v>0</v>
+      </c>
+      <c r="F410" s="1">
+        <f>VLOOKUP(D410,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5031</v>
+      </c>
+      <c r="G410" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H410" s="1">
+        <v>1</v>
+      </c>
+      <c r="I410" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A411" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B411" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C411" s="1">
+        <v>1</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E411" s="1">
+        <v>0</v>
+      </c>
+      <c r="F411" s="1">
+        <f>VLOOKUP(D411,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5032</v>
+      </c>
+      <c r="G411" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H411" s="1">
+        <v>1</v>
+      </c>
+      <c r="I411" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A412" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B412" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C412" s="1">
+        <v>1</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E412" s="1">
+        <v>0</v>
+      </c>
+      <c r="F412" s="1">
+        <f>VLOOKUP(D412,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5006</v>
+      </c>
+      <c r="G412" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H412" s="1">
+        <v>1</v>
+      </c>
+      <c r="I412" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A413" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B413" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C413" s="1">
+        <v>1</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E413" s="1">
+        <v>0</v>
+      </c>
+      <c r="F413" s="1">
+        <f>VLOOKUP(D413,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5004</v>
+      </c>
+      <c r="G413" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H413" s="1">
+        <v>1</v>
+      </c>
+      <c r="I413" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A414" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B414" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C414" s="1">
+        <v>1</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E414" s="1">
+        <v>0</v>
+      </c>
+      <c r="F414" s="1">
+        <f>VLOOKUP(D414,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5005</v>
+      </c>
+      <c r="G414" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H414" s="1">
+        <v>1</v>
+      </c>
+      <c r="I414" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A415" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B415" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C415" s="1">
+        <v>1</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E415" s="1">
+        <v>0</v>
+      </c>
+      <c r="F415" s="1">
+        <f>VLOOKUP(D415,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5012</v>
+      </c>
+      <c r="G415" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H415" s="1">
+        <v>1</v>
+      </c>
+      <c r="I415" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A416" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B416" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C416" s="1">
+        <v>1</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E416" s="1">
+        <v>0</v>
+      </c>
+      <c r="F416" s="1">
+        <f>VLOOKUP(D416,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5015</v>
+      </c>
+      <c r="G416" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H416" s="1">
+        <v>1</v>
+      </c>
+      <c r="I416" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A417" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B417" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C417" s="1">
+        <v>1</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E417" s="1">
+        <v>0</v>
+      </c>
+      <c r="F417" s="1">
+        <f>VLOOKUP(D417,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5024</v>
+      </c>
+      <c r="G417" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H417" s="1">
+        <v>1</v>
+      </c>
+      <c r="I417" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A418" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B418" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C418" s="1">
+        <v>1</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E418" s="1">
+        <v>0</v>
+      </c>
+      <c r="F418" s="1">
+        <f>VLOOKUP(D418,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5008</v>
+      </c>
+      <c r="G418" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H418" s="1">
+        <v>1</v>
+      </c>
+      <c r="I418" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A419" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B419" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C419" s="1">
+        <v>1</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E419" s="1">
+        <v>0</v>
+      </c>
+      <c r="F419" s="1">
+        <f>VLOOKUP(D419,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5009</v>
+      </c>
+      <c r="G419" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H419" s="1">
+        <v>1</v>
+      </c>
+      <c r="I419" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A420" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B420" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C420" s="1">
+        <v>1</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E420" s="1">
+        <v>0</v>
+      </c>
+      <c r="F420" s="1">
+        <f>VLOOKUP(D420,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5025</v>
+      </c>
+      <c r="G420" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H420" s="1">
+        <v>1</v>
+      </c>
+      <c r="I420" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A421" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B421" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C421" s="1">
+        <v>1</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E421" s="1">
+        <v>0</v>
+      </c>
+      <c r="F421" s="1">
+        <f>VLOOKUP(D421,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5026</v>
+      </c>
+      <c r="G421" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H421" s="1">
+        <v>1</v>
+      </c>
+      <c r="I421" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A422" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B422" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C422" s="1">
+        <v>1</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E422" s="1">
+        <v>0</v>
+      </c>
+      <c r="F422" s="1">
+        <f>VLOOKUP(D422,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5031</v>
+      </c>
+      <c r="G422" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H422" s="1">
+        <v>1</v>
+      </c>
+      <c r="I422" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A423" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B423" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C423" s="1">
+        <v>1</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E423" s="1">
+        <v>0</v>
+      </c>
+      <c r="F423" s="1">
+        <f>VLOOKUP(D423,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5032</v>
+      </c>
+      <c r="G423" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H423" s="1">
+        <v>1</v>
+      </c>
+      <c r="I423" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A424" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B424" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C424" s="1">
+        <v>1</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E424" s="1">
+        <v>0</v>
+      </c>
+      <c r="F424" s="1">
+        <f>VLOOKUP(D424,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5019</v>
+      </c>
+      <c r="G424" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H424" s="1">
+        <v>1</v>
+      </c>
+      <c r="I424" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A425" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B425" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C425" s="1">
+        <v>1</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E425" s="1">
+        <v>0</v>
+      </c>
+      <c r="F425" s="1">
+        <f>VLOOKUP(D425,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5006</v>
+      </c>
+      <c r="G425" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H425" s="1">
+        <v>1</v>
+      </c>
+      <c r="I425" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A426" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B426" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C426" s="1">
+        <v>1</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E426" s="1">
+        <v>0</v>
+      </c>
+      <c r="F426" s="1">
+        <f>VLOOKUP(D426,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5001</v>
+      </c>
+      <c r="G426" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H426" s="1">
+        <v>1</v>
+      </c>
+      <c r="I426" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A427" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B427" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C427" s="1">
+        <v>1</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E427" s="1">
+        <v>0</v>
+      </c>
+      <c r="F427" s="1">
+        <f>VLOOKUP(D427,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5014</v>
+      </c>
+      <c r="G427" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H427" s="1">
+        <v>1</v>
+      </c>
+      <c r="I427" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A428" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B428" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C428" s="1">
+        <v>1</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E428" s="1">
+        <v>0</v>
+      </c>
+      <c r="F428" s="1">
+        <f>VLOOKUP(D428,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G428" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H428" s="1">
+        <v>1</v>
+      </c>
+      <c r="I428" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A429" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B429" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C429" s="1">
+        <v>1</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E429" s="1">
+        <v>0</v>
+      </c>
+      <c r="F429" s="1">
+        <f>VLOOKUP(D429,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G429" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H429" s="1">
+        <v>1</v>
+      </c>
+      <c r="I429" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A430" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B430" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C430" s="1">
+        <v>1</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E430" s="1">
+        <v>0</v>
+      </c>
+      <c r="F430" s="1">
+        <f>VLOOKUP(D430,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G430" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H430" s="1">
+        <v>1</v>
+      </c>
+      <c r="I430" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A431" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B431" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C431" s="1">
+        <v>1</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E431" s="1">
+        <v>0</v>
+      </c>
+      <c r="F431" s="1">
+        <f>VLOOKUP(D431,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G431" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H431" s="1">
+        <v>1</v>
+      </c>
+      <c r="I431" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A432" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B432" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C432" s="1">
+        <v>1</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E432" s="1">
+        <v>0</v>
+      </c>
+      <c r="F432" s="1">
+        <f>VLOOKUP(D432,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G432" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H432" s="1">
+        <v>1</v>
+      </c>
+      <c r="I432" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A433" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B433" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C433" s="1">
+        <v>1</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E433" s="1">
+        <v>0</v>
+      </c>
+      <c r="F433" s="1">
+        <f>VLOOKUP(D433,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G433" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H433" s="1">
+        <v>1</v>
+      </c>
+      <c r="I433" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A434" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B434" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C434" s="1">
+        <v>1</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E434" s="1">
+        <v>0</v>
+      </c>
+      <c r="F434" s="1">
+        <f>VLOOKUP(D434,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5007</v>
+      </c>
+      <c r="G434" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H434" s="1">
+        <v>1</v>
+      </c>
+      <c r="I434" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A435" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B435" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C435" s="1">
+        <v>1</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E435" s="1">
+        <v>0</v>
+      </c>
+      <c r="F435" s="1">
+        <f>VLOOKUP(D435,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5017</v>
+      </c>
+      <c r="G435" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H435" s="1">
+        <v>1</v>
+      </c>
+      <c r="I435" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A436" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B436" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C436" s="1">
+        <v>1</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E436" s="1">
+        <v>0</v>
+      </c>
+      <c r="F436" s="1">
+        <f>VLOOKUP(D436,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5019</v>
+      </c>
+      <c r="G436" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H436" s="1">
+        <v>1</v>
+      </c>
+      <c r="I436" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A437" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B437" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C437" s="1">
+        <v>1</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E437" s="1">
+        <v>0</v>
+      </c>
+      <c r="F437" s="1">
+        <f>VLOOKUP(D437,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5001</v>
+      </c>
+      <c r="G437" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H437" s="1">
+        <v>1</v>
+      </c>
+      <c r="I437" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A438" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B438" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C438" s="1">
+        <v>1</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E438" s="1">
+        <v>0</v>
+      </c>
+      <c r="F438" s="1">
+        <f>VLOOKUP(D438,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5014</v>
+      </c>
+      <c r="G438" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H438" s="1">
+        <v>1</v>
+      </c>
+      <c r="I438" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A439" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B439" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C439" s="1">
+        <v>1</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E439" s="1">
+        <v>0</v>
+      </c>
+      <c r="F439" s="1">
+        <f>VLOOKUP(D439,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G439" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H439" s="1">
+        <v>1</v>
+      </c>
+      <c r="I439" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A440" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B440" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C440" s="1">
+        <v>1</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E440" s="1">
+        <v>0</v>
+      </c>
+      <c r="F440" s="1">
+        <f>VLOOKUP(D440,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G440" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H440" s="1">
+        <v>1</v>
+      </c>
+      <c r="I440" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A441" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B441" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C441" s="1">
+        <v>1</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E441" s="1">
+        <v>0</v>
+      </c>
+      <c r="F441" s="1">
+        <f>VLOOKUP(D441,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G441" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H441" s="1">
+        <v>1</v>
+      </c>
+      <c r="I441" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A442" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B442" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C442" s="1">
+        <v>1</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E442" s="1">
+        <v>0</v>
+      </c>
+      <c r="F442" s="1">
+        <f>VLOOKUP(D442,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G442" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H442" s="1">
+        <v>1</v>
+      </c>
+      <c r="I442" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A443" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B443" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C443" s="1">
+        <v>1</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E443" s="1">
+        <v>0</v>
+      </c>
+      <c r="F443" s="1">
+        <f>VLOOKUP(D443,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G443" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H443" s="1">
+        <v>1</v>
+      </c>
+      <c r="I443" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A444" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B444" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C444" s="1">
+        <v>1</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E444" s="1">
+        <v>0</v>
+      </c>
+      <c r="F444" s="1">
+        <f>VLOOKUP(D444,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G444" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H444" s="1">
+        <v>1</v>
+      </c>
+      <c r="I444" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A445" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B445" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C445" s="1">
+        <v>1</v>
+      </c>
+      <c r="D445" t="s">
+        <v>556</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
+      </c>
+      <c r="F445" s="1">
+        <f>VLOOKUP(D445,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G445" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H445" s="1">
+        <v>1</v>
+      </c>
+      <c r="I445" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A446" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B446" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C446" s="1">
+        <v>1</v>
+      </c>
+      <c r="D446" t="s">
+        <v>557</v>
+      </c>
+      <c r="E446" s="1">
+        <v>0</v>
+      </c>
+      <c r="F446" s="1">
+        <f>VLOOKUP(D446,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G446" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H446" s="1">
+        <v>1</v>
+      </c>
+      <c r="I446" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A447" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B447" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C447" s="1">
+        <v>1</v>
+      </c>
+      <c r="D447" t="s">
+        <v>558</v>
+      </c>
+      <c r="E447" s="1">
+        <v>0</v>
+      </c>
+      <c r="F447" s="1">
+        <f>VLOOKUP(D447,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G447" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H447" s="1">
+        <v>1</v>
+      </c>
+      <c r="I447" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A448" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B448" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C448" s="1">
+        <v>1</v>
+      </c>
+      <c r="D448" t="s">
+        <v>559</v>
+      </c>
+      <c r="E448" s="1">
+        <v>0</v>
+      </c>
+      <c r="F448" s="1">
+        <f>VLOOKUP(D448,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G448" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H448" s="1">
+        <v>1</v>
+      </c>
+      <c r="I448" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A449" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B449" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C449" s="1">
+        <v>1</v>
+      </c>
+      <c r="D449" t="s">
+        <v>560</v>
+      </c>
+      <c r="E449" s="1">
+        <v>0</v>
+      </c>
+      <c r="F449" s="1">
+        <f>VLOOKUP(D449,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G449" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H449" s="1">
+        <v>1</v>
+      </c>
+      <c r="I449" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A450" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B450" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C450" s="1">
+        <v>1</v>
+      </c>
+      <c r="D450" t="s">
+        <v>561</v>
+      </c>
+      <c r="E450" s="1">
+        <v>0</v>
+      </c>
+      <c r="F450" s="1">
+        <f>VLOOKUP(D450,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G450" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H450" s="1">
+        <v>1</v>
+      </c>
+      <c r="I450" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:I3">
-    <sortState ref="A4:J359">
+    <sortState ref="A4:I389">
       <sortCondition ref="B3"/>
     </sortState>
   </autoFilter>
@@ -16459,7 +18463,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B7:I223"/>
+  <dimension ref="B7:I290"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="9" customWidth="1"/>
@@ -20824,6 +22828,342 @@
       <c r="I223" t="e">
         <f>VLOOKUP(C223,[1]MonsterData!$I$2:$L$84,4,FALSE)</f>
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="249" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G249" t="s">
+        <v>554</v>
+      </c>
+      <c r="H249">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="250" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G250" t="s">
+        <v>556</v>
+      </c>
+      <c r="H250">
+        <v>5002</v>
+      </c>
+    </row>
+    <row r="251" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G251" t="s">
+        <v>557</v>
+      </c>
+      <c r="H251">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="252" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G252" t="s">
+        <v>550</v>
+      </c>
+      <c r="H252">
+        <v>5004</v>
+      </c>
+    </row>
+    <row r="253" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G253" t="s">
+        <v>568</v>
+      </c>
+      <c r="H253">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="254" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G254" t="s">
+        <v>531</v>
+      </c>
+      <c r="H254">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="255" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G255" t="s">
+        <v>532</v>
+      </c>
+      <c r="H255">
+        <v>5007</v>
+      </c>
+    </row>
+    <row r="256" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G256" t="s">
+        <v>542</v>
+      </c>
+      <c r="H256">
+        <v>5008</v>
+      </c>
+    </row>
+    <row r="257" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G257" t="s">
+        <v>543</v>
+      </c>
+      <c r="H257">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="258" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G258" t="s">
+        <v>569</v>
+      </c>
+      <c r="H258">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="259" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G259" t="s">
+        <v>570</v>
+      </c>
+      <c r="H259">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="260" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G260" t="s">
+        <v>552</v>
+      </c>
+      <c r="H260">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="261" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G261" t="s">
+        <v>571</v>
+      </c>
+      <c r="H261">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="262" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G262" t="s">
+        <v>555</v>
+      </c>
+      <c r="H262">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="263" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G263" t="s">
+        <v>538</v>
+      </c>
+      <c r="H263">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="264" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G264" t="s">
+        <v>533</v>
+      </c>
+      <c r="H264">
+        <v>5016</v>
+      </c>
+    </row>
+    <row r="265" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G265" t="s">
+        <v>534</v>
+      </c>
+      <c r="H265">
+        <v>5017</v>
+      </c>
+    </row>
+    <row r="266" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G266" t="s">
+        <v>558</v>
+      </c>
+      <c r="H266">
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="267" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G267" t="s">
+        <v>537</v>
+      </c>
+      <c r="H267">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="268" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G268" t="s">
+        <v>535</v>
+      </c>
+      <c r="H268">
+        <v>5020</v>
+      </c>
+    </row>
+    <row r="269" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G269" t="s">
+        <v>572</v>
+      </c>
+      <c r="H269">
+        <v>5021</v>
+      </c>
+    </row>
+    <row r="270" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G270" t="s">
+        <v>536</v>
+      </c>
+      <c r="H270">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="271" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G271" t="s">
+        <v>573</v>
+      </c>
+      <c r="H271">
+        <v>5023</v>
+      </c>
+    </row>
+    <row r="272" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G272" t="s">
+        <v>539</v>
+      </c>
+      <c r="H272">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="273" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G273" t="s">
+        <v>544</v>
+      </c>
+      <c r="H273">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="274" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G274" t="s">
+        <v>545</v>
+      </c>
+      <c r="H274">
+        <v>5026</v>
+      </c>
+    </row>
+    <row r="275" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G275" t="s">
+        <v>559</v>
+      </c>
+      <c r="H275">
+        <v>5027</v>
+      </c>
+    </row>
+    <row r="276" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G276" t="s">
+        <v>560</v>
+      </c>
+      <c r="H276">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="277" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G277" t="s">
+        <v>561</v>
+      </c>
+      <c r="H277">
+        <v>5029</v>
+      </c>
+    </row>
+    <row r="278" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G278" t="s">
+        <v>574</v>
+      </c>
+      <c r="H278">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="279" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G279" t="s">
+        <v>546</v>
+      </c>
+      <c r="H279">
+        <v>5031</v>
+      </c>
+    </row>
+    <row r="280" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G280" t="s">
+        <v>547</v>
+      </c>
+      <c r="H280">
+        <v>5032</v>
+      </c>
+    </row>
+    <row r="281" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G281" t="s">
+        <v>575</v>
+      </c>
+      <c r="H281">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="282" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G282" t="s">
+        <v>576</v>
+      </c>
+      <c r="H282">
+        <v>5201</v>
+      </c>
+    </row>
+    <row r="283" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G283" t="s">
+        <v>577</v>
+      </c>
+      <c r="H283">
+        <v>5202</v>
+      </c>
+    </row>
+    <row r="284" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G284" t="s">
+        <v>578</v>
+      </c>
+      <c r="H284">
+        <v>5203</v>
+      </c>
+    </row>
+    <row r="285" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G285" t="s">
+        <v>579</v>
+      </c>
+      <c r="H285">
+        <v>5204</v>
+      </c>
+    </row>
+    <row r="286" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G286" t="s">
+        <v>580</v>
+      </c>
+      <c r="H286">
+        <v>5205</v>
+      </c>
+    </row>
+    <row r="287" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G287" t="s">
+        <v>581</v>
+      </c>
+      <c r="H287">
+        <v>5206</v>
+      </c>
+    </row>
+    <row r="288" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G288" t="s">
+        <v>582</v>
+      </c>
+      <c r="H288">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="289" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G289" t="s">
+        <v>583</v>
+      </c>
+      <c r="H289">
+        <v>5208</v>
+      </c>
+    </row>
+    <row r="290" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G290" t="s">
+        <v>584</v>
+      </c>
+      <c r="H290">
+        <v>5209</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="595">
   <si>
     <t>text</t>
   </si>
@@ -1636,10 +1636,6 @@
     <t>黑线</t>
   </si>
   <si>
-    <t>临时npc默认表情</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>住宅区家桥表情</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1684,10 +1680,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>彩带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>亮灯</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1700,10 +1692,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>晕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>汗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1908,6 +1896,50 @@
   </si>
   <si>
     <t>幽灵战士</t>
+  </si>
+  <si>
+    <t>购买失败表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心破碎</t>
+  </si>
+  <si>
+    <t>购买失败表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开裂</t>
+  </si>
+  <si>
+    <t>购买成功表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大星星</t>
+  </si>
+  <si>
+    <t>爱心</t>
+  </si>
+  <si>
+    <t>流口水</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>彩虹</t>
+  </si>
+  <si>
+    <t>苹果</t>
   </si>
 </sst>
 </file>
@@ -3484,7 +3516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I450"/>
+  <dimension ref="A1:I459"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -12326,19 +12358,19 @@
         <v>506</v>
       </c>
       <c r="B306" s="1">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="C306" s="1">
         <v>1</v>
       </c>
-      <c r="D306" s="1" t="s">
-        <v>505</v>
+      <c r="D306" t="s">
+        <v>511</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
       </c>
-      <c r="F306" s="1">
-        <v>24</v>
+      <c r="F306">
+        <v>61</v>
       </c>
       <c r="G306" s="1">
         <v>1000</v>
@@ -12352,7 +12384,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B307" s="1">
         <v>20002</v>
@@ -12361,13 +12393,13 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>512</v>
+        <v>593</v>
       </c>
       <c r="E307" s="1">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G307" s="1">
         <v>1000</v>
@@ -12381,7 +12413,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B308" s="1">
         <v>20002</v>
@@ -12390,13 +12422,13 @@
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E308" s="1">
         <v>0</v>
       </c>
       <c r="F308">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G308" s="1">
         <v>1000</v>
@@ -12410,7 +12442,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B309" s="1">
         <v>20002</v>
@@ -12419,13 +12451,13 @@
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="E309" s="1">
         <v>0</v>
       </c>
       <c r="F309">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G309" s="1">
         <v>1000</v>
@@ -12439,7 +12471,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B310" s="1">
         <v>20002</v>
@@ -12447,14 +12479,14 @@
       <c r="C310" s="1">
         <v>1</v>
       </c>
-      <c r="D310" t="s">
-        <v>503</v>
+      <c r="D310" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
       </c>
-      <c r="F310">
-        <v>18</v>
+      <c r="F310" s="1">
+        <v>1</v>
       </c>
       <c r="G310" s="1">
         <v>1000</v>
@@ -12471,19 +12503,19 @@
         <v>507</v>
       </c>
       <c r="B311" s="1">
-        <v>20002</v>
+        <v>20003</v>
       </c>
       <c r="C311" s="1">
         <v>1</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>504</v>
+      <c r="D311" t="s">
+        <v>592</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
       </c>
-      <c r="F311" s="1">
-        <v>1</v>
+      <c r="F311">
+        <v>14</v>
       </c>
       <c r="G311" s="1">
         <v>1000</v>
@@ -12497,7 +12529,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B312" s="1">
         <v>20003</v>
@@ -12506,13 +12538,13 @@
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E312" s="1">
         <v>0</v>
       </c>
       <c r="F312">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G312" s="1">
         <v>1000</v>
@@ -12526,7 +12558,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B313" s="1">
         <v>20003</v>
@@ -12535,13 +12567,13 @@
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E313" s="1">
         <v>0</v>
       </c>
       <c r="F313">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G313" s="1">
         <v>1000</v>
@@ -12555,7 +12587,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B314" s="1">
         <v>20003</v>
@@ -12564,13 +12596,13 @@
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
       </c>
       <c r="F314">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G314" s="1">
         <v>1000</v>
@@ -12584,7 +12616,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B315" s="1">
         <v>20003</v>
@@ -12593,13 +12625,13 @@
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
       </c>
       <c r="F315">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G315" s="1">
         <v>1000</v>
@@ -12616,19 +12648,19 @@
         <v>508</v>
       </c>
       <c r="B316" s="1">
-        <v>20003</v>
+        <v>20004</v>
       </c>
       <c r="C316" s="1">
         <v>1</v>
       </c>
       <c r="D316" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
       </c>
       <c r="F316">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G316" s="1">
         <v>1000</v>
@@ -12642,7 +12674,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B317" s="1">
         <v>20004</v>
@@ -12651,13 +12683,13 @@
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E317" s="1">
         <v>0</v>
       </c>
       <c r="F317">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G317" s="1">
         <v>1000</v>
@@ -12671,7 +12703,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B318" s="1">
         <v>20004</v>
@@ -12680,13 +12712,13 @@
         <v>1</v>
       </c>
       <c r="D318" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E318" s="1">
         <v>0</v>
       </c>
       <c r="F318">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G318" s="1">
         <v>1000</v>
@@ -12700,7 +12732,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B319" s="1">
         <v>20004</v>
@@ -12709,13 +12741,13 @@
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E319" s="1">
         <v>0</v>
       </c>
       <c r="F319">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="G319" s="1">
         <v>1000</v>
@@ -12729,7 +12761,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B320" s="1">
         <v>20004</v>
@@ -12738,13 +12770,13 @@
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="E320" s="1">
         <v>0</v>
       </c>
       <c r="F320">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G320" s="1">
         <v>1000</v>
@@ -12761,19 +12793,19 @@
         <v>509</v>
       </c>
       <c r="B321" s="1">
-        <v>20004</v>
+        <v>20005</v>
       </c>
       <c r="C321" s="1">
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E321" s="1">
         <v>0</v>
       </c>
       <c r="F321">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="G321" s="1">
         <v>1000</v>
@@ -12787,7 +12819,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B322" s="1">
         <v>20005</v>
@@ -12796,13 +12828,13 @@
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>517</v>
+        <v>594</v>
       </c>
       <c r="E322" s="1">
         <v>0</v>
       </c>
       <c r="F322">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="G322" s="1">
         <v>1000</v>
@@ -12816,7 +12848,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B323" s="1">
         <v>20005</v>
@@ -12825,13 +12857,13 @@
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E323" s="1">
         <v>0</v>
       </c>
       <c r="F323">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G323" s="1">
         <v>1000</v>
@@ -12845,7 +12877,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B324" s="1">
         <v>20005</v>
@@ -12854,13 +12886,13 @@
         <v>1</v>
       </c>
       <c r="D324" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
       </c>
       <c r="F324">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G324" s="1">
         <v>1000</v>
@@ -12877,19 +12909,19 @@
         <v>510</v>
       </c>
       <c r="B325" s="1">
-        <v>20005</v>
+        <v>20006</v>
       </c>
       <c r="C325" s="1">
         <v>1</v>
       </c>
       <c r="D325" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
       </c>
       <c r="F325">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G325" s="1">
         <v>1000</v>
@@ -12903,7 +12935,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B326" s="1">
         <v>20006</v>
@@ -12912,13 +12944,13 @@
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
       </c>
       <c r="F326">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G326" s="1">
         <v>1000</v>
@@ -12932,7 +12964,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B327" s="1">
         <v>20006</v>
@@ -12941,13 +12973,13 @@
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E327" s="1">
         <v>0</v>
       </c>
       <c r="F327">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G327" s="1">
         <v>1000</v>
@@ -12961,7 +12993,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B328" s="1">
         <v>20006</v>
@@ -12970,13 +13002,13 @@
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E328" s="1">
         <v>0</v>
       </c>
       <c r="F328">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G328" s="1">
         <v>1000</v>
@@ -12990,7 +13022,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B329" s="1">
         <v>20006</v>
@@ -12999,13 +13031,13 @@
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E329" s="1">
         <v>0</v>
       </c>
       <c r="F329">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G329" s="1">
         <v>1000</v>
@@ -13019,25 +13051,22 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>511</v>
+        <v>15</v>
       </c>
       <c r="B330" s="1">
-        <v>20006</v>
+        <v>30000</v>
       </c>
       <c r="C330" s="1">
         <v>1</v>
       </c>
-      <c r="D330" t="s">
-        <v>530</v>
-      </c>
       <c r="E330" s="1">
         <v>0</v>
       </c>
-      <c r="F330">
-        <v>49</v>
+      <c r="F330" s="2">
+        <v>6000</v>
       </c>
       <c r="G330" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H330" s="1">
         <v>1</v>
@@ -13060,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="F331" s="2">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="G331" s="1">
         <v>5000</v>
@@ -13086,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="F332" s="2">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="G332" s="1">
         <v>5000</v>
@@ -13112,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="F333" s="2">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="G333" s="1">
         <v>5000</v>
@@ -13126,10 +13155,10 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B334" s="1">
-        <v>30000</v>
+        <v>30001</v>
       </c>
       <c r="C334" s="1">
         <v>1</v>
@@ -13138,7 +13167,7 @@
         <v>0</v>
       </c>
       <c r="F334" s="2">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="G334" s="1">
         <v>5000</v>
@@ -13164,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="F335" s="2">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="G335" s="1">
         <v>5000</v>
@@ -13178,7 +13207,7 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B336" s="1">
         <v>30001</v>
@@ -13190,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="F336" s="2">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="G336" s="1">
         <v>5000</v>
@@ -13204,10 +13233,10 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B337" s="1">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C337" s="1">
         <v>1</v>
@@ -13215,8 +13244,8 @@
       <c r="E337" s="1">
         <v>0</v>
       </c>
-      <c r="F337" s="2">
-        <v>6006</v>
+      <c r="F337" s="1">
+        <v>30</v>
       </c>
       <c r="G337" s="1">
         <v>5000</v>
@@ -13242,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="F338" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G338" s="1">
         <v>5000</v>
@@ -13268,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="F339" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G339" s="1">
         <v>5000</v>
@@ -13294,7 +13323,7 @@
         <v>0</v>
       </c>
       <c r="F340" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G340" s="1">
         <v>5000</v>
@@ -13308,10 +13337,10 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B341" s="1">
-        <v>30002</v>
+        <v>30003</v>
       </c>
       <c r="C341" s="1">
         <v>1</v>
@@ -13320,7 +13349,7 @@
         <v>0</v>
       </c>
       <c r="F341" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G341" s="1">
         <v>5000</v>
@@ -13346,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="F342" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G342" s="1">
         <v>5000</v>
@@ -13372,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="F343" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G343" s="1">
         <v>5000</v>
@@ -13386,7 +13415,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B344" s="1">
         <v>30003</v>
@@ -13398,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="F344" s="1">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G344" s="1">
         <v>5000</v>
@@ -13412,10 +13441,10 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B345" s="1">
-        <v>30003</v>
+        <v>30004</v>
       </c>
       <c r="C345" s="1">
         <v>1</v>
@@ -13424,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="F345" s="1">
-        <v>19</v>
+        <v>6007</v>
       </c>
       <c r="G345" s="1">
         <v>5000</v>
@@ -13438,10 +13467,10 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B346" s="1">
-        <v>30004</v>
+        <v>30005</v>
       </c>
       <c r="C346" s="1">
         <v>1</v>
@@ -13450,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="F346" s="1">
-        <v>6007</v>
+        <v>4</v>
       </c>
       <c r="G346" s="1">
         <v>5000</v>
@@ -13464,7 +13493,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B347" s="1">
         <v>30005</v>
@@ -13476,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="F347" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G347" s="1">
         <v>5000</v>
@@ -13490,7 +13519,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B348" s="1">
         <v>30005</v>
@@ -13502,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="F348" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G348" s="1">
         <v>5000</v>
@@ -13516,19 +13545,22 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>22</v>
+        <v>585</v>
       </c>
       <c r="B349" s="1">
-        <v>30005</v>
+        <v>30006</v>
       </c>
       <c r="C349" s="1">
         <v>1</v>
       </c>
+      <c r="D349" t="s">
+        <v>583</v>
+      </c>
       <c r="E349" s="1">
         <v>0</v>
       </c>
       <c r="F349" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G349" s="1">
         <v>5000</v>
@@ -13541,273 +13573,264 @@
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A350" s="6" t="s">
+      <c r="A350" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B350" s="1">
+        <v>30006</v>
+      </c>
+      <c r="C350" s="1">
+        <v>1</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="E350" s="1">
+        <v>0</v>
+      </c>
+      <c r="F350" s="1">
+        <v>9</v>
+      </c>
+      <c r="G350" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H350" s="1">
+        <v>1</v>
+      </c>
+      <c r="I350" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A351" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B351" s="1">
+        <v>30006</v>
+      </c>
+      <c r="C351" s="1">
+        <v>1</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E351" s="1">
+        <v>0</v>
+      </c>
+      <c r="F351" s="1">
         <v>24</v>
       </c>
-      <c r="B350" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C350" s="6">
-        <v>1</v>
-      </c>
-      <c r="D350" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E350" s="6">
-        <v>0</v>
-      </c>
-      <c r="F350" s="7">
-        <f>VLOOKUP(D350,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1100</v>
-      </c>
-      <c r="G350" s="6">
-        <v>10000</v>
-      </c>
-      <c r="H350" s="6">
-        <v>10</v>
-      </c>
-      <c r="I350" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A351" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B351" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C351" s="6">
-        <v>1</v>
-      </c>
-      <c r="D351" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E351" s="6">
-        <v>0</v>
-      </c>
-      <c r="F351" s="7">
-        <f>VLOOKUP(D351,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1101</v>
-      </c>
-      <c r="G351" s="6">
-        <v>9400</v>
-      </c>
-      <c r="H351" s="6">
-        <v>10</v>
-      </c>
-      <c r="I351" s="6">
-        <v>30</v>
+      <c r="G351" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H351" s="1">
+        <v>1</v>
+      </c>
+      <c r="I351" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A352" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B352" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C352" s="6">
-        <v>1</v>
-      </c>
-      <c r="D352" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E352" s="6">
-        <v>0</v>
-      </c>
-      <c r="F352" s="7">
-        <f>VLOOKUP(D352,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1103</v>
-      </c>
-      <c r="G352" s="6">
-        <v>8800</v>
-      </c>
-      <c r="H352" s="6">
-        <v>10</v>
-      </c>
-      <c r="I352" s="6">
-        <v>30</v>
+      <c r="A352" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B352" s="1">
+        <v>30006</v>
+      </c>
+      <c r="C352" s="1">
+        <v>1</v>
+      </c>
+      <c r="D352" t="s">
+        <v>586</v>
+      </c>
+      <c r="E352" s="1">
+        <v>0</v>
+      </c>
+      <c r="F352" s="1">
+        <v>21</v>
+      </c>
+      <c r="G352" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H352" s="1">
+        <v>1</v>
+      </c>
+      <c r="I352" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A353" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B353" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C353" s="6">
-        <v>1</v>
-      </c>
-      <c r="D353" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E353" s="6">
-        <v>0</v>
-      </c>
-      <c r="F353" s="7">
-        <f>VLOOKUP(D353,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1105</v>
-      </c>
-      <c r="G353" s="6">
-        <v>8200</v>
-      </c>
-      <c r="H353" s="6">
-        <v>10</v>
-      </c>
-      <c r="I353" s="6">
-        <v>30</v>
+      <c r="A353" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B353" s="1">
+        <v>30006</v>
+      </c>
+      <c r="C353" s="1">
+        <v>1</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E353" s="1">
+        <v>0</v>
+      </c>
+      <c r="F353" s="1">
+        <v>40</v>
+      </c>
+      <c r="G353" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H353" s="1">
+        <v>1</v>
+      </c>
+      <c r="I353" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A354" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B354" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C354" s="6">
-        <v>1</v>
-      </c>
-      <c r="D354" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E354" s="6">
-        <v>0</v>
-      </c>
-      <c r="F354" s="7">
-        <f>VLOOKUP(D354,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1106</v>
-      </c>
-      <c r="G354" s="6">
-        <v>7600</v>
-      </c>
-      <c r="H354" s="6">
-        <v>10</v>
-      </c>
-      <c r="I354" s="6">
-        <v>30</v>
+      <c r="A354" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B354" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C354" s="1">
+        <v>1</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E354" s="1">
+        <v>0</v>
+      </c>
+      <c r="F354" s="1">
+        <v>6</v>
+      </c>
+      <c r="G354" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H354" s="1">
+        <v>1</v>
+      </c>
+      <c r="I354" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A355" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B355" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C355" s="6">
-        <v>1</v>
-      </c>
-      <c r="D355" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E355" s="6">
-        <v>0</v>
-      </c>
-      <c r="F355" s="7">
-        <f>VLOOKUP(D355,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1109</v>
-      </c>
-      <c r="G355" s="6">
-        <v>7000</v>
-      </c>
-      <c r="H355" s="6">
-        <v>10</v>
-      </c>
-      <c r="I355" s="6">
-        <v>30</v>
+      <c r="A355" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B355" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C355" s="1">
+        <v>1</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E355" s="1">
+        <v>0</v>
+      </c>
+      <c r="F355" s="1">
+        <v>8</v>
+      </c>
+      <c r="G355" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H355" s="1">
+        <v>1</v>
+      </c>
+      <c r="I355" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A356" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B356" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C356" s="6">
-        <v>1</v>
-      </c>
-      <c r="D356" s="6" t="s">
+      <c r="A356" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B356" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C356" s="1">
+        <v>1</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E356" s="1">
+        <v>0</v>
+      </c>
+      <c r="F356" s="1">
         <v>34</v>
       </c>
-      <c r="E356" s="6">
-        <v>0</v>
-      </c>
-      <c r="F356" s="7">
-        <f>VLOOKUP(D356,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1110</v>
-      </c>
-      <c r="G356" s="6">
-        <v>6400</v>
-      </c>
-      <c r="H356" s="6">
-        <v>10</v>
-      </c>
-      <c r="I356" s="6">
-        <v>30</v>
+      <c r="G356" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H356" s="1">
+        <v>1</v>
+      </c>
+      <c r="I356" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A357" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B357" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C357" s="6">
-        <v>1</v>
-      </c>
-      <c r="D357" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E357" s="6">
-        <v>0</v>
-      </c>
-      <c r="F357" s="7">
-        <f>VLOOKUP(D357,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1111</v>
-      </c>
-      <c r="G357" s="6">
-        <v>5800</v>
-      </c>
-      <c r="H357" s="6">
-        <v>10</v>
-      </c>
-      <c r="I357" s="6">
-        <v>30</v>
+      <c r="A357" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B357" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C357" s="1">
+        <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>516</v>
+      </c>
+      <c r="E357" s="1">
+        <v>0</v>
+      </c>
+      <c r="F357" s="1">
+        <v>14</v>
+      </c>
+      <c r="G357" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H357" s="1">
+        <v>1</v>
+      </c>
+      <c r="I357" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A358" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B358" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C358" s="6">
-        <v>1</v>
-      </c>
-      <c r="D358" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E358" s="6">
-        <v>0</v>
-      </c>
-      <c r="F358" s="7">
-        <f>VLOOKUP(D358,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1112</v>
-      </c>
-      <c r="G358" s="6">
-        <v>5200</v>
-      </c>
-      <c r="H358" s="6">
-        <v>10</v>
-      </c>
-      <c r="I358" s="6">
-        <v>30</v>
+      <c r="A358" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B358" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C358" s="1">
+        <v>1</v>
+      </c>
+      <c r="D358" t="s">
+        <v>512</v>
+      </c>
+      <c r="E358" s="1">
+        <v>0</v>
+      </c>
+      <c r="F358" s="1">
+        <v>16</v>
+      </c>
+      <c r="G358" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H358" s="1">
+        <v>1</v>
+      </c>
+      <c r="I358" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
@@ -13821,17 +13844,17 @@
         <v>1</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E359" s="6">
         <v>0</v>
       </c>
       <c r="F359" s="7">
         <f>VLOOKUP(D359,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="G359" s="6">
-        <v>4600</v>
+        <v>10000</v>
       </c>
       <c r="H359" s="6">
         <v>10</v>
@@ -13851,17 +13874,17 @@
         <v>1</v>
       </c>
       <c r="D360" s="6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E360" s="6">
         <v>0</v>
       </c>
       <c r="F360" s="7">
         <f>VLOOKUP(D360,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="G360" s="6">
-        <v>4000</v>
+        <v>9400</v>
       </c>
       <c r="H360" s="6">
         <v>10</v>
@@ -13881,17 +13904,17 @@
         <v>1</v>
       </c>
       <c r="D361" s="6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E361" s="6">
         <v>0</v>
       </c>
       <c r="F361" s="7">
         <f>VLOOKUP(D361,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="G361" s="6">
-        <v>3400</v>
+        <v>8800</v>
       </c>
       <c r="H361" s="6">
         <v>10</v>
@@ -13911,17 +13934,17 @@
         <v>1</v>
       </c>
       <c r="D362" s="6" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="E362" s="6">
         <v>0</v>
       </c>
       <c r="F362" s="7">
         <f>VLOOKUP(D362,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1116</v>
+        <v>1105</v>
       </c>
       <c r="G362" s="6">
-        <v>2800</v>
+        <v>8200</v>
       </c>
       <c r="H362" s="6">
         <v>10</v>
@@ -13941,17 +13964,17 @@
         <v>1</v>
       </c>
       <c r="D363" s="6" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E363" s="6">
         <v>0</v>
       </c>
       <c r="F363" s="7">
         <f>VLOOKUP(D363,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1117</v>
+        <v>1106</v>
       </c>
       <c r="G363" s="6">
-        <v>2200</v>
+        <v>7600</v>
       </c>
       <c r="H363" s="6">
         <v>10</v>
@@ -13961,417 +13984,417 @@
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A364" s="8" t="s">
+      <c r="A364" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B364" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C364" s="6">
+        <v>1</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E364" s="6">
+        <v>0</v>
+      </c>
+      <c r="F364" s="7">
+        <f>VLOOKUP(D364,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1109</v>
+      </c>
+      <c r="G364" s="6">
+        <v>7000</v>
+      </c>
+      <c r="H364" s="6">
+        <v>10</v>
+      </c>
+      <c r="I364" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A365" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B365" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C365" s="6">
+        <v>1</v>
+      </c>
+      <c r="D365" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E365" s="6">
+        <v>0</v>
+      </c>
+      <c r="F365" s="7">
+        <f>VLOOKUP(D365,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1110</v>
+      </c>
+      <c r="G365" s="6">
+        <v>6400</v>
+      </c>
+      <c r="H365" s="6">
+        <v>10</v>
+      </c>
+      <c r="I365" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A366" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B366" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C366" s="6">
+        <v>1</v>
+      </c>
+      <c r="D366" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E366" s="6">
+        <v>0</v>
+      </c>
+      <c r="F366" s="7">
+        <f>VLOOKUP(D366,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1111</v>
+      </c>
+      <c r="G366" s="6">
+        <v>5800</v>
+      </c>
+      <c r="H366" s="6">
+        <v>10</v>
+      </c>
+      <c r="I366" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A367" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B367" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C367" s="6">
+        <v>1</v>
+      </c>
+      <c r="D367" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E367" s="6">
+        <v>0</v>
+      </c>
+      <c r="F367" s="7">
+        <f>VLOOKUP(D367,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1112</v>
+      </c>
+      <c r="G367" s="6">
+        <v>5200</v>
+      </c>
+      <c r="H367" s="6">
+        <v>10</v>
+      </c>
+      <c r="I367" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A368" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B368" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C368" s="6">
+        <v>1</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E368" s="6">
+        <v>0</v>
+      </c>
+      <c r="F368" s="7">
+        <f>VLOOKUP(D368,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1113</v>
+      </c>
+      <c r="G368" s="6">
+        <v>4600</v>
+      </c>
+      <c r="H368" s="6">
+        <v>10</v>
+      </c>
+      <c r="I368" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A369" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B369" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C369" s="6">
+        <v>1</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E369" s="6">
+        <v>0</v>
+      </c>
+      <c r="F369" s="7">
+        <f>VLOOKUP(D369,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1114</v>
+      </c>
+      <c r="G369" s="6">
+        <v>4000</v>
+      </c>
+      <c r="H369" s="6">
+        <v>10</v>
+      </c>
+      <c r="I369" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A370" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B370" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C370" s="6">
+        <v>1</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E370" s="6">
+        <v>0</v>
+      </c>
+      <c r="F370" s="7">
+        <f>VLOOKUP(D370,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1115</v>
+      </c>
+      <c r="G370" s="6">
+        <v>3400</v>
+      </c>
+      <c r="H370" s="6">
+        <v>10</v>
+      </c>
+      <c r="I370" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A371" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B371" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C371" s="6">
+        <v>1</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E371" s="6">
+        <v>0</v>
+      </c>
+      <c r="F371" s="7">
+        <f>VLOOKUP(D371,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1116</v>
+      </c>
+      <c r="G371" s="6">
+        <v>2800</v>
+      </c>
+      <c r="H371" s="6">
+        <v>10</v>
+      </c>
+      <c r="I371" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A372" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B372" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C372" s="6">
+        <v>1</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E372" s="6">
+        <v>0</v>
+      </c>
+      <c r="F372" s="7">
+        <f>VLOOKUP(D372,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1117</v>
+      </c>
+      <c r="G372" s="6">
+        <v>2200</v>
+      </c>
+      <c r="H372" s="6">
+        <v>10</v>
+      </c>
+      <c r="I372" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A373" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B364" s="8">
+      <c r="B373" s="8">
         <v>40001</v>
       </c>
-      <c r="C364" s="8">
-        <v>1</v>
-      </c>
-      <c r="D364" s="8" t="s">
+      <c r="C373" s="8">
+        <v>1</v>
+      </c>
+      <c r="D373" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E364" s="8">
-        <v>0</v>
-      </c>
-      <c r="F364" s="9">
-        <f>VLOOKUP(D364,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E373" s="8">
+        <v>0</v>
+      </c>
+      <c r="F373" s="9">
+        <f>VLOOKUP(D373,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1009</v>
       </c>
-      <c r="G364" s="8">
+      <c r="G373" s="8">
         <v>8800</v>
       </c>
-      <c r="H364" s="8">
+      <c r="H373" s="8">
         <v>10</v>
       </c>
-      <c r="I364" s="8">
+      <c r="I373" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A365" s="8" t="s">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A374" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B365" s="8">
+      <c r="B374" s="8">
         <v>40001</v>
       </c>
-      <c r="C365" s="8">
-        <v>1</v>
-      </c>
-      <c r="D365" s="8" t="s">
+      <c r="C374" s="8">
+        <v>1</v>
+      </c>
+      <c r="D374" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E365" s="8">
-        <v>0</v>
-      </c>
-      <c r="F365" s="9">
-        <f>VLOOKUP(D365,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E374" s="8">
+        <v>0</v>
+      </c>
+      <c r="F374" s="9">
+        <f>VLOOKUP(D374,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1011</v>
       </c>
-      <c r="G365" s="8">
+      <c r="G374" s="8">
         <v>7600</v>
       </c>
-      <c r="H365" s="8">
+      <c r="H374" s="8">
         <v>10</v>
       </c>
-      <c r="I365" s="8">
+      <c r="I374" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A366" s="8" t="s">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A375" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B366" s="8">
+      <c r="B375" s="8">
         <v>40001</v>
       </c>
-      <c r="C366" s="8">
-        <v>1</v>
-      </c>
-      <c r="D366" s="8" t="s">
+      <c r="C375" s="8">
+        <v>1</v>
+      </c>
+      <c r="D375" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E366" s="8">
-        <v>0</v>
-      </c>
-      <c r="F366" s="9">
-        <f>VLOOKUP(D366,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E375" s="8">
+        <v>0</v>
+      </c>
+      <c r="F375" s="9">
+        <f>VLOOKUP(D375,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1014</v>
       </c>
-      <c r="G366" s="8">
+      <c r="G375" s="8">
         <v>6400</v>
       </c>
-      <c r="H366" s="8">
+      <c r="H375" s="8">
         <v>10</v>
       </c>
-      <c r="I366" s="8">
+      <c r="I375" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A367" s="8" t="s">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A376" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B367" s="8">
+      <c r="B376" s="8">
         <v>40001</v>
       </c>
-      <c r="C367" s="8">
-        <v>1</v>
-      </c>
-      <c r="D367" s="8" t="s">
+      <c r="C376" s="8">
+        <v>1</v>
+      </c>
+      <c r="D376" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E367" s="8">
-        <v>0</v>
-      </c>
-      <c r="F367" s="9">
-        <f>VLOOKUP(D367,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E376" s="8">
+        <v>0</v>
+      </c>
+      <c r="F376" s="9">
+        <f>VLOOKUP(D376,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1016</v>
       </c>
-      <c r="G367" s="8">
+      <c r="G376" s="8">
         <v>5200</v>
       </c>
-      <c r="H367" s="8">
+      <c r="H376" s="8">
         <v>10</v>
       </c>
-      <c r="I367" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A368" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B368" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C368" s="8">
-        <v>1</v>
-      </c>
-      <c r="D368" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E368" s="8">
-        <v>0</v>
-      </c>
-      <c r="F368" s="9">
-        <f>VLOOKUP(D368,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1017</v>
-      </c>
-      <c r="G368" s="8">
-        <v>4000</v>
-      </c>
-      <c r="H368" s="8">
-        <v>10</v>
-      </c>
-      <c r="I368" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A369" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B369" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C369" s="8">
-        <v>1</v>
-      </c>
-      <c r="D369" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E369" s="8">
-        <v>0</v>
-      </c>
-      <c r="F369" s="9">
-        <f>VLOOKUP(D369,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1022</v>
-      </c>
-      <c r="G369" s="8">
-        <v>2800</v>
-      </c>
-      <c r="H369" s="8">
-        <v>10</v>
-      </c>
-      <c r="I369" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A370" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B370" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C370" s="8">
-        <v>1</v>
-      </c>
-      <c r="D370" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E370" s="8">
-        <v>0</v>
-      </c>
-      <c r="F370" s="9">
-        <f>VLOOKUP(D370,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1024</v>
-      </c>
-      <c r="G370" s="8">
-        <v>1600</v>
-      </c>
-      <c r="H370" s="8">
-        <v>10</v>
-      </c>
-      <c r="I370" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A371" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B371" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C371" s="4">
-        <v>1</v>
-      </c>
-      <c r="D371" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E371" s="4">
-        <v>0</v>
-      </c>
-      <c r="F371" s="5">
-        <f>VLOOKUP(D371,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1000</v>
-      </c>
-      <c r="G371" s="4">
-        <v>10000</v>
-      </c>
-      <c r="H371" s="4">
-        <v>10</v>
-      </c>
-      <c r="I371" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A372" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B372" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C372" s="4">
-        <v>1</v>
-      </c>
-      <c r="D372" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E372" s="4">
-        <v>0</v>
-      </c>
-      <c r="F372" s="5">
-        <f>VLOOKUP(D372,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1010</v>
-      </c>
-      <c r="G372" s="4">
-        <v>7200</v>
-      </c>
-      <c r="H372" s="4">
-        <v>10</v>
-      </c>
-      <c r="I372" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A373" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B373" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C373" s="4">
-        <v>1</v>
-      </c>
-      <c r="D373" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E373" s="4">
-        <v>0</v>
-      </c>
-      <c r="F373" s="5">
-        <f>VLOOKUP(D373,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1013</v>
-      </c>
-      <c r="G373" s="4">
-        <v>5800</v>
-      </c>
-      <c r="H373" s="4">
-        <v>10</v>
-      </c>
-      <c r="I373" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A374" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B374" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C374" s="4">
-        <v>1</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E374" s="4">
-        <v>0</v>
-      </c>
-      <c r="F374" s="5">
-        <f>VLOOKUP(D374,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1018</v>
-      </c>
-      <c r="G374" s="4">
-        <v>4400</v>
-      </c>
-      <c r="H374" s="4">
-        <v>10</v>
-      </c>
-      <c r="I374" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A375" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B375" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C375" s="4">
-        <v>1</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E375" s="4">
-        <v>0</v>
-      </c>
-      <c r="F375" s="5">
-        <f>VLOOKUP(D375,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1020</v>
-      </c>
-      <c r="G375" s="4">
-        <v>3000</v>
-      </c>
-      <c r="H375" s="4">
-        <v>10</v>
-      </c>
-      <c r="I375" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A376" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B376" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C376" s="4">
-        <v>1</v>
-      </c>
-      <c r="D376" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E376" s="4">
-        <v>0</v>
-      </c>
-      <c r="F376" s="5">
-        <f>VLOOKUP(D376,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1023</v>
-      </c>
-      <c r="G376" s="4">
-        <v>1600</v>
-      </c>
-      <c r="H376" s="4">
-        <v>10</v>
-      </c>
-      <c r="I376" s="4">
+      <c r="I376" s="8">
         <v>30</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B377" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C377" s="8">
         <v>1</v>
       </c>
       <c r="D377" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E377" s="8">
         <v>0</v>
       </c>
       <c r="F377" s="9">
         <f>VLOOKUP(D377,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1000</v>
+        <v>1017</v>
       </c>
       <c r="G377" s="8">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H377" s="8">
         <v>10</v>
@@ -14382,26 +14405,26 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B378" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C378" s="8">
         <v>1</v>
       </c>
       <c r="D378" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E378" s="8">
         <v>0</v>
       </c>
       <c r="F378" s="9">
         <f>VLOOKUP(D378,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="G378" s="8">
-        <v>8600</v>
+        <v>2800</v>
       </c>
       <c r="H378" s="8">
         <v>10</v>
@@ -14412,26 +14435,26 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B379" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C379" s="8">
         <v>1</v>
       </c>
       <c r="D379" s="8" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E379" s="8">
         <v>0</v>
       </c>
       <c r="F379" s="9">
         <f>VLOOKUP(D379,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1006</v>
+        <v>1024</v>
       </c>
       <c r="G379" s="8">
-        <v>7200</v>
+        <v>1600</v>
       </c>
       <c r="H379" s="8">
         <v>10</v>
@@ -14440,588 +14463,588 @@
         <v>30</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A380" s="8" t="s">
+    <row r="380" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A380" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B380" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C380" s="4">
+        <v>1</v>
+      </c>
+      <c r="D380" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E380" s="4">
+        <v>0</v>
+      </c>
+      <c r="F380" s="5">
+        <f>VLOOKUP(D380,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="G380" s="4">
+        <v>10000</v>
+      </c>
+      <c r="H380" s="4">
+        <v>10</v>
+      </c>
+      <c r="I380" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A381" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B381" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C381" s="4">
+        <v>1</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E381" s="4">
+        <v>0</v>
+      </c>
+      <c r="F381" s="5">
+        <f>VLOOKUP(D381,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
+      </c>
+      <c r="G381" s="4">
+        <v>7200</v>
+      </c>
+      <c r="H381" s="4">
+        <v>10</v>
+      </c>
+      <c r="I381" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A382" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B382" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C382" s="4">
+        <v>1</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E382" s="4">
+        <v>0</v>
+      </c>
+      <c r="F382" s="5">
+        <f>VLOOKUP(D382,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1013</v>
+      </c>
+      <c r="G382" s="4">
+        <v>5800</v>
+      </c>
+      <c r="H382" s="4">
+        <v>10</v>
+      </c>
+      <c r="I382" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A383" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B383" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C383" s="4">
+        <v>1</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E383" s="4">
+        <v>0</v>
+      </c>
+      <c r="F383" s="5">
+        <f>VLOOKUP(D383,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1018</v>
+      </c>
+      <c r="G383" s="4">
+        <v>4400</v>
+      </c>
+      <c r="H383" s="4">
+        <v>10</v>
+      </c>
+      <c r="I383" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A384" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B384" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C384" s="4">
+        <v>1</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E384" s="4">
+        <v>0</v>
+      </c>
+      <c r="F384" s="5">
+        <f>VLOOKUP(D384,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1020</v>
+      </c>
+      <c r="G384" s="4">
+        <v>3000</v>
+      </c>
+      <c r="H384" s="4">
+        <v>10</v>
+      </c>
+      <c r="I384" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A385" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B385" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C385" s="4">
+        <v>1</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E385" s="4">
+        <v>0</v>
+      </c>
+      <c r="F385" s="5">
+        <f>VLOOKUP(D385,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1023</v>
+      </c>
+      <c r="G385" s="4">
+        <v>1600</v>
+      </c>
+      <c r="H385" s="4">
+        <v>10</v>
+      </c>
+      <c r="I385" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A386" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B380" s="8">
+      <c r="B386" s="8">
         <v>40003</v>
       </c>
-      <c r="C380" s="8">
-        <v>1</v>
-      </c>
-      <c r="D380" s="8" t="s">
+      <c r="C386" s="8">
+        <v>1</v>
+      </c>
+      <c r="D386" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E386" s="8">
+        <v>0</v>
+      </c>
+      <c r="F386" s="9">
+        <f>VLOOKUP(D386,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="G386" s="8">
+        <v>10000</v>
+      </c>
+      <c r="H386" s="8">
+        <v>10</v>
+      </c>
+      <c r="I386" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A387" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B387" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C387" s="8">
+        <v>1</v>
+      </c>
+      <c r="D387" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E387" s="8">
+        <v>0</v>
+      </c>
+      <c r="F387" s="9">
+        <f>VLOOKUP(D387,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1009</v>
+      </c>
+      <c r="G387" s="8">
+        <v>8600</v>
+      </c>
+      <c r="H387" s="8">
+        <v>10</v>
+      </c>
+      <c r="I387" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A388" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B388" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C388" s="8">
+        <v>1</v>
+      </c>
+      <c r="D388" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E388" s="8">
+        <v>0</v>
+      </c>
+      <c r="F388" s="9">
+        <f>VLOOKUP(D388,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
+      </c>
+      <c r="G388" s="8">
+        <v>7200</v>
+      </c>
+      <c r="H388" s="8">
+        <v>10</v>
+      </c>
+      <c r="I388" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A389" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B389" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C389" s="8">
+        <v>1</v>
+      </c>
+      <c r="D389" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E380" s="8">
-        <v>0</v>
-      </c>
-      <c r="F380" s="9">
-        <f>VLOOKUP(D380,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E389" s="8">
+        <v>0</v>
+      </c>
+      <c r="F389" s="9">
+        <f>VLOOKUP(D389,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1007</v>
       </c>
-      <c r="G380" s="8">
+      <c r="G389" s="8">
         <v>5800</v>
       </c>
-      <c r="H380" s="8">
+      <c r="H389" s="8">
         <v>10</v>
       </c>
-      <c r="I380" s="8">
+      <c r="I389" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A381" s="8" t="s">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A390" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B381" s="8">
+      <c r="B390" s="8">
         <v>40003</v>
       </c>
-      <c r="C381" s="8">
-        <v>1</v>
-      </c>
-      <c r="D381" s="8" t="s">
+      <c r="C390" s="8">
+        <v>1</v>
+      </c>
+      <c r="D390" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E381" s="8">
-        <v>0</v>
-      </c>
-      <c r="F381" s="9">
-        <f>VLOOKUP(D381,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E390" s="8">
+        <v>0</v>
+      </c>
+      <c r="F390" s="9">
+        <f>VLOOKUP(D390,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1014</v>
       </c>
-      <c r="G381" s="8">
+      <c r="G390" s="8">
         <v>4400</v>
       </c>
-      <c r="H381" s="8">
+      <c r="H390" s="8">
         <v>10</v>
       </c>
-      <c r="I381" s="8">
+      <c r="I390" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A382" s="8" t="s">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A391" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B382" s="8">
+      <c r="B391" s="8">
         <v>40003</v>
       </c>
-      <c r="C382" s="8">
-        <v>1</v>
-      </c>
-      <c r="D382" s="8" t="s">
+      <c r="C391" s="8">
+        <v>1</v>
+      </c>
+      <c r="D391" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E382" s="8">
-        <v>0</v>
-      </c>
-      <c r="F382" s="9">
-        <f>VLOOKUP(D382,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E391" s="8">
+        <v>0</v>
+      </c>
+      <c r="F391" s="9">
+        <f>VLOOKUP(D391,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1017</v>
       </c>
-      <c r="G382" s="8">
+      <c r="G391" s="8">
         <v>3000</v>
       </c>
-      <c r="H382" s="8">
+      <c r="H391" s="8">
         <v>10</v>
       </c>
-      <c r="I382" s="8">
+      <c r="I391" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A383" s="8" t="s">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A392" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B383" s="8">
+      <c r="B392" s="8">
         <v>40003</v>
       </c>
-      <c r="C383" s="8">
-        <v>1</v>
-      </c>
-      <c r="D383" s="8" t="s">
+      <c r="C392" s="8">
+        <v>1</v>
+      </c>
+      <c r="D392" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E383" s="8">
-        <v>0</v>
-      </c>
-      <c r="F383" s="9">
-        <f>VLOOKUP(D383,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E392" s="8">
+        <v>0</v>
+      </c>
+      <c r="F392" s="9">
+        <f>VLOOKUP(D392,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1020</v>
       </c>
-      <c r="G383" s="8">
+      <c r="G392" s="8">
         <v>1600</v>
       </c>
-      <c r="H383" s="8">
+      <c r="H392" s="8">
         <v>10</v>
       </c>
-      <c r="I383" s="8">
+      <c r="I392" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A384" s="1" t="s">
+    <row r="393" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A393" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B384" s="1">
+      <c r="B393" s="1">
         <v>40004</v>
       </c>
-      <c r="C384" s="1">
-        <v>1</v>
-      </c>
-      <c r="D384" s="3" t="s">
+      <c r="C393" s="1">
+        <v>1</v>
+      </c>
+      <c r="D393" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E384" s="1">
-        <v>0</v>
-      </c>
-      <c r="F384">
-        <f>VLOOKUP(D384,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E393" s="1">
+        <v>0</v>
+      </c>
+      <c r="F393">
+        <f>VLOOKUP(D393,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="G384" s="1">
+      <c r="G393" s="1">
         <v>10000</v>
       </c>
-      <c r="H384" s="1">
+      <c r="H393" s="1">
         <v>10</v>
       </c>
-      <c r="I384" s="1">
+      <c r="I393" s="1">
         <v>30</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A385" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B385" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C385" s="1">
-        <v>1</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E385" s="1">
-        <v>0</v>
-      </c>
-      <c r="F385">
-        <f>VLOOKUP(D385,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1006</v>
-      </c>
-      <c r="G385" s="1">
-        <v>7200</v>
-      </c>
-      <c r="H385" s="1">
-        <v>10</v>
-      </c>
-      <c r="I385" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A386" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B386" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C386" s="1">
-        <v>1</v>
-      </c>
-      <c r="D386" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E386" s="1">
-        <v>0</v>
-      </c>
-      <c r="F386">
-        <f>VLOOKUP(D386,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1007</v>
-      </c>
-      <c r="G386" s="1">
-        <v>5800</v>
-      </c>
-      <c r="H386" s="1">
-        <v>10</v>
-      </c>
-      <c r="I386" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A387" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B387" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C387" s="1">
-        <v>1</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E387" s="1">
-        <v>0</v>
-      </c>
-      <c r="F387">
-        <f>VLOOKUP(D387,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1010</v>
-      </c>
-      <c r="G387" s="1">
-        <v>4400</v>
-      </c>
-      <c r="H387" s="1">
-        <v>10</v>
-      </c>
-      <c r="I387" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A388" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B388" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C388" s="1">
-        <v>1</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E388" s="1">
-        <v>0</v>
-      </c>
-      <c r="F388">
-        <f>VLOOKUP(D388,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1015</v>
-      </c>
-      <c r="G388" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H388" s="1">
-        <v>10</v>
-      </c>
-      <c r="I388" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A389" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B389" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C389" s="1">
-        <v>1</v>
-      </c>
-      <c r="D389" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E389" s="1">
-        <v>0</v>
-      </c>
-      <c r="F389">
-        <f>VLOOKUP(D389,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1021</v>
-      </c>
-      <c r="G389" s="1">
-        <v>1600</v>
-      </c>
-      <c r="H389" s="1">
-        <v>10</v>
-      </c>
-      <c r="I389" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A390" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B390" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C390" s="1">
-        <v>1</v>
-      </c>
-      <c r="D390" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E390" s="1">
-        <v>0</v>
-      </c>
-      <c r="F390" s="1">
-        <f>VLOOKUP(D390,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
-      </c>
-      <c r="G390" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H390" s="1">
-        <v>1</v>
-      </c>
-      <c r="I390" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A391" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B391" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C391" s="1">
-        <v>1</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E391" s="1">
-        <v>0</v>
-      </c>
-      <c r="F391" s="1">
-        <f>VLOOKUP(D391,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
-      </c>
-      <c r="G391" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H391" s="1">
-        <v>1</v>
-      </c>
-      <c r="I391" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A392" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B392" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C392" s="1">
-        <v>1</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E392" s="1">
-        <v>0</v>
-      </c>
-      <c r="F392" s="1">
-        <f>VLOOKUP(D392,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
-      </c>
-      <c r="G392" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H392" s="1">
-        <v>1</v>
-      </c>
-      <c r="I392" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A393" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B393" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C393" s="1">
-        <v>1</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E393" s="1">
-        <v>0</v>
-      </c>
-      <c r="F393" s="1">
-        <f>VLOOKUP(D393,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
-      </c>
-      <c r="G393" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H393" s="1">
-        <v>1</v>
-      </c>
-      <c r="I393" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="B394" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C394" s="1">
         <v>1</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>535</v>
+        <v>58</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
       </c>
-      <c r="F394" s="1">
-        <f>VLOOKUP(D394,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
+      <c r="F394">
+        <f>VLOOKUP(D394,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
       </c>
       <c r="G394" s="1">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="H394" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I394" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="B395" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C395" s="1">
         <v>1</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>536</v>
+        <v>59</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
       </c>
-      <c r="F395" s="1">
-        <f>VLOOKUP(D395,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
+      <c r="F395">
+        <f>VLOOKUP(D395,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
       </c>
       <c r="G395" s="1">
-        <v>1000</v>
+        <v>5800</v>
       </c>
       <c r="H395" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I395" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="B396" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C396" s="1">
         <v>1</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>537</v>
+        <v>66</v>
       </c>
       <c r="E396" s="1">
         <v>0</v>
       </c>
-      <c r="F396" s="1">
-        <f>VLOOKUP(D396,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+      <c r="F396">
+        <f>VLOOKUP(D396,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
       </c>
       <c r="G396" s="1">
-        <v>1000</v>
+        <v>4400</v>
       </c>
       <c r="H396" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I396" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="B397" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C397" s="1">
         <v>1</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>538</v>
+        <v>60</v>
       </c>
       <c r="E397" s="1">
         <v>0</v>
       </c>
-      <c r="F397" s="1">
-        <f>VLOOKUP(D397,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+      <c r="F397">
+        <f>VLOOKUP(D397,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1015</v>
       </c>
       <c r="G397" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H397" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I397" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
-        <v>548</v>
+        <v>28</v>
       </c>
       <c r="B398" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C398" s="1">
         <v>1</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>539</v>
+        <v>61</v>
       </c>
       <c r="E398" s="1">
         <v>0</v>
       </c>
-      <c r="F398" s="1">
-        <f>VLOOKUP(D398,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+      <c r="F398">
+        <f>VLOOKUP(D398,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1021</v>
       </c>
       <c r="G398" s="1">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H398" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I398" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B399" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C399" s="1">
         <v>1</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E399" s="1">
         <v>0</v>
@@ -15042,23 +15065,23 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B400" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C400" s="1">
         <v>1</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E400" s="1">
         <v>0</v>
       </c>
       <c r="F400" s="1">
         <f>VLOOKUP(D400,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
+        <v>5007</v>
       </c>
       <c r="G400" s="1">
         <v>1000</v>
@@ -15072,23 +15095,23 @@
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B401" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C401" s="1">
         <v>1</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E401" s="1">
         <v>0</v>
       </c>
       <c r="F401" s="1">
         <f>VLOOKUP(D401,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5016</v>
       </c>
       <c r="G401" s="1">
         <v>1000</v>
@@ -15102,23 +15125,23 @@
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B402" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C402" s="1">
         <v>1</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E402" s="1">
         <v>0</v>
       </c>
       <c r="F402" s="1">
         <f>VLOOKUP(D402,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
+        <v>5017</v>
       </c>
       <c r="G402" s="1">
         <v>1000</v>
@@ -15132,23 +15155,23 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B403" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C403" s="1">
         <v>1</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E403" s="1">
         <v>0</v>
       </c>
       <c r="F403" s="1">
         <f>VLOOKUP(D403,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
+        <v>5020</v>
       </c>
       <c r="G403" s="1">
         <v>1000</v>
@@ -15162,23 +15185,23 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B404" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C404" s="1">
         <v>1</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E404" s="1">
         <v>0</v>
       </c>
       <c r="F404" s="1">
         <f>VLOOKUP(D404,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5022</v>
       </c>
       <c r="G404" s="1">
         <v>1000</v>
@@ -15192,23 +15215,23 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B405" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C405" s="1">
         <v>1</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
       </c>
       <c r="F405" s="1">
         <f>VLOOKUP(D405,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5019</v>
       </c>
       <c r="G405" s="1">
         <v>1000</v>
@@ -15222,23 +15245,23 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B406" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C406" s="1">
         <v>1</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
       </c>
       <c r="F406" s="1">
         <f>VLOOKUP(D406,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5008</v>
+        <v>5015</v>
       </c>
       <c r="G406" s="1">
         <v>1000</v>
@@ -15252,23 +15275,23 @@
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B407" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C407" s="1">
         <v>1</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
       </c>
       <c r="F407" s="1">
         <f>VLOOKUP(D407,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5009</v>
+        <v>5024</v>
       </c>
       <c r="G407" s="1">
         <v>1000</v>
@@ -15282,7 +15305,7 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B408" s="1">
         <v>50001</v>
@@ -15291,14 +15314,14 @@
         <v>1</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
       </c>
       <c r="F408" s="1">
         <f>VLOOKUP(D408,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5025</v>
+        <v>5006</v>
       </c>
       <c r="G408" s="1">
         <v>1000</v>
@@ -15312,7 +15335,7 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B409" s="1">
         <v>50001</v>
@@ -15321,14 +15344,14 @@
         <v>1</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
       </c>
       <c r="F409" s="1">
         <f>VLOOKUP(D409,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5026</v>
+        <v>5016</v>
       </c>
       <c r="G409" s="1">
         <v>1000</v>
@@ -15342,7 +15365,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B410" s="1">
         <v>50001</v>
@@ -15351,14 +15374,14 @@
         <v>1</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
       </c>
       <c r="F410" s="1">
         <f>VLOOKUP(D410,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5031</v>
+        <v>5017</v>
       </c>
       <c r="G410" s="1">
         <v>1000</v>
@@ -15372,7 +15395,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B411" s="1">
         <v>50001</v>
@@ -15381,14 +15404,14 @@
         <v>1</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
       </c>
       <c r="F411" s="1">
         <f>VLOOKUP(D411,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5032</v>
+        <v>5020</v>
       </c>
       <c r="G411" s="1">
         <v>1000</v>
@@ -15402,23 +15425,23 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B412" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C412" s="1">
         <v>1</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
       </c>
       <c r="F412" s="1">
         <f>VLOOKUP(D412,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5022</v>
       </c>
       <c r="G412" s="1">
         <v>1000</v>
@@ -15432,23 +15455,23 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B413" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C413" s="1">
         <v>1</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
       </c>
       <c r="F413" s="1">
         <f>VLOOKUP(D413,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5004</v>
+        <v>5015</v>
       </c>
       <c r="G413" s="1">
         <v>1000</v>
@@ -15462,23 +15485,23 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B414" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C414" s="1">
         <v>1</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
       </c>
       <c r="F414" s="1">
         <f>VLOOKUP(D414,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5005</v>
+        <v>5024</v>
       </c>
       <c r="G414" s="1">
         <v>1000</v>
@@ -15492,23 +15515,23 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B415" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C415" s="1">
         <v>1</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
       </c>
       <c r="F415" s="1">
         <f>VLOOKUP(D415,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="G415" s="1">
         <v>1000</v>
@@ -15522,23 +15545,23 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B416" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C416" s="1">
         <v>1</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
       </c>
       <c r="F416" s="1">
         <f>VLOOKUP(D416,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5009</v>
       </c>
       <c r="G416" s="1">
         <v>1000</v>
@@ -15552,23 +15575,23 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B417" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C417" s="1">
         <v>1</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
       </c>
       <c r="F417" s="1">
         <f>VLOOKUP(D417,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="G417" s="1">
         <v>1000</v>
@@ -15582,10 +15605,10 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B418" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C418" s="1">
         <v>1</v>
@@ -15598,7 +15621,7 @@
       </c>
       <c r="F418" s="1">
         <f>VLOOKUP(D418,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5008</v>
+        <v>5026</v>
       </c>
       <c r="G418" s="1">
         <v>1000</v>
@@ -15612,10 +15635,10 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B419" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C419" s="1">
         <v>1</v>
@@ -15628,7 +15651,7 @@
       </c>
       <c r="F419" s="1">
         <f>VLOOKUP(D419,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5009</v>
+        <v>5031</v>
       </c>
       <c r="G419" s="1">
         <v>1000</v>
@@ -15642,10 +15665,10 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B420" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C420" s="1">
         <v>1</v>
@@ -15658,7 +15681,7 @@
       </c>
       <c r="F420" s="1">
         <f>VLOOKUP(D420,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5025</v>
+        <v>5032</v>
       </c>
       <c r="G420" s="1">
         <v>1000</v>
@@ -15672,7 +15695,7 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B421" s="1">
         <v>50002</v>
@@ -15681,14 +15704,14 @@
         <v>1</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
       </c>
       <c r="F421" s="1">
         <f>VLOOKUP(D421,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5026</v>
+        <v>5006</v>
       </c>
       <c r="G421" s="1">
         <v>1000</v>
@@ -15702,7 +15725,7 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B422" s="1">
         <v>50002</v>
@@ -15711,14 +15734,14 @@
         <v>1</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
       </c>
       <c r="F422" s="1">
         <f>VLOOKUP(D422,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5031</v>
+        <v>5004</v>
       </c>
       <c r="G422" s="1">
         <v>1000</v>
@@ -15732,7 +15755,7 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B423" s="1">
         <v>50002</v>
@@ -15741,14 +15764,14 @@
         <v>1</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
       </c>
       <c r="F423" s="1">
         <f>VLOOKUP(D423,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5032</v>
+        <v>5005</v>
       </c>
       <c r="G423" s="1">
         <v>1000</v>
@@ -15762,7 +15785,7 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B424" s="1">
         <v>50002</v>
@@ -15771,14 +15794,14 @@
         <v>1</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
       </c>
       <c r="F424" s="1">
         <f>VLOOKUP(D424,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5012</v>
       </c>
       <c r="G424" s="1">
         <v>1000</v>
@@ -15792,23 +15815,23 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B425" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C425" s="1">
         <v>1</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>562</v>
+        <v>535</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
       </c>
       <c r="F425" s="1">
         <f>VLOOKUP(D425,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5015</v>
       </c>
       <c r="G425" s="1">
         <v>1000</v>
@@ -15822,23 +15845,23 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B426" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C426" s="1">
         <v>1</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
       </c>
       <c r="F426" s="1">
         <f>VLOOKUP(D426,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5024</v>
       </c>
       <c r="G426" s="1">
         <v>1000</v>
@@ -15852,23 +15875,23 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B427" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C427" s="1">
         <v>1</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
       </c>
       <c r="F427" s="1">
         <f>VLOOKUP(D427,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5008</v>
       </c>
       <c r="G427" s="1">
         <v>1000</v>
@@ -15882,23 +15905,23 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B428" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C428" s="1">
         <v>1</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
       </c>
       <c r="F428" s="1">
         <f>VLOOKUP(D428,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5009</v>
       </c>
       <c r="G428" s="1">
         <v>1000</v>
@@ -15912,23 +15935,23 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B429" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C429" s="1">
         <v>1</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
       </c>
       <c r="F429" s="1">
         <f>VLOOKUP(D429,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5025</v>
       </c>
       <c r="G429" s="1">
         <v>1000</v>
@@ -15942,23 +15965,23 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B430" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C430" s="1">
         <v>1</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
       </c>
       <c r="F430" s="1">
         <f>VLOOKUP(D430,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5026</v>
       </c>
       <c r="G430" s="1">
         <v>1000</v>
@@ -15972,23 +15995,23 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B431" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C431" s="1">
         <v>1</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
       </c>
       <c r="F431" s="1">
         <f>VLOOKUP(D431,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5031</v>
       </c>
       <c r="G431" s="1">
         <v>1000</v>
@@ -16002,23 +16025,23 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B432" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C432" s="1">
         <v>1</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
       </c>
       <c r="F432" s="1">
         <f>VLOOKUP(D432,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5032</v>
       </c>
       <c r="G432" s="1">
         <v>1000</v>
@@ -16032,23 +16055,23 @@
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B433" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C433" s="1">
         <v>1</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
       </c>
       <c r="F433" s="1">
         <f>VLOOKUP(D433,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5019</v>
       </c>
       <c r="G433" s="1">
         <v>1000</v>
@@ -16062,7 +16085,7 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B434" s="1">
         <v>50003</v>
@@ -16071,14 +16094,14 @@
         <v>1</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
       </c>
       <c r="F434" s="1">
         <f>VLOOKUP(D434,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
+        <v>5006</v>
       </c>
       <c r="G434" s="1">
         <v>1000</v>
@@ -16092,7 +16115,7 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B435" s="1">
         <v>50003</v>
@@ -16101,14 +16124,14 @@
         <v>1</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
       </c>
       <c r="F435" s="1">
         <f>VLOOKUP(D435,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5001</v>
       </c>
       <c r="G435" s="1">
         <v>1000</v>
@@ -16122,7 +16145,7 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B436" s="1">
         <v>50003</v>
@@ -16131,14 +16154,14 @@
         <v>1</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
       </c>
       <c r="F436" s="1">
         <f>VLOOKUP(D436,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5014</v>
       </c>
       <c r="G436" s="1">
         <v>1000</v>
@@ -16152,23 +16175,23 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B437" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C437" s="1">
         <v>1</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
       </c>
       <c r="F437" s="1">
         <f>VLOOKUP(D437,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="G437" s="1">
         <v>1000</v>
@@ -16182,23 +16205,23 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B438" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C438" s="1">
         <v>1</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
       </c>
       <c r="F438" s="1">
         <f>VLOOKUP(D438,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5003</v>
       </c>
       <c r="G438" s="1">
         <v>1000</v>
@@ -16212,23 +16235,23 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B439" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C439" s="1">
         <v>1</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
       </c>
       <c r="F439" s="1">
         <f>VLOOKUP(D439,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5018</v>
       </c>
       <c r="G439" s="1">
         <v>1000</v>
@@ -16242,23 +16265,23 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B440" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C440" s="1">
         <v>1</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
       </c>
       <c r="F440" s="1">
         <f>VLOOKUP(D440,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5027</v>
       </c>
       <c r="G440" s="1">
         <v>1000</v>
@@ -16272,23 +16295,23 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B441" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C441" s="1">
         <v>1</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
       </c>
       <c r="F441" s="1">
         <f>VLOOKUP(D441,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5028</v>
       </c>
       <c r="G441" s="1">
         <v>1000</v>
@@ -16302,23 +16325,23 @@
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B442" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C442" s="1">
         <v>1</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
       </c>
       <c r="F442" s="1">
         <f>VLOOKUP(D442,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5029</v>
       </c>
       <c r="G442" s="1">
         <v>1000</v>
@@ -16332,23 +16355,23 @@
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B443" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C443" s="1">
         <v>1</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
       </c>
       <c r="F443" s="1">
         <f>VLOOKUP(D443,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5007</v>
       </c>
       <c r="G443" s="1">
         <v>1000</v>
@@ -16362,23 +16385,23 @@
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B444" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C444" s="1">
         <v>1</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
       </c>
       <c r="F444" s="1">
         <f>VLOOKUP(D444,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5017</v>
       </c>
       <c r="G444" s="1">
         <v>1000</v>
@@ -16392,23 +16415,23 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B445" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C445" s="1">
         <v>1</v>
       </c>
-      <c r="D445" t="s">
-        <v>556</v>
+      <c r="D445" s="1" t="s">
+        <v>534</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
       </c>
       <c r="F445" s="1">
         <f>VLOOKUP(D445,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5019</v>
       </c>
       <c r="G445" s="1">
         <v>1000</v>
@@ -16422,23 +16445,23 @@
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B446" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C446" s="1">
         <v>1</v>
       </c>
-      <c r="D446" t="s">
-        <v>557</v>
+      <c r="D446" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
       </c>
       <c r="F446" s="1">
         <f>VLOOKUP(D446,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="G446" s="1">
         <v>1000</v>
@@ -16452,23 +16475,23 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B447" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C447" s="1">
         <v>1</v>
       </c>
-      <c r="D447" t="s">
-        <v>558</v>
+      <c r="D447" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
       </c>
       <c r="F447" s="1">
         <f>VLOOKUP(D447,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="G447" s="1">
         <v>1000</v>
@@ -16482,23 +16505,23 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B448" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C448" s="1">
         <v>1</v>
       </c>
-      <c r="D448" t="s">
-        <v>559</v>
+      <c r="D448" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
       </c>
       <c r="F448" s="1">
         <f>VLOOKUP(D448,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5002</v>
       </c>
       <c r="G448" s="1">
         <v>1000</v>
@@ -16512,23 +16535,23 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B449" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C449" s="1">
         <v>1</v>
       </c>
-      <c r="D449" t="s">
-        <v>560</v>
+      <c r="D449" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
       </c>
       <c r="F449" s="1">
         <f>VLOOKUP(D449,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5003</v>
       </c>
       <c r="G449" s="1">
         <v>1000</v>
@@ -16542,23 +16565,23 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B450" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C450" s="1">
         <v>1</v>
       </c>
-      <c r="D450" t="s">
-        <v>561</v>
+      <c r="D450" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
       </c>
       <c r="F450" s="1">
         <f>VLOOKUP(D450,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5018</v>
       </c>
       <c r="G450" s="1">
         <v>1000</v>
@@ -16567,6 +16590,276 @@
         <v>1</v>
       </c>
       <c r="I450" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A451" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B451" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C451" s="1">
+        <v>1</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E451" s="1">
+        <v>0</v>
+      </c>
+      <c r="F451" s="1">
+        <f>VLOOKUP(D451,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G451" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H451" s="1">
+        <v>1</v>
+      </c>
+      <c r="I451" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A452" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B452" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C452" s="1">
+        <v>1</v>
+      </c>
+      <c r="D452" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E452" s="1">
+        <v>0</v>
+      </c>
+      <c r="F452" s="1">
+        <f>VLOOKUP(D452,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G452" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H452" s="1">
+        <v>1</v>
+      </c>
+      <c r="I452" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A453" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B453" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C453" s="1">
+        <v>1</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E453" s="1">
+        <v>0</v>
+      </c>
+      <c r="F453" s="1">
+        <f>VLOOKUP(D453,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G453" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H453" s="1">
+        <v>1</v>
+      </c>
+      <c r="I453" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A454" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B454" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C454" s="1">
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>553</v>
+      </c>
+      <c r="E454" s="1">
+        <v>0</v>
+      </c>
+      <c r="F454" s="1">
+        <f>VLOOKUP(D454,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G454" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H454" s="1">
+        <v>1</v>
+      </c>
+      <c r="I454" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A455" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B455" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C455" s="1">
+        <v>1</v>
+      </c>
+      <c r="D455" t="s">
+        <v>554</v>
+      </c>
+      <c r="E455" s="1">
+        <v>0</v>
+      </c>
+      <c r="F455" s="1">
+        <f>VLOOKUP(D455,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G455" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H455" s="1">
+        <v>1</v>
+      </c>
+      <c r="I455" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A456" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B456" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C456" s="1">
+        <v>1</v>
+      </c>
+      <c r="D456" t="s">
+        <v>555</v>
+      </c>
+      <c r="E456" s="1">
+        <v>0</v>
+      </c>
+      <c r="F456" s="1">
+        <f>VLOOKUP(D456,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G456" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H456" s="1">
+        <v>1</v>
+      </c>
+      <c r="I456" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A457" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B457" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C457" s="1">
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>556</v>
+      </c>
+      <c r="E457" s="1">
+        <v>0</v>
+      </c>
+      <c r="F457" s="1">
+        <f>VLOOKUP(D457,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G457" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H457" s="1">
+        <v>1</v>
+      </c>
+      <c r="I457" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A458" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B458" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C458" s="1">
+        <v>1</v>
+      </c>
+      <c r="D458" t="s">
+        <v>557</v>
+      </c>
+      <c r="E458" s="1">
+        <v>0</v>
+      </c>
+      <c r="F458" s="1">
+        <f>VLOOKUP(D458,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G458" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H458" s="1">
+        <v>1</v>
+      </c>
+      <c r="I458" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A459" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B459" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C459" s="1">
+        <v>1</v>
+      </c>
+      <c r="D459" t="s">
+        <v>558</v>
+      </c>
+      <c r="E459" s="1">
+        <v>0</v>
+      </c>
+      <c r="F459" s="1">
+        <f>VLOOKUP(D459,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G459" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H459" s="1">
+        <v>1</v>
+      </c>
+      <c r="I459" s="1">
         <v>1</v>
       </c>
     </row>
@@ -22832,7 +23125,7 @@
     </row>
     <row r="249" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G249" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H249">
         <v>5001</v>
@@ -22840,7 +23133,7 @@
     </row>
     <row r="250" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G250" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H250">
         <v>5002</v>
@@ -22848,7 +23141,7 @@
     </row>
     <row r="251" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G251" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H251">
         <v>5003</v>
@@ -22856,7 +23149,7 @@
     </row>
     <row r="252" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G252" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H252">
         <v>5004</v>
@@ -22864,7 +23157,7 @@
     </row>
     <row r="253" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G253" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="H253">
         <v>5005</v>
@@ -22872,7 +23165,7 @@
     </row>
     <row r="254" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G254" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H254">
         <v>5006</v>
@@ -22880,7 +23173,7 @@
     </row>
     <row r="255" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G255" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H255">
         <v>5007</v>
@@ -22888,7 +23181,7 @@
     </row>
     <row r="256" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G256" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H256">
         <v>5008</v>
@@ -22896,7 +23189,7 @@
     </row>
     <row r="257" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G257" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H257">
         <v>5009</v>
@@ -22904,7 +23197,7 @@
     </row>
     <row r="258" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G258" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H258">
         <v>5010</v>
@@ -22912,7 +23205,7 @@
     </row>
     <row r="259" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G259" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H259">
         <v>5011</v>
@@ -22920,7 +23213,7 @@
     </row>
     <row r="260" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G260" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H260">
         <v>5012</v>
@@ -22928,7 +23221,7 @@
     </row>
     <row r="261" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G261" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H261">
         <v>5013</v>
@@ -22936,7 +23229,7 @@
     </row>
     <row r="262" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G262" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H262">
         <v>5014</v>
@@ -22944,7 +23237,7 @@
     </row>
     <row r="263" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G263" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H263">
         <v>5015</v>
@@ -22952,7 +23245,7 @@
     </row>
     <row r="264" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G264" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H264">
         <v>5016</v>
@@ -22960,7 +23253,7 @@
     </row>
     <row r="265" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G265" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H265">
         <v>5017</v>
@@ -22968,7 +23261,7 @@
     </row>
     <row r="266" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G266" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H266">
         <v>5018</v>
@@ -22976,7 +23269,7 @@
     </row>
     <row r="267" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G267" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H267">
         <v>5019</v>
@@ -22984,7 +23277,7 @@
     </row>
     <row r="268" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G268" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H268">
         <v>5020</v>
@@ -22992,7 +23285,7 @@
     </row>
     <row r="269" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G269" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H269">
         <v>5021</v>
@@ -23000,7 +23293,7 @@
     </row>
     <row r="270" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G270" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H270">
         <v>5022</v>
@@ -23008,7 +23301,7 @@
     </row>
     <row r="271" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G271" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H271">
         <v>5023</v>
@@ -23016,7 +23309,7 @@
     </row>
     <row r="272" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G272" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H272">
         <v>5024</v>
@@ -23024,7 +23317,7 @@
     </row>
     <row r="273" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G273" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H273">
         <v>5025</v>
@@ -23032,7 +23325,7 @@
     </row>
     <row r="274" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G274" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H274">
         <v>5026</v>
@@ -23040,7 +23333,7 @@
     </row>
     <row r="275" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G275" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H275">
         <v>5027</v>
@@ -23048,7 +23341,7 @@
     </row>
     <row r="276" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G276" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H276">
         <v>5028</v>
@@ -23056,7 +23349,7 @@
     </row>
     <row r="277" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G277" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H277">
         <v>5029</v>
@@ -23064,7 +23357,7 @@
     </row>
     <row r="278" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G278" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H278">
         <v>5030</v>
@@ -23072,7 +23365,7 @@
     </row>
     <row r="279" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G279" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H279">
         <v>5031</v>
@@ -23080,7 +23373,7 @@
     </row>
     <row r="280" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G280" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H280">
         <v>5032</v>
@@ -23088,7 +23381,7 @@
     </row>
     <row r="281" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G281" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H281">
         <v>5200</v>
@@ -23096,7 +23389,7 @@
     </row>
     <row r="282" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G282" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H282">
         <v>5201</v>
@@ -23104,7 +23397,7 @@
     </row>
     <row r="283" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G283" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="H283">
         <v>5202</v>
@@ -23112,7 +23405,7 @@
     </row>
     <row r="284" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G284" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H284">
         <v>5203</v>
@@ -23120,7 +23413,7 @@
     </row>
     <row r="285" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G285" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="H285">
         <v>5204</v>
@@ -23128,7 +23421,7 @@
     </row>
     <row r="286" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G286" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H286">
         <v>5205</v>
@@ -23136,7 +23429,7 @@
     </row>
     <row r="287" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G287" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="H287">
         <v>5206</v>
@@ -23144,7 +23437,7 @@
     </row>
     <row r="288" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G288" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="H288">
         <v>5207</v>
@@ -23152,7 +23445,7 @@
     </row>
     <row r="289" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G289" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H289">
         <v>5208</v>
@@ -23160,7 +23453,7 @@
     </row>
     <row r="290" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G290" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="H290">
         <v>5209</v>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="606">
   <si>
     <t>text</t>
   </si>
@@ -1940,6 +1940,41 @@
   </si>
   <si>
     <t>苹果</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>小星星</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>做梦表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看守柜台表情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眨眼</t>
+  </si>
+  <si>
+    <t>思考</t>
+  </si>
+  <si>
+    <t>哼唱</t>
+  </si>
+  <si>
+    <t>计算符号</t>
+  </si>
+  <si>
+    <t>翻书</t>
   </si>
 </sst>
 </file>
@@ -3516,7 +3551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I459"/>
+  <dimension ref="A1:I471"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -13834,363 +13869,351 @@
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A359" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B359" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C359" s="6">
-        <v>1</v>
-      </c>
-      <c r="D359" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E359" s="6">
-        <v>0</v>
-      </c>
-      <c r="F359" s="7">
-        <f>VLOOKUP(D359,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1100</v>
-      </c>
-      <c r="G359" s="6">
-        <v>10000</v>
-      </c>
-      <c r="H359" s="6">
-        <v>10</v>
-      </c>
-      <c r="I359" s="6">
-        <v>30</v>
+      <c r="A359" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B359" s="1">
+        <v>30008</v>
+      </c>
+      <c r="C359" s="1">
+        <v>1</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E359" s="1">
+        <v>0</v>
+      </c>
+      <c r="F359" s="1">
+        <v>34</v>
+      </c>
+      <c r="G359" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H359" s="1">
+        <v>1</v>
+      </c>
+      <c r="I359" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A360" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B360" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C360" s="6">
-        <v>1</v>
-      </c>
-      <c r="D360" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E360" s="6">
-        <v>0</v>
-      </c>
-      <c r="F360" s="7">
-        <f>VLOOKUP(D360,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1101</v>
-      </c>
-      <c r="G360" s="6">
-        <v>9400</v>
-      </c>
-      <c r="H360" s="6">
-        <v>10</v>
-      </c>
-      <c r="I360" s="6">
-        <v>30</v>
+      <c r="A360" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B360" s="1">
+        <v>30008</v>
+      </c>
+      <c r="C360" s="1">
+        <v>1</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E360" s="1">
+        <v>0</v>
+      </c>
+      <c r="F360" s="1">
+        <v>20</v>
+      </c>
+      <c r="G360" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H360" s="1">
+        <v>1</v>
+      </c>
+      <c r="I360" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A361" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B361" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C361" s="6">
-        <v>1</v>
-      </c>
-      <c r="D361" s="6" t="s">
+      <c r="A361" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B361" s="1">
+        <v>30008</v>
+      </c>
+      <c r="C361" s="1">
+        <v>1</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E361" s="1">
+        <v>0</v>
+      </c>
+      <c r="F361" s="1">
+        <v>81</v>
+      </c>
+      <c r="G361" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H361" s="1">
+        <v>1</v>
+      </c>
+      <c r="I361" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A362" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B362" s="1">
+        <v>30008</v>
+      </c>
+      <c r="C362" s="1">
+        <v>1</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E362" s="1">
+        <v>0</v>
+      </c>
+      <c r="F362" s="1">
+        <v>5</v>
+      </c>
+      <c r="G362" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H362" s="1">
+        <v>1</v>
+      </c>
+      <c r="I362" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A363" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B363" s="1">
+        <v>30008</v>
+      </c>
+      <c r="C363" s="1">
+        <v>1</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E363" s="1">
+        <v>0</v>
+      </c>
+      <c r="F363" s="1">
+        <v>74</v>
+      </c>
+      <c r="G363" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H363" s="1">
+        <v>1</v>
+      </c>
+      <c r="I363" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A364" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B364" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C364" s="1">
+        <v>1</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E364" s="1">
+        <v>0</v>
+      </c>
+      <c r="F364" s="1">
         <v>31</v>
       </c>
-      <c r="E361" s="6">
-        <v>0</v>
-      </c>
-      <c r="F361" s="7">
-        <f>VLOOKUP(D361,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1103</v>
-      </c>
-      <c r="G361" s="6">
-        <v>8800</v>
-      </c>
-      <c r="H361" s="6">
-        <v>10</v>
-      </c>
-      <c r="I361" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A362" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B362" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C362" s="6">
-        <v>1</v>
-      </c>
-      <c r="D362" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E362" s="6">
-        <v>0</v>
-      </c>
-      <c r="F362" s="7">
-        <f>VLOOKUP(D362,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1105</v>
-      </c>
-      <c r="G362" s="6">
-        <v>8200</v>
-      </c>
-      <c r="H362" s="6">
-        <v>10</v>
-      </c>
-      <c r="I362" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A363" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B363" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C363" s="6">
-        <v>1</v>
-      </c>
-      <c r="D363" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E363" s="6">
-        <v>0</v>
-      </c>
-      <c r="F363" s="7">
-        <f>VLOOKUP(D363,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1106</v>
-      </c>
-      <c r="G363" s="6">
-        <v>7600</v>
-      </c>
-      <c r="H363" s="6">
-        <v>10</v>
-      </c>
-      <c r="I363" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A364" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B364" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C364" s="6">
-        <v>1</v>
-      </c>
-      <c r="D364" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E364" s="6">
-        <v>0</v>
-      </c>
-      <c r="F364" s="7">
-        <f>VLOOKUP(D364,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1109</v>
-      </c>
-      <c r="G364" s="6">
-        <v>7000</v>
-      </c>
-      <c r="H364" s="6">
-        <v>10</v>
-      </c>
-      <c r="I364" s="6">
-        <v>30</v>
+      <c r="G364" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H364" s="1">
+        <v>1</v>
+      </c>
+      <c r="I364" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A365" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B365" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C365" s="6">
-        <v>1</v>
-      </c>
-      <c r="D365" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E365" s="6">
-        <v>0</v>
-      </c>
-      <c r="F365" s="7">
-        <f>VLOOKUP(D365,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1110</v>
-      </c>
-      <c r="G365" s="6">
-        <v>6400</v>
-      </c>
-      <c r="H365" s="6">
-        <v>10</v>
-      </c>
-      <c r="I365" s="6">
-        <v>30</v>
+      <c r="A365" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B365" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C365" s="1">
+        <v>1</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E365" s="1">
+        <v>0</v>
+      </c>
+      <c r="F365" s="1">
+        <v>17</v>
+      </c>
+      <c r="G365" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H365" s="1">
+        <v>1</v>
+      </c>
+      <c r="I365" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A366" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B366" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C366" s="6">
-        <v>1</v>
-      </c>
-      <c r="D366" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E366" s="6">
-        <v>0</v>
-      </c>
-      <c r="F366" s="7">
-        <f>VLOOKUP(D366,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1111</v>
-      </c>
-      <c r="G366" s="6">
-        <v>5800</v>
-      </c>
-      <c r="H366" s="6">
-        <v>10</v>
-      </c>
-      <c r="I366" s="6">
-        <v>30</v>
+      <c r="A366" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B366" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C366" s="1">
+        <v>1</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E366" s="1">
+        <v>0</v>
+      </c>
+      <c r="F366" s="1">
+        <v>4</v>
+      </c>
+      <c r="G366" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H366" s="1">
+        <v>1</v>
+      </c>
+      <c r="I366" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A367" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B367" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C367" s="6">
-        <v>1</v>
-      </c>
-      <c r="D367" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E367" s="6">
-        <v>0</v>
-      </c>
-      <c r="F367" s="7">
-        <f>VLOOKUP(D367,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1112</v>
-      </c>
-      <c r="G367" s="6">
-        <v>5200</v>
-      </c>
-      <c r="H367" s="6">
-        <v>10</v>
-      </c>
-      <c r="I367" s="6">
-        <v>30</v>
+      <c r="A367" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B367" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C367" s="1">
+        <v>1</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E367" s="1">
+        <v>0</v>
+      </c>
+      <c r="F367" s="1">
+        <v>51</v>
+      </c>
+      <c r="G367" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H367" s="1">
+        <v>1</v>
+      </c>
+      <c r="I367" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A368" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B368" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C368" s="6">
-        <v>1</v>
-      </c>
-      <c r="D368" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E368" s="6">
-        <v>0</v>
-      </c>
-      <c r="F368" s="7">
-        <f>VLOOKUP(D368,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1113</v>
-      </c>
-      <c r="G368" s="6">
-        <v>4600</v>
-      </c>
-      <c r="H368" s="6">
-        <v>10</v>
-      </c>
-      <c r="I368" s="6">
-        <v>30</v>
+      <c r="A368" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B368" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C368" s="1">
+        <v>1</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E368" s="1">
+        <v>0</v>
+      </c>
+      <c r="F368" s="1">
+        <v>73</v>
+      </c>
+      <c r="G368" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H368" s="1">
+        <v>1</v>
+      </c>
+      <c r="I368" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A369" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B369" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C369" s="6">
-        <v>1</v>
-      </c>
-      <c r="D369" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E369" s="6">
-        <v>0</v>
-      </c>
-      <c r="F369" s="7">
-        <f>VLOOKUP(D369,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1114</v>
-      </c>
-      <c r="G369" s="6">
-        <v>4000</v>
-      </c>
-      <c r="H369" s="6">
-        <v>10</v>
-      </c>
-      <c r="I369" s="6">
-        <v>30</v>
+      <c r="A369" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B369" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C369" s="1">
+        <v>1</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E369" s="1">
+        <v>0</v>
+      </c>
+      <c r="F369" s="1">
+        <v>57</v>
+      </c>
+      <c r="G369" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H369" s="1">
+        <v>1</v>
+      </c>
+      <c r="I369" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A370" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B370" s="6">
-        <v>40000</v>
-      </c>
-      <c r="C370" s="6">
-        <v>1</v>
-      </c>
-      <c r="D370" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E370" s="6">
-        <v>0</v>
-      </c>
-      <c r="F370" s="7">
-        <f>VLOOKUP(D370,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1115</v>
-      </c>
-      <c r="G370" s="6">
-        <v>3400</v>
-      </c>
-      <c r="H370" s="6">
-        <v>10</v>
-      </c>
-      <c r="I370" s="6">
-        <v>30</v>
+      <c r="A370" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B370" s="1">
+        <v>30009</v>
+      </c>
+      <c r="C370" s="1">
+        <v>1</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E370" s="1">
+        <v>0</v>
+      </c>
+      <c r="F370" s="1">
+        <v>68</v>
+      </c>
+      <c r="G370" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H370" s="1">
+        <v>1</v>
+      </c>
+      <c r="I370" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.2">
@@ -14204,17 +14227,17 @@
         <v>1</v>
       </c>
       <c r="D371" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E371" s="6">
         <v>0</v>
       </c>
       <c r="F371" s="7">
         <f>VLOOKUP(D371,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1116</v>
+        <v>1100</v>
       </c>
       <c r="G371" s="6">
-        <v>2800</v>
+        <v>10000</v>
       </c>
       <c r="H371" s="6">
         <v>10</v>
@@ -14234,17 +14257,17 @@
         <v>1</v>
       </c>
       <c r="D372" s="6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E372" s="6">
         <v>0</v>
       </c>
       <c r="F372" s="7">
         <f>VLOOKUP(D372,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1117</v>
+        <v>1101</v>
       </c>
       <c r="G372" s="6">
-        <v>2200</v>
+        <v>9400</v>
       </c>
       <c r="H372" s="6">
         <v>10</v>
@@ -14254,417 +14277,417 @@
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A373" s="8" t="s">
+      <c r="A373" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B373" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C373" s="6">
+        <v>1</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E373" s="6">
+        <v>0</v>
+      </c>
+      <c r="F373" s="7">
+        <f>VLOOKUP(D373,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1103</v>
+      </c>
+      <c r="G373" s="6">
+        <v>8800</v>
+      </c>
+      <c r="H373" s="6">
+        <v>10</v>
+      </c>
+      <c r="I373" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A374" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B374" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C374" s="6">
+        <v>1</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E374" s="6">
+        <v>0</v>
+      </c>
+      <c r="F374" s="7">
+        <f>VLOOKUP(D374,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1105</v>
+      </c>
+      <c r="G374" s="6">
+        <v>8200</v>
+      </c>
+      <c r="H374" s="6">
+        <v>10</v>
+      </c>
+      <c r="I374" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A375" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B375" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C375" s="6">
+        <v>1</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E375" s="6">
+        <v>0</v>
+      </c>
+      <c r="F375" s="7">
+        <f>VLOOKUP(D375,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1106</v>
+      </c>
+      <c r="G375" s="6">
+        <v>7600</v>
+      </c>
+      <c r="H375" s="6">
+        <v>10</v>
+      </c>
+      <c r="I375" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A376" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B376" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C376" s="6">
+        <v>1</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E376" s="6">
+        <v>0</v>
+      </c>
+      <c r="F376" s="7">
+        <f>VLOOKUP(D376,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1109</v>
+      </c>
+      <c r="G376" s="6">
+        <v>7000</v>
+      </c>
+      <c r="H376" s="6">
+        <v>10</v>
+      </c>
+      <c r="I376" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A377" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B377" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C377" s="6">
+        <v>1</v>
+      </c>
+      <c r="D377" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E377" s="6">
+        <v>0</v>
+      </c>
+      <c r="F377" s="7">
+        <f>VLOOKUP(D377,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1110</v>
+      </c>
+      <c r="G377" s="6">
+        <v>6400</v>
+      </c>
+      <c r="H377" s="6">
+        <v>10</v>
+      </c>
+      <c r="I377" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A378" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B378" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C378" s="6">
+        <v>1</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E378" s="6">
+        <v>0</v>
+      </c>
+      <c r="F378" s="7">
+        <f>VLOOKUP(D378,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1111</v>
+      </c>
+      <c r="G378" s="6">
+        <v>5800</v>
+      </c>
+      <c r="H378" s="6">
+        <v>10</v>
+      </c>
+      <c r="I378" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A379" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B379" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C379" s="6">
+        <v>1</v>
+      </c>
+      <c r="D379" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E379" s="6">
+        <v>0</v>
+      </c>
+      <c r="F379" s="7">
+        <f>VLOOKUP(D379,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1112</v>
+      </c>
+      <c r="G379" s="6">
+        <v>5200</v>
+      </c>
+      <c r="H379" s="6">
+        <v>10</v>
+      </c>
+      <c r="I379" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A380" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B380" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C380" s="6">
+        <v>1</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E380" s="6">
+        <v>0</v>
+      </c>
+      <c r="F380" s="7">
+        <f>VLOOKUP(D380,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1113</v>
+      </c>
+      <c r="G380" s="6">
+        <v>4600</v>
+      </c>
+      <c r="H380" s="6">
+        <v>10</v>
+      </c>
+      <c r="I380" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A381" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B381" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C381" s="6">
+        <v>1</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E381" s="6">
+        <v>0</v>
+      </c>
+      <c r="F381" s="7">
+        <f>VLOOKUP(D381,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1114</v>
+      </c>
+      <c r="G381" s="6">
+        <v>4000</v>
+      </c>
+      <c r="H381" s="6">
+        <v>10</v>
+      </c>
+      <c r="I381" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A382" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B382" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C382" s="6">
+        <v>1</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E382" s="6">
+        <v>0</v>
+      </c>
+      <c r="F382" s="7">
+        <f>VLOOKUP(D382,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1115</v>
+      </c>
+      <c r="G382" s="6">
+        <v>3400</v>
+      </c>
+      <c r="H382" s="6">
+        <v>10</v>
+      </c>
+      <c r="I382" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A383" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B383" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C383" s="6">
+        <v>1</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E383" s="6">
+        <v>0</v>
+      </c>
+      <c r="F383" s="7">
+        <f>VLOOKUP(D383,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1116</v>
+      </c>
+      <c r="G383" s="6">
+        <v>2800</v>
+      </c>
+      <c r="H383" s="6">
+        <v>10</v>
+      </c>
+      <c r="I383" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A384" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B384" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C384" s="6">
+        <v>1</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E384" s="6">
+        <v>0</v>
+      </c>
+      <c r="F384" s="7">
+        <f>VLOOKUP(D384,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1117</v>
+      </c>
+      <c r="G384" s="6">
+        <v>2200</v>
+      </c>
+      <c r="H384" s="6">
+        <v>10</v>
+      </c>
+      <c r="I384" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A385" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B373" s="8">
+      <c r="B385" s="8">
         <v>40001</v>
       </c>
-      <c r="C373" s="8">
-        <v>1</v>
-      </c>
-      <c r="D373" s="8" t="s">
+      <c r="C385" s="8">
+        <v>1</v>
+      </c>
+      <c r="D385" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E373" s="8">
-        <v>0</v>
-      </c>
-      <c r="F373" s="9">
-        <f>VLOOKUP(D373,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E385" s="8">
+        <v>0</v>
+      </c>
+      <c r="F385" s="9">
+        <f>VLOOKUP(D385,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1009</v>
       </c>
-      <c r="G373" s="8">
+      <c r="G385" s="8">
         <v>8800</v>
       </c>
-      <c r="H373" s="8">
+      <c r="H385" s="8">
         <v>10</v>
       </c>
-      <c r="I373" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A374" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B374" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C374" s="8">
-        <v>1</v>
-      </c>
-      <c r="D374" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E374" s="8">
-        <v>0</v>
-      </c>
-      <c r="F374" s="9">
-        <f>VLOOKUP(D374,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1011</v>
-      </c>
-      <c r="G374" s="8">
-        <v>7600</v>
-      </c>
-      <c r="H374" s="8">
-        <v>10</v>
-      </c>
-      <c r="I374" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A375" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B375" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C375" s="8">
-        <v>1</v>
-      </c>
-      <c r="D375" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E375" s="8">
-        <v>0</v>
-      </c>
-      <c r="F375" s="9">
-        <f>VLOOKUP(D375,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1014</v>
-      </c>
-      <c r="G375" s="8">
-        <v>6400</v>
-      </c>
-      <c r="H375" s="8">
-        <v>10</v>
-      </c>
-      <c r="I375" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A376" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B376" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C376" s="8">
-        <v>1</v>
-      </c>
-      <c r="D376" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E376" s="8">
-        <v>0</v>
-      </c>
-      <c r="F376" s="9">
-        <f>VLOOKUP(D376,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1016</v>
-      </c>
-      <c r="G376" s="8">
-        <v>5200</v>
-      </c>
-      <c r="H376" s="8">
-        <v>10</v>
-      </c>
-      <c r="I376" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A377" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B377" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C377" s="8">
-        <v>1</v>
-      </c>
-      <c r="D377" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E377" s="8">
-        <v>0</v>
-      </c>
-      <c r="F377" s="9">
-        <f>VLOOKUP(D377,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1017</v>
-      </c>
-      <c r="G377" s="8">
-        <v>4000</v>
-      </c>
-      <c r="H377" s="8">
-        <v>10</v>
-      </c>
-      <c r="I377" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A378" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B378" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C378" s="8">
-        <v>1</v>
-      </c>
-      <c r="D378" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E378" s="8">
-        <v>0</v>
-      </c>
-      <c r="F378" s="9">
-        <f>VLOOKUP(D378,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1022</v>
-      </c>
-      <c r="G378" s="8">
-        <v>2800</v>
-      </c>
-      <c r="H378" s="8">
-        <v>10</v>
-      </c>
-      <c r="I378" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A379" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B379" s="8">
-        <v>40001</v>
-      </c>
-      <c r="C379" s="8">
-        <v>1</v>
-      </c>
-      <c r="D379" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E379" s="8">
-        <v>0</v>
-      </c>
-      <c r="F379" s="9">
-        <f>VLOOKUP(D379,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1024</v>
-      </c>
-      <c r="G379" s="8">
-        <v>1600</v>
-      </c>
-      <c r="H379" s="8">
-        <v>10</v>
-      </c>
-      <c r="I379" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="380" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A380" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B380" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C380" s="4">
-        <v>1</v>
-      </c>
-      <c r="D380" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E380" s="4">
-        <v>0</v>
-      </c>
-      <c r="F380" s="5">
-        <f>VLOOKUP(D380,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1000</v>
-      </c>
-      <c r="G380" s="4">
-        <v>10000</v>
-      </c>
-      <c r="H380" s="4">
-        <v>10</v>
-      </c>
-      <c r="I380" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A381" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B381" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C381" s="4">
-        <v>1</v>
-      </c>
-      <c r="D381" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E381" s="4">
-        <v>0</v>
-      </c>
-      <c r="F381" s="5">
-        <f>VLOOKUP(D381,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1010</v>
-      </c>
-      <c r="G381" s="4">
-        <v>7200</v>
-      </c>
-      <c r="H381" s="4">
-        <v>10</v>
-      </c>
-      <c r="I381" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A382" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B382" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C382" s="4">
-        <v>1</v>
-      </c>
-      <c r="D382" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E382" s="4">
-        <v>0</v>
-      </c>
-      <c r="F382" s="5">
-        <f>VLOOKUP(D382,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1013</v>
-      </c>
-      <c r="G382" s="4">
-        <v>5800</v>
-      </c>
-      <c r="H382" s="4">
-        <v>10</v>
-      </c>
-      <c r="I382" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A383" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B383" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C383" s="4">
-        <v>1</v>
-      </c>
-      <c r="D383" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E383" s="4">
-        <v>0</v>
-      </c>
-      <c r="F383" s="5">
-        <f>VLOOKUP(D383,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1018</v>
-      </c>
-      <c r="G383" s="4">
-        <v>4400</v>
-      </c>
-      <c r="H383" s="4">
-        <v>10</v>
-      </c>
-      <c r="I383" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A384" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B384" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C384" s="4">
-        <v>1</v>
-      </c>
-      <c r="D384" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E384" s="4">
-        <v>0</v>
-      </c>
-      <c r="F384" s="5">
-        <f>VLOOKUP(D384,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1020</v>
-      </c>
-      <c r="G384" s="4">
-        <v>3000</v>
-      </c>
-      <c r="H384" s="4">
-        <v>10</v>
-      </c>
-      <c r="I384" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A385" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B385" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C385" s="4">
-        <v>1</v>
-      </c>
-      <c r="D385" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E385" s="4">
-        <v>0</v>
-      </c>
-      <c r="F385" s="5">
-        <f>VLOOKUP(D385,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1023</v>
-      </c>
-      <c r="G385" s="4">
-        <v>1600</v>
-      </c>
-      <c r="H385" s="4">
-        <v>10</v>
-      </c>
-      <c r="I385" s="4">
+      <c r="I385" s="8">
         <v>30</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B386" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C386" s="8">
         <v>1</v>
       </c>
       <c r="D386" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E386" s="8">
         <v>0</v>
       </c>
       <c r="F386" s="9">
         <f>VLOOKUP(D386,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="G386" s="8">
-        <v>10000</v>
+        <v>7600</v>
       </c>
       <c r="H386" s="8">
         <v>10</v>
@@ -14675,26 +14698,26 @@
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B387" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C387" s="8">
         <v>1</v>
       </c>
       <c r="D387" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E387" s="8">
         <v>0</v>
       </c>
       <c r="F387" s="9">
         <f>VLOOKUP(D387,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="G387" s="8">
-        <v>8600</v>
+        <v>6400</v>
       </c>
       <c r="H387" s="8">
         <v>10</v>
@@ -14705,26 +14728,26 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B388" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C388" s="8">
         <v>1</v>
       </c>
       <c r="D388" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E388" s="8">
         <v>0</v>
       </c>
       <c r="F388" s="9">
         <f>VLOOKUP(D388,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="G388" s="8">
-        <v>7200</v>
+        <v>5200</v>
       </c>
       <c r="H388" s="8">
         <v>10</v>
@@ -14735,26 +14758,26 @@
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B389" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C389" s="8">
         <v>1</v>
       </c>
       <c r="D389" s="8" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E389" s="8">
         <v>0</v>
       </c>
       <c r="F389" s="9">
         <f>VLOOKUP(D389,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="G389" s="8">
-        <v>5800</v>
+        <v>4000</v>
       </c>
       <c r="H389" s="8">
         <v>10</v>
@@ -14765,26 +14788,26 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B390" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C390" s="8">
         <v>1</v>
       </c>
       <c r="D390" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E390" s="8">
         <v>0</v>
       </c>
       <c r="F390" s="9">
         <f>VLOOKUP(D390,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="G390" s="8">
-        <v>4400</v>
+        <v>2800</v>
       </c>
       <c r="H390" s="8">
         <v>10</v>
@@ -14795,26 +14818,26 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B391" s="8">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C391" s="8">
         <v>1</v>
       </c>
       <c r="D391" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E391" s="8">
         <v>0</v>
       </c>
       <c r="F391" s="9">
         <f>VLOOKUP(D391,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="G391" s="8">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="H391" s="8">
         <v>10</v>
@@ -14823,595 +14846,595 @@
         <v>30</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A392" s="8" t="s">
+    <row r="392" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A392" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B392" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C392" s="4">
+        <v>1</v>
+      </c>
+      <c r="D392" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E392" s="4">
+        <v>0</v>
+      </c>
+      <c r="F392" s="5">
+        <f>VLOOKUP(D392,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="G392" s="4">
+        <v>10000</v>
+      </c>
+      <c r="H392" s="4">
+        <v>10</v>
+      </c>
+      <c r="I392" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A393" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B393" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C393" s="4">
+        <v>1</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E393" s="4">
+        <v>0</v>
+      </c>
+      <c r="F393" s="5">
+        <f>VLOOKUP(D393,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
+      </c>
+      <c r="G393" s="4">
+        <v>7200</v>
+      </c>
+      <c r="H393" s="4">
+        <v>10</v>
+      </c>
+      <c r="I393" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A394" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B394" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C394" s="4">
+        <v>1</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E394" s="4">
+        <v>0</v>
+      </c>
+      <c r="F394" s="5">
+        <f>VLOOKUP(D394,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1013</v>
+      </c>
+      <c r="G394" s="4">
+        <v>5800</v>
+      </c>
+      <c r="H394" s="4">
+        <v>10</v>
+      </c>
+      <c r="I394" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A395" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B395" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C395" s="4">
+        <v>1</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E395" s="4">
+        <v>0</v>
+      </c>
+      <c r="F395" s="5">
+        <f>VLOOKUP(D395,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1018</v>
+      </c>
+      <c r="G395" s="4">
+        <v>4400</v>
+      </c>
+      <c r="H395" s="4">
+        <v>10</v>
+      </c>
+      <c r="I395" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A396" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B396" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C396" s="4">
+        <v>1</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E396" s="4">
+        <v>0</v>
+      </c>
+      <c r="F396" s="5">
+        <f>VLOOKUP(D396,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1020</v>
+      </c>
+      <c r="G396" s="4">
+        <v>3000</v>
+      </c>
+      <c r="H396" s="4">
+        <v>10</v>
+      </c>
+      <c r="I396" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A397" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B397" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C397" s="4">
+        <v>1</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E397" s="4">
+        <v>0</v>
+      </c>
+      <c r="F397" s="5">
+        <f>VLOOKUP(D397,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1023</v>
+      </c>
+      <c r="G397" s="4">
+        <v>1600</v>
+      </c>
+      <c r="H397" s="4">
+        <v>10</v>
+      </c>
+      <c r="I397" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A398" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B392" s="8">
+      <c r="B398" s="8">
         <v>40003</v>
       </c>
-      <c r="C392" s="8">
-        <v>1</v>
-      </c>
-      <c r="D392" s="8" t="s">
+      <c r="C398" s="8">
+        <v>1</v>
+      </c>
+      <c r="D398" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E398" s="8">
+        <v>0</v>
+      </c>
+      <c r="F398" s="9">
+        <f>VLOOKUP(D398,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="G398" s="8">
+        <v>10000</v>
+      </c>
+      <c r="H398" s="8">
+        <v>10</v>
+      </c>
+      <c r="I398" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A399" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B399" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C399" s="8">
+        <v>1</v>
+      </c>
+      <c r="D399" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E399" s="8">
+        <v>0</v>
+      </c>
+      <c r="F399" s="9">
+        <f>VLOOKUP(D399,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1009</v>
+      </c>
+      <c r="G399" s="8">
+        <v>8600</v>
+      </c>
+      <c r="H399" s="8">
+        <v>10</v>
+      </c>
+      <c r="I399" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A400" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B400" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C400" s="8">
+        <v>1</v>
+      </c>
+      <c r="D400" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E400" s="8">
+        <v>0</v>
+      </c>
+      <c r="F400" s="9">
+        <f>VLOOKUP(D400,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
+      </c>
+      <c r="G400" s="8">
+        <v>7200</v>
+      </c>
+      <c r="H400" s="8">
+        <v>10</v>
+      </c>
+      <c r="I400" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A401" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B401" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C401" s="8">
+        <v>1</v>
+      </c>
+      <c r="D401" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E401" s="8">
+        <v>0</v>
+      </c>
+      <c r="F401" s="9">
+        <f>VLOOKUP(D401,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
+      </c>
+      <c r="G401" s="8">
+        <v>5800</v>
+      </c>
+      <c r="H401" s="8">
+        <v>10</v>
+      </c>
+      <c r="I401" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A402" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B402" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C402" s="8">
+        <v>1</v>
+      </c>
+      <c r="D402" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E402" s="8">
+        <v>0</v>
+      </c>
+      <c r="F402" s="9">
+        <f>VLOOKUP(D402,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1014</v>
+      </c>
+      <c r="G402" s="8">
+        <v>4400</v>
+      </c>
+      <c r="H402" s="8">
+        <v>10</v>
+      </c>
+      <c r="I402" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A403" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B403" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C403" s="8">
+        <v>1</v>
+      </c>
+      <c r="D403" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E403" s="8">
+        <v>0</v>
+      </c>
+      <c r="F403" s="9">
+        <f>VLOOKUP(D403,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1017</v>
+      </c>
+      <c r="G403" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H403" s="8">
+        <v>10</v>
+      </c>
+      <c r="I403" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A404" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B404" s="8">
+        <v>40003</v>
+      </c>
+      <c r="C404" s="8">
+        <v>1</v>
+      </c>
+      <c r="D404" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E392" s="8">
-        <v>0</v>
-      </c>
-      <c r="F392" s="9">
-        <f>VLOOKUP(D392,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E404" s="8">
+        <v>0</v>
+      </c>
+      <c r="F404" s="9">
+        <f>VLOOKUP(D404,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1020</v>
       </c>
-      <c r="G392" s="8">
+      <c r="G404" s="8">
         <v>1600</v>
       </c>
-      <c r="H392" s="8">
+      <c r="H404" s="8">
         <v>10</v>
       </c>
-      <c r="I392" s="8">
+      <c r="I404" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A393" s="1" t="s">
+    <row r="405" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A405" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B393" s="1">
+      <c r="B405" s="1">
         <v>40004</v>
       </c>
-      <c r="C393" s="1">
-        <v>1</v>
-      </c>
-      <c r="D393" s="3" t="s">
+      <c r="C405" s="1">
+        <v>1</v>
+      </c>
+      <c r="D405" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E393" s="1">
-        <v>0</v>
-      </c>
-      <c r="F393">
-        <f>VLOOKUP(D393,Sheet1!$B$2:$C$35,2,FALSE)</f>
+      <c r="E405" s="1">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <f>VLOOKUP(D405,Sheet1!$B$2:$C$35,2,FALSE)</f>
         <v>1000</v>
       </c>
-      <c r="G393" s="1">
+      <c r="G405" s="1">
         <v>10000</v>
       </c>
-      <c r="H393" s="1">
+      <c r="H405" s="1">
         <v>10</v>
       </c>
-      <c r="I393" s="1">
+      <c r="I405" s="1">
         <v>30</v>
-      </c>
-    </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A394" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B394" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C394" s="1">
-        <v>1</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E394" s="1">
-        <v>0</v>
-      </c>
-      <c r="F394">
-        <f>VLOOKUP(D394,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1006</v>
-      </c>
-      <c r="G394" s="1">
-        <v>7200</v>
-      </c>
-      <c r="H394" s="1">
-        <v>10</v>
-      </c>
-      <c r="I394" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A395" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B395" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C395" s="1">
-        <v>1</v>
-      </c>
-      <c r="D395" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E395" s="1">
-        <v>0</v>
-      </c>
-      <c r="F395">
-        <f>VLOOKUP(D395,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1007</v>
-      </c>
-      <c r="G395" s="1">
-        <v>5800</v>
-      </c>
-      <c r="H395" s="1">
-        <v>10</v>
-      </c>
-      <c r="I395" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A396" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B396" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C396" s="1">
-        <v>1</v>
-      </c>
-      <c r="D396" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E396" s="1">
-        <v>0</v>
-      </c>
-      <c r="F396">
-        <f>VLOOKUP(D396,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1010</v>
-      </c>
-      <c r="G396" s="1">
-        <v>4400</v>
-      </c>
-      <c r="H396" s="1">
-        <v>10</v>
-      </c>
-      <c r="I396" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A397" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B397" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C397" s="1">
-        <v>1</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E397" s="1">
-        <v>0</v>
-      </c>
-      <c r="F397">
-        <f>VLOOKUP(D397,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1015</v>
-      </c>
-      <c r="G397" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H397" s="1">
-        <v>10</v>
-      </c>
-      <c r="I397" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A398" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B398" s="1">
-        <v>40004</v>
-      </c>
-      <c r="C398" s="1">
-        <v>1</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E398" s="1">
-        <v>0</v>
-      </c>
-      <c r="F398">
-        <f>VLOOKUP(D398,Sheet1!$B$2:$C$35,2,FALSE)</f>
-        <v>1021</v>
-      </c>
-      <c r="G398" s="1">
-        <v>1600</v>
-      </c>
-      <c r="H398" s="1">
-        <v>10</v>
-      </c>
-      <c r="I398" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A399" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B399" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C399" s="1">
-        <v>1</v>
-      </c>
-      <c r="D399" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E399" s="1">
-        <v>0</v>
-      </c>
-      <c r="F399" s="1">
-        <f>VLOOKUP(D399,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
-      </c>
-      <c r="G399" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H399" s="1">
-        <v>1</v>
-      </c>
-      <c r="I399" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A400" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B400" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C400" s="1">
-        <v>1</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E400" s="1">
-        <v>0</v>
-      </c>
-      <c r="F400" s="1">
-        <f>VLOOKUP(D400,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
-      </c>
-      <c r="G400" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H400" s="1">
-        <v>1</v>
-      </c>
-      <c r="I400" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A401" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B401" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C401" s="1">
-        <v>1</v>
-      </c>
-      <c r="D401" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E401" s="1">
-        <v>0</v>
-      </c>
-      <c r="F401" s="1">
-        <f>VLOOKUP(D401,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
-      </c>
-      <c r="G401" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H401" s="1">
-        <v>1</v>
-      </c>
-      <c r="I401" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A402" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B402" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C402" s="1">
-        <v>1</v>
-      </c>
-      <c r="D402" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E402" s="1">
-        <v>0</v>
-      </c>
-      <c r="F402" s="1">
-        <f>VLOOKUP(D402,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
-      </c>
-      <c r="G402" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H402" s="1">
-        <v>1</v>
-      </c>
-      <c r="I402" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A403" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B403" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C403" s="1">
-        <v>1</v>
-      </c>
-      <c r="D403" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E403" s="1">
-        <v>0</v>
-      </c>
-      <c r="F403" s="1">
-        <f>VLOOKUP(D403,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
-      </c>
-      <c r="G403" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H403" s="1">
-        <v>1</v>
-      </c>
-      <c r="I403" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A404" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B404" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C404" s="1">
-        <v>1</v>
-      </c>
-      <c r="D404" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E404" s="1">
-        <v>0</v>
-      </c>
-      <c r="F404" s="1">
-        <f>VLOOKUP(D404,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
-      </c>
-      <c r="G404" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H404" s="1">
-        <v>1</v>
-      </c>
-      <c r="I404" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A405" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B405" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C405" s="1">
-        <v>1</v>
-      </c>
-      <c r="D405" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E405" s="1">
-        <v>0</v>
-      </c>
-      <c r="F405" s="1">
-        <f>VLOOKUP(D405,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
-      </c>
-      <c r="G405" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H405" s="1">
-        <v>1</v>
-      </c>
-      <c r="I405" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>538</v>
+        <v>28</v>
       </c>
       <c r="B406" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C406" s="1">
         <v>1</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>535</v>
+        <v>58</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
       </c>
-      <c r="F406" s="1">
-        <f>VLOOKUP(D406,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+      <c r="F406">
+        <f>VLOOKUP(D406,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1006</v>
       </c>
       <c r="G406" s="1">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="H406" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I406" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>545</v>
+        <v>28</v>
       </c>
       <c r="B407" s="1">
-        <v>50000</v>
+        <v>40004</v>
       </c>
       <c r="C407" s="1">
         <v>1</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>536</v>
+        <v>59</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
       </c>
-      <c r="F407" s="1">
-        <f>VLOOKUP(D407,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+      <c r="F407">
+        <f>VLOOKUP(D407,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1007</v>
       </c>
       <c r="G407" s="1">
-        <v>1000</v>
+        <v>5800</v>
       </c>
       <c r="H407" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I407" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>546</v>
+        <v>28</v>
       </c>
       <c r="B408" s="1">
-        <v>50001</v>
+        <v>40004</v>
       </c>
       <c r="C408" s="1">
         <v>1</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>537</v>
+        <v>66</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
       </c>
-      <c r="F408" s="1">
-        <f>VLOOKUP(D408,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+      <c r="F408">
+        <f>VLOOKUP(D408,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1010</v>
       </c>
       <c r="G408" s="1">
-        <v>1000</v>
+        <v>4400</v>
       </c>
       <c r="H408" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I408" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>546</v>
+        <v>28</v>
       </c>
       <c r="B409" s="1">
-        <v>50001</v>
+        <v>40004</v>
       </c>
       <c r="C409" s="1">
         <v>1</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>530</v>
+        <v>60</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
       </c>
-      <c r="F409" s="1">
-        <f>VLOOKUP(D409,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
+      <c r="F409">
+        <f>VLOOKUP(D409,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1015</v>
       </c>
       <c r="G409" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H409" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I409" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>546</v>
+        <v>28</v>
       </c>
       <c r="B410" s="1">
-        <v>50001</v>
+        <v>40004</v>
       </c>
       <c r="C410" s="1">
         <v>1</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>531</v>
+        <v>61</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
       </c>
-      <c r="F410" s="1">
-        <f>VLOOKUP(D410,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+      <c r="F410">
+        <f>VLOOKUP(D410,Sheet1!$B$2:$C$35,2,FALSE)</f>
+        <v>1021</v>
       </c>
       <c r="G410" s="1">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H410" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I410" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B411" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C411" s="1">
         <v>1</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
       </c>
       <c r="F411" s="1">
         <f>VLOOKUP(D411,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
+        <v>5006</v>
       </c>
       <c r="G411" s="1">
         <v>1000</v>
@@ -15425,23 +15448,23 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B412" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C412" s="1">
         <v>1</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
       </c>
       <c r="F412" s="1">
         <f>VLOOKUP(D412,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
+        <v>5007</v>
       </c>
       <c r="G412" s="1">
         <v>1000</v>
@@ -15455,23 +15478,23 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B413" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C413" s="1">
         <v>1</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
       </c>
       <c r="F413" s="1">
         <f>VLOOKUP(D413,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5016</v>
       </c>
       <c r="G413" s="1">
         <v>1000</v>
@@ -15485,23 +15508,23 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B414" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C414" s="1">
         <v>1</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
       </c>
       <c r="F414" s="1">
         <f>VLOOKUP(D414,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5017</v>
       </c>
       <c r="G414" s="1">
         <v>1000</v>
@@ -15515,23 +15538,23 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B415" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C415" s="1">
         <v>1</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
       </c>
       <c r="F415" s="1">
         <f>VLOOKUP(D415,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5008</v>
+        <v>5020</v>
       </c>
       <c r="G415" s="1">
         <v>1000</v>
@@ -15545,23 +15568,23 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B416" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C416" s="1">
         <v>1</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
       </c>
       <c r="F416" s="1">
         <f>VLOOKUP(D416,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5009</v>
+        <v>5022</v>
       </c>
       <c r="G416" s="1">
         <v>1000</v>
@@ -15575,23 +15598,23 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B417" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C417" s="1">
         <v>1</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
       </c>
       <c r="F417" s="1">
         <f>VLOOKUP(D417,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5025</v>
+        <v>5019</v>
       </c>
       <c r="G417" s="1">
         <v>1000</v>
@@ -15605,23 +15628,23 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B418" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C418" s="1">
         <v>1</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
       </c>
       <c r="F418" s="1">
         <f>VLOOKUP(D418,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5026</v>
+        <v>5015</v>
       </c>
       <c r="G418" s="1">
         <v>1000</v>
@@ -15635,23 +15658,23 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B419" s="1">
-        <v>50001</v>
+        <v>50000</v>
       </c>
       <c r="C419" s="1">
         <v>1</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
       </c>
       <c r="F419" s="1">
         <f>VLOOKUP(D419,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5031</v>
+        <v>5024</v>
       </c>
       <c r="G419" s="1">
         <v>1000</v>
@@ -15674,14 +15697,14 @@
         <v>1</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
       </c>
       <c r="F420" s="1">
         <f>VLOOKUP(D420,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5032</v>
+        <v>5006</v>
       </c>
       <c r="G420" s="1">
         <v>1000</v>
@@ -15695,23 +15718,23 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B421" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C421" s="1">
         <v>1</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
       </c>
       <c r="F421" s="1">
         <f>VLOOKUP(D421,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5016</v>
       </c>
       <c r="G421" s="1">
         <v>1000</v>
@@ -15725,23 +15748,23 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B422" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C422" s="1">
         <v>1</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
       </c>
       <c r="F422" s="1">
         <f>VLOOKUP(D422,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5004</v>
+        <v>5017</v>
       </c>
       <c r="G422" s="1">
         <v>1000</v>
@@ -15755,23 +15778,23 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B423" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C423" s="1">
         <v>1</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
       </c>
       <c r="F423" s="1">
         <f>VLOOKUP(D423,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5005</v>
+        <v>5020</v>
       </c>
       <c r="G423" s="1">
         <v>1000</v>
@@ -15785,23 +15808,23 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B424" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C424" s="1">
         <v>1</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
       </c>
       <c r="F424" s="1">
         <f>VLOOKUP(D424,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5012</v>
+        <v>5022</v>
       </c>
       <c r="G424" s="1">
         <v>1000</v>
@@ -15815,10 +15838,10 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B425" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C425" s="1">
         <v>1</v>
@@ -15845,10 +15868,10 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B426" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C426" s="1">
         <v>1</v>
@@ -15875,10 +15898,10 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B427" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C427" s="1">
         <v>1</v>
@@ -15905,10 +15928,10 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B428" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C428" s="1">
         <v>1</v>
@@ -15935,10 +15958,10 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B429" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C429" s="1">
         <v>1</v>
@@ -15965,10 +15988,10 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B430" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C430" s="1">
         <v>1</v>
@@ -15995,10 +16018,10 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B431" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C431" s="1">
         <v>1</v>
@@ -16025,10 +16048,10 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B432" s="1">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C432" s="1">
         <v>1</v>
@@ -16064,14 +16087,14 @@
         <v>1</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
       </c>
       <c r="F433" s="1">
         <f>VLOOKUP(D433,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5006</v>
       </c>
       <c r="G433" s="1">
         <v>1000</v>
@@ -16085,23 +16108,23 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B434" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C434" s="1">
         <v>1</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
       </c>
       <c r="F434" s="1">
         <f>VLOOKUP(D434,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5004</v>
       </c>
       <c r="G434" s="1">
         <v>1000</v>
@@ -16115,23 +16138,23 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B435" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C435" s="1">
         <v>1</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
       </c>
       <c r="F435" s="1">
         <f>VLOOKUP(D435,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5005</v>
       </c>
       <c r="G435" s="1">
         <v>1000</v>
@@ -16145,23 +16168,23 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B436" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C436" s="1">
         <v>1</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
       </c>
       <c r="F436" s="1">
         <f>VLOOKUP(D436,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5012</v>
       </c>
       <c r="G436" s="1">
         <v>1000</v>
@@ -16175,23 +16198,23 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B437" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C437" s="1">
         <v>1</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
       </c>
       <c r="F437" s="1">
         <f>VLOOKUP(D437,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5015</v>
       </c>
       <c r="G437" s="1">
         <v>1000</v>
@@ -16205,23 +16228,23 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B438" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C438" s="1">
         <v>1</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
       </c>
       <c r="F438" s="1">
         <f>VLOOKUP(D438,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5024</v>
       </c>
       <c r="G438" s="1">
         <v>1000</v>
@@ -16235,23 +16258,23 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B439" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C439" s="1">
         <v>1</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
       </c>
       <c r="F439" s="1">
         <f>VLOOKUP(D439,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5008</v>
       </c>
       <c r="G439" s="1">
         <v>1000</v>
@@ -16265,23 +16288,23 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B440" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C440" s="1">
         <v>1</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
       </c>
       <c r="F440" s="1">
         <f>VLOOKUP(D440,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5009</v>
       </c>
       <c r="G440" s="1">
         <v>1000</v>
@@ -16295,23 +16318,23 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B441" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C441" s="1">
         <v>1</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
       </c>
       <c r="F441" s="1">
         <f>VLOOKUP(D441,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5025</v>
       </c>
       <c r="G441" s="1">
         <v>1000</v>
@@ -16325,23 +16348,23 @@
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B442" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C442" s="1">
         <v>1</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
       </c>
       <c r="F442" s="1">
         <f>VLOOKUP(D442,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5026</v>
       </c>
       <c r="G442" s="1">
         <v>1000</v>
@@ -16355,23 +16378,23 @@
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B443" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C443" s="1">
         <v>1</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
       </c>
       <c r="F443" s="1">
         <f>VLOOKUP(D443,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
+        <v>5031</v>
       </c>
       <c r="G443" s="1">
         <v>1000</v>
@@ -16385,23 +16408,23 @@
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B444" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C444" s="1">
         <v>1</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
       </c>
       <c r="F444" s="1">
         <f>VLOOKUP(D444,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5032</v>
       </c>
       <c r="G444" s="1">
         <v>1000</v>
@@ -16415,10 +16438,10 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B445" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C445" s="1">
         <v>1</v>
@@ -16445,23 +16468,23 @@
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B446" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C446" s="1">
         <v>1</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
       </c>
       <c r="F446" s="1">
         <f>VLOOKUP(D446,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5006</v>
       </c>
       <c r="G446" s="1">
         <v>1000</v>
@@ -16475,23 +16498,23 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B447" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C447" s="1">
         <v>1</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
       </c>
       <c r="F447" s="1">
         <f>VLOOKUP(D447,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5001</v>
       </c>
       <c r="G447" s="1">
         <v>1000</v>
@@ -16505,23 +16528,23 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B448" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C448" s="1">
         <v>1</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
       </c>
       <c r="F448" s="1">
         <f>VLOOKUP(D448,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5014</v>
       </c>
       <c r="G448" s="1">
         <v>1000</v>
@@ -16535,23 +16558,23 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B449" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C449" s="1">
         <v>1</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
       </c>
       <c r="F449" s="1">
         <f>VLOOKUP(D449,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="G449" s="1">
         <v>1000</v>
@@ -16565,23 +16588,23 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B450" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C450" s="1">
         <v>1</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
       </c>
       <c r="F450" s="1">
         <f>VLOOKUP(D450,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5003</v>
       </c>
       <c r="G450" s="1">
         <v>1000</v>
@@ -16595,23 +16618,23 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B451" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C451" s="1">
         <v>1</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
       </c>
       <c r="F451" s="1">
         <f>VLOOKUP(D451,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5018</v>
       </c>
       <c r="G451" s="1">
         <v>1000</v>
@@ -16625,23 +16648,23 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B452" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C452" s="1">
         <v>1</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
       </c>
       <c r="F452" s="1">
         <f>VLOOKUP(D452,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5027</v>
       </c>
       <c r="G452" s="1">
         <v>1000</v>
@@ -16655,23 +16678,23 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B453" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C453" s="1">
         <v>1</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E453" s="1">
         <v>0</v>
       </c>
       <c r="F453" s="1">
         <f>VLOOKUP(D453,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5028</v>
       </c>
       <c r="G453" s="1">
         <v>1000</v>
@@ -16685,23 +16708,23 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B454" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C454" s="1">
         <v>1</v>
       </c>
-      <c r="D454" t="s">
-        <v>553</v>
+      <c r="D454" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
       </c>
       <c r="F454" s="1">
         <f>VLOOKUP(D454,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5029</v>
       </c>
       <c r="G454" s="1">
         <v>1000</v>
@@ -16715,23 +16738,23 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B455" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C455" s="1">
         <v>1</v>
       </c>
-      <c r="D455" t="s">
-        <v>554</v>
+      <c r="D455" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="E455" s="1">
         <v>0</v>
       </c>
       <c r="F455" s="1">
         <f>VLOOKUP(D455,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5007</v>
       </c>
       <c r="G455" s="1">
         <v>1000</v>
@@ -16745,23 +16768,23 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B456" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C456" s="1">
         <v>1</v>
       </c>
-      <c r="D456" t="s">
-        <v>555</v>
+      <c r="D456" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
       </c>
       <c r="F456" s="1">
         <f>VLOOKUP(D456,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5017</v>
       </c>
       <c r="G456" s="1">
         <v>1000</v>
@@ -16775,23 +16798,23 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B457" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C457" s="1">
         <v>1</v>
       </c>
-      <c r="D457" t="s">
-        <v>556</v>
+      <c r="D457" s="1" t="s">
+        <v>534</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
       </c>
       <c r="F457" s="1">
         <f>VLOOKUP(D457,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5019</v>
       </c>
       <c r="G457" s="1">
         <v>1000</v>
@@ -16805,23 +16828,23 @@
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B458" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C458" s="1">
         <v>1</v>
       </c>
-      <c r="D458" t="s">
-        <v>557</v>
+      <c r="D458" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
       </c>
       <c r="F458" s="1">
         <f>VLOOKUP(D458,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5001</v>
       </c>
       <c r="G458" s="1">
         <v>1000</v>
@@ -16835,23 +16858,23 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B459" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C459" s="1">
         <v>1</v>
       </c>
-      <c r="D459" t="s">
-        <v>558</v>
+      <c r="D459" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
       </c>
       <c r="F459" s="1">
         <f>VLOOKUP(D459,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5014</v>
       </c>
       <c r="G459" s="1">
         <v>1000</v>
@@ -16863,9 +16886,369 @@
         <v>1</v>
       </c>
     </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A460" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B460" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C460" s="1">
+        <v>1</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E460" s="1">
+        <v>0</v>
+      </c>
+      <c r="F460" s="1">
+        <f>VLOOKUP(D460,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G460" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H460" s="1">
+        <v>1</v>
+      </c>
+      <c r="I460" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A461" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B461" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C461" s="1">
+        <v>1</v>
+      </c>
+      <c r="D461" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E461" s="1">
+        <v>0</v>
+      </c>
+      <c r="F461" s="1">
+        <f>VLOOKUP(D461,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G461" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H461" s="1">
+        <v>1</v>
+      </c>
+      <c r="I461" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A462" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B462" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C462" s="1">
+        <v>1</v>
+      </c>
+      <c r="D462" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E462" s="1">
+        <v>0</v>
+      </c>
+      <c r="F462" s="1">
+        <f>VLOOKUP(D462,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G462" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H462" s="1">
+        <v>1</v>
+      </c>
+      <c r="I462" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A463" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B463" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C463" s="1">
+        <v>1</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E463" s="1">
+        <v>0</v>
+      </c>
+      <c r="F463" s="1">
+        <f>VLOOKUP(D463,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G463" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H463" s="1">
+        <v>1</v>
+      </c>
+      <c r="I463" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A464" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B464" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C464" s="1">
+        <v>1</v>
+      </c>
+      <c r="D464" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E464" s="1">
+        <v>0</v>
+      </c>
+      <c r="F464" s="1">
+        <f>VLOOKUP(D464,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G464" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H464" s="1">
+        <v>1</v>
+      </c>
+      <c r="I464" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A465" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B465" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C465" s="1">
+        <v>1</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E465" s="1">
+        <v>0</v>
+      </c>
+      <c r="F465" s="1">
+        <f>VLOOKUP(D465,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G465" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H465" s="1">
+        <v>1</v>
+      </c>
+      <c r="I465" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A466" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B466" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C466" s="1">
+        <v>1</v>
+      </c>
+      <c r="D466" t="s">
+        <v>553</v>
+      </c>
+      <c r="E466" s="1">
+        <v>0</v>
+      </c>
+      <c r="F466" s="1">
+        <f>VLOOKUP(D466,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G466" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H466" s="1">
+        <v>1</v>
+      </c>
+      <c r="I466" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A467" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B467" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C467" s="1">
+        <v>1</v>
+      </c>
+      <c r="D467" t="s">
+        <v>554</v>
+      </c>
+      <c r="E467" s="1">
+        <v>0</v>
+      </c>
+      <c r="F467" s="1">
+        <f>VLOOKUP(D467,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G467" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H467" s="1">
+        <v>1</v>
+      </c>
+      <c r="I467" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A468" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B468" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C468" s="1">
+        <v>1</v>
+      </c>
+      <c r="D468" t="s">
+        <v>555</v>
+      </c>
+      <c r="E468" s="1">
+        <v>0</v>
+      </c>
+      <c r="F468" s="1">
+        <f>VLOOKUP(D468,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G468" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H468" s="1">
+        <v>1</v>
+      </c>
+      <c r="I468" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A469" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B469" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C469" s="1">
+        <v>1</v>
+      </c>
+      <c r="D469" t="s">
+        <v>556</v>
+      </c>
+      <c r="E469" s="1">
+        <v>0</v>
+      </c>
+      <c r="F469" s="1">
+        <f>VLOOKUP(D469,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G469" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H469" s="1">
+        <v>1</v>
+      </c>
+      <c r="I469" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A470" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B470" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C470" s="1">
+        <v>1</v>
+      </c>
+      <c r="D470" t="s">
+        <v>557</v>
+      </c>
+      <c r="E470" s="1">
+        <v>0</v>
+      </c>
+      <c r="F470" s="1">
+        <f>VLOOKUP(D470,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G470" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H470" s="1">
+        <v>1</v>
+      </c>
+      <c r="I470" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A471" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B471" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C471" s="1">
+        <v>1</v>
+      </c>
+      <c r="D471" t="s">
+        <v>558</v>
+      </c>
+      <c r="E471" s="1">
+        <v>0</v>
+      </c>
+      <c r="F471" s="1">
+        <f>VLOOKUP(D471,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G471" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H471" s="1">
+        <v>1</v>
+      </c>
+      <c r="I471" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:I3">
-    <sortState ref="A4:I389">
+    <sortState ref="A4:I471">
       <sortCondition ref="B3"/>
     </sortState>
   </autoFilter>
@@ -23462,6 +23845,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="605">
   <si>
     <t>text</t>
   </si>
@@ -1877,27 +1877,6 @@
     <t>魔族法师</t>
   </si>
   <si>
-    <t>魔族娃娃</t>
-  </si>
-  <si>
-    <t>女鬼</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>小精灵黄</t>
-  </si>
-  <si>
-    <t>邪恶法师</t>
-  </si>
-  <si>
-    <t>幽灵战士</t>
-  </si>
-  <si>
     <t>购买失败表情</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1975,6 +1954,24 @@
   </si>
   <si>
     <t>翻书</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>路人男</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+  </si>
+  <si>
+    <t>中年路人男</t>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
   </si>
 </sst>
 </file>
@@ -2010,7 +2007,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2041,6 +2038,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2054,7 +2057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2089,6 +2092,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3551,7 +3555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I471"/>
+  <dimension ref="A1:I485"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -12428,7 +12432,7 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E307" s="1">
         <v>0</v>
@@ -12544,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -12863,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E322" s="1">
         <v>0</v>
@@ -13580,7 +13584,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B349" s="1">
         <v>30006</v>
@@ -13589,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="E349" s="1">
         <v>0</v>
@@ -13609,7 +13613,7 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B350" s="1">
         <v>30006</v>
@@ -13618,7 +13622,7 @@
         <v>1</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="E350" s="1">
         <v>0</v>
@@ -13638,7 +13642,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B351" s="1">
         <v>30006</v>
@@ -13667,7 +13671,7 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B352" s="1">
         <v>30006</v>
@@ -13676,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E352" s="1">
         <v>0</v>
@@ -13696,7 +13700,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B353" s="1">
         <v>30006</v>
@@ -13705,7 +13709,7 @@
         <v>1</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E353" s="1">
         <v>0</v>
@@ -13725,7 +13729,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B354" s="1">
         <v>30007</v>
@@ -13734,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E354" s="1">
         <v>0</v>
@@ -13754,7 +13758,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B355" s="1">
         <v>30007</v>
@@ -13763,7 +13767,7 @@
         <v>1</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E355" s="1">
         <v>0</v>
@@ -13783,7 +13787,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B356" s="1">
         <v>30007</v>
@@ -13792,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E356" s="1">
         <v>0</v>
@@ -13812,7 +13816,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B357" s="1">
         <v>30007</v>
@@ -13841,7 +13845,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B358" s="1">
         <v>30007</v>
@@ -13870,7 +13874,7 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B359" s="1">
         <v>30008</v>
@@ -13879,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E359" s="1">
         <v>0</v>
@@ -13899,7 +13903,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B360" s="1">
         <v>30008</v>
@@ -13908,7 +13912,7 @@
         <v>1</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E360" s="1">
         <v>0</v>
@@ -13928,7 +13932,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B361" s="1">
         <v>30008</v>
@@ -13937,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E361" s="1">
         <v>0</v>
@@ -13957,7 +13961,7 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B362" s="1">
         <v>30008</v>
@@ -13966,7 +13970,7 @@
         <v>1</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E362" s="1">
         <v>0</v>
@@ -13986,7 +13990,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B363" s="1">
         <v>30008</v>
@@ -13995,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E363" s="1">
         <v>0</v>
@@ -14015,7 +14019,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B364" s="1">
         <v>30009</v>
@@ -14024,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E364" s="1">
         <v>0</v>
@@ -14044,7 +14048,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B365" s="1">
         <v>30009</v>
@@ -14053,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E365" s="1">
         <v>0</v>
@@ -14073,7 +14077,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B366" s="1">
         <v>30009</v>
@@ -14082,7 +14086,7 @@
         <v>1</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E366" s="1">
         <v>0</v>
@@ -14102,7 +14106,7 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B367" s="1">
         <v>30009</v>
@@ -14111,7 +14115,7 @@
         <v>1</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E367" s="1">
         <v>0</v>
@@ -14131,7 +14135,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B368" s="1">
         <v>30009</v>
@@ -14140,7 +14144,7 @@
         <v>1</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -14160,7 +14164,7 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B369" s="1">
         <v>30009</v>
@@ -14169,7 +14173,7 @@
         <v>1</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E369" s="1">
         <v>0</v>
@@ -14189,7 +14193,7 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B370" s="1">
         <v>30009</v>
@@ -14198,7 +14202,7 @@
         <v>1</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="E370" s="1">
         <v>0</v>
@@ -15457,14 +15461,14 @@
         <v>1</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
       </c>
       <c r="F412" s="1">
         <f>VLOOKUP(D412,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
+        <v>5016</v>
       </c>
       <c r="G412" s="1">
         <v>1000</v>
@@ -15487,14 +15491,14 @@
         <v>1</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
       </c>
       <c r="F413" s="1">
         <f>VLOOKUP(D413,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
+        <v>5017</v>
       </c>
       <c r="G413" s="1">
         <v>1000</v>
@@ -15517,14 +15521,14 @@
         <v>1</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
       </c>
       <c r="F414" s="1">
         <f>VLOOKUP(D414,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5020</v>
       </c>
       <c r="G414" s="1">
         <v>1000</v>
@@ -15547,14 +15551,14 @@
         <v>1</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
       </c>
       <c r="F415" s="1">
         <f>VLOOKUP(D415,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
+        <v>5022</v>
       </c>
       <c r="G415" s="1">
         <v>1000</v>
@@ -15577,14 +15581,14 @@
         <v>1</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
       </c>
       <c r="F416" s="1">
         <f>VLOOKUP(D416,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
+        <v>5019</v>
       </c>
       <c r="G416" s="1">
         <v>1000</v>
@@ -15606,15 +15610,15 @@
       <c r="C417" s="1">
         <v>1</v>
       </c>
-      <c r="D417" s="1" t="s">
-        <v>534</v>
+      <c r="D417" t="s">
+        <v>599</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
       </c>
       <c r="F417" s="1">
         <f>VLOOKUP(D417,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5206</v>
       </c>
       <c r="G417" s="1">
         <v>1000</v>
@@ -15628,7 +15632,7 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B418" s="1">
         <v>50000</v>
@@ -15636,15 +15640,15 @@
       <c r="C418" s="1">
         <v>1</v>
       </c>
-      <c r="D418" s="1" t="s">
-        <v>535</v>
+      <c r="D418" t="s">
+        <v>600</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
       </c>
       <c r="F418" s="1">
         <f>VLOOKUP(D418,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5207</v>
       </c>
       <c r="G418" s="1">
         <v>1000</v>
@@ -15658,23 +15662,23 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B419" s="1">
-        <v>50000</v>
+        <v>50001</v>
       </c>
       <c r="C419" s="1">
         <v>1</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
       </c>
       <c r="F419" s="1">
         <f>VLOOKUP(D419,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5006</v>
       </c>
       <c r="G419" s="1">
         <v>1000</v>
@@ -15697,14 +15701,14 @@
         <v>1</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
       </c>
       <c r="F420" s="1">
         <f>VLOOKUP(D420,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5016</v>
       </c>
       <c r="G420" s="1">
         <v>1000</v>
@@ -15727,14 +15731,14 @@
         <v>1</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
       </c>
       <c r="F421" s="1">
         <f>VLOOKUP(D421,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5016</v>
+        <v>5017</v>
       </c>
       <c r="G421" s="1">
         <v>1000</v>
@@ -15757,14 +15761,14 @@
         <v>1</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
       </c>
       <c r="F422" s="1">
         <f>VLOOKUP(D422,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5020</v>
       </c>
       <c r="G422" s="1">
         <v>1000</v>
@@ -15787,14 +15791,14 @@
         <v>1</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
       </c>
       <c r="F423" s="1">
         <f>VLOOKUP(D423,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5020</v>
+        <v>5022</v>
       </c>
       <c r="G423" s="1">
         <v>1000</v>
@@ -15817,14 +15821,14 @@
         <v>1</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
       </c>
       <c r="F424" s="1">
         <f>VLOOKUP(D424,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5022</v>
+        <v>5015</v>
       </c>
       <c r="G424" s="1">
         <v>1000</v>
@@ -15847,14 +15851,14 @@
         <v>1</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
       </c>
       <c r="F425" s="1">
         <f>VLOOKUP(D425,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5024</v>
       </c>
       <c r="G425" s="1">
         <v>1000</v>
@@ -15877,14 +15881,14 @@
         <v>1</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
       </c>
       <c r="F426" s="1">
         <f>VLOOKUP(D426,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5008</v>
       </c>
       <c r="G426" s="1">
         <v>1000</v>
@@ -15907,14 +15911,14 @@
         <v>1</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
       </c>
       <c r="F427" s="1">
         <f>VLOOKUP(D427,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5008</v>
+        <v>5009</v>
       </c>
       <c r="G427" s="1">
         <v>1000</v>
@@ -15936,15 +15940,15 @@
       <c r="C428" s="1">
         <v>1</v>
       </c>
-      <c r="D428" s="1" t="s">
-        <v>540</v>
+      <c r="D428" s="14" t="s">
+        <v>601</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
       </c>
       <c r="F428" s="1">
         <f>VLOOKUP(D428,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5009</v>
+        <v>5203</v>
       </c>
       <c r="G428" s="1">
         <v>1000</v>
@@ -15966,15 +15970,15 @@
       <c r="C429" s="1">
         <v>1</v>
       </c>
-      <c r="D429" s="1" t="s">
-        <v>541</v>
+      <c r="D429" s="14" t="s">
+        <v>602</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
       </c>
       <c r="F429" s="1">
         <f>VLOOKUP(D429,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5025</v>
+        <v>5204</v>
       </c>
       <c r="G429" s="1">
         <v>1000</v>
@@ -15996,15 +16000,15 @@
       <c r="C430" s="1">
         <v>1</v>
       </c>
-      <c r="D430" s="1" t="s">
-        <v>542</v>
+      <c r="D430" s="14" t="s">
+        <v>599</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
       </c>
       <c r="F430" s="1">
         <f>VLOOKUP(D430,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5026</v>
+        <v>5206</v>
       </c>
       <c r="G430" s="1">
         <v>1000</v>
@@ -16026,15 +16030,15 @@
       <c r="C431" s="1">
         <v>1</v>
       </c>
-      <c r="D431" s="1" t="s">
-        <v>543</v>
+      <c r="D431" s="14" t="s">
+        <v>600</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
       </c>
       <c r="F431" s="1">
         <f>VLOOKUP(D431,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5031</v>
+        <v>5207</v>
       </c>
       <c r="G431" s="1">
         <v>1000</v>
@@ -16048,23 +16052,23 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B432" s="1">
-        <v>50001</v>
+        <v>50002</v>
       </c>
       <c r="C432" s="1">
         <v>1</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
       </c>
       <c r="F432" s="1">
         <f>VLOOKUP(D432,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5032</v>
+        <v>5006</v>
       </c>
       <c r="G432" s="1">
         <v>1000</v>
@@ -16087,14 +16091,14 @@
         <v>1</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
       </c>
       <c r="F433" s="1">
         <f>VLOOKUP(D433,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5004</v>
       </c>
       <c r="G433" s="1">
         <v>1000</v>
@@ -16117,14 +16121,14 @@
         <v>1</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
       </c>
       <c r="F434" s="1">
         <f>VLOOKUP(D434,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5004</v>
+        <v>5005</v>
       </c>
       <c r="G434" s="1">
         <v>1000</v>
@@ -16147,14 +16151,14 @@
         <v>1</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
       </c>
       <c r="F435" s="1">
         <f>VLOOKUP(D435,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5005</v>
+        <v>5012</v>
       </c>
       <c r="G435" s="1">
         <v>1000</v>
@@ -16177,14 +16181,14 @@
         <v>1</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
       </c>
       <c r="F436" s="1">
         <f>VLOOKUP(D436,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5012</v>
+        <v>5015</v>
       </c>
       <c r="G436" s="1">
         <v>1000</v>
@@ -16207,14 +16211,14 @@
         <v>1</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
       </c>
       <c r="F437" s="1">
         <f>VLOOKUP(D437,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5015</v>
+        <v>5024</v>
       </c>
       <c r="G437" s="1">
         <v>1000</v>
@@ -16237,14 +16241,14 @@
         <v>1</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
       </c>
       <c r="F438" s="1">
         <f>VLOOKUP(D438,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5024</v>
+        <v>5008</v>
       </c>
       <c r="G438" s="1">
         <v>1000</v>
@@ -16267,14 +16271,14 @@
         <v>1</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
       </c>
       <c r="F439" s="1">
         <f>VLOOKUP(D439,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5008</v>
+        <v>5009</v>
       </c>
       <c r="G439" s="1">
         <v>1000</v>
@@ -16297,14 +16301,14 @@
         <v>1</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
       </c>
       <c r="F440" s="1">
         <f>VLOOKUP(D440,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5009</v>
+        <v>5025</v>
       </c>
       <c r="G440" s="1">
         <v>1000</v>
@@ -16327,14 +16331,14 @@
         <v>1</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
       </c>
       <c r="F441" s="1">
         <f>VLOOKUP(D441,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="G441" s="1">
         <v>1000</v>
@@ -16356,15 +16360,15 @@
       <c r="C442" s="1">
         <v>1</v>
       </c>
-      <c r="D442" s="1" t="s">
-        <v>542</v>
+      <c r="D442" s="14" t="s">
+        <v>603</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
       </c>
       <c r="F442" s="1">
         <f>VLOOKUP(D442,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5026</v>
+        <v>5205</v>
       </c>
       <c r="G442" s="1">
         <v>1000</v>
@@ -16386,15 +16390,15 @@
       <c r="C443" s="1">
         <v>1</v>
       </c>
-      <c r="D443" s="1" t="s">
-        <v>543</v>
+      <c r="D443" s="14" t="s">
+        <v>604</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
       </c>
       <c r="F443" s="1">
         <f>VLOOKUP(D443,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5031</v>
+        <v>5208</v>
       </c>
       <c r="G443" s="1">
         <v>1000</v>
@@ -16416,15 +16420,15 @@
       <c r="C444" s="1">
         <v>1</v>
       </c>
-      <c r="D444" s="1" t="s">
-        <v>544</v>
+      <c r="D444" s="14" t="s">
+        <v>601</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
       </c>
       <c r="F444" s="1">
         <f>VLOOKUP(D444,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5032</v>
+        <v>5203</v>
       </c>
       <c r="G444" s="1">
         <v>1000</v>
@@ -16446,15 +16450,15 @@
       <c r="C445" s="1">
         <v>1</v>
       </c>
-      <c r="D445" s="1" t="s">
-        <v>534</v>
+      <c r="D445" s="14" t="s">
+        <v>602</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
       </c>
       <c r="F445" s="1">
         <f>VLOOKUP(D445,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5204</v>
       </c>
       <c r="G445" s="1">
         <v>1000</v>
@@ -16468,23 +16472,23 @@
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B446" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C446" s="1">
         <v>1</v>
       </c>
-      <c r="D446" s="1" t="s">
-        <v>559</v>
+      <c r="D446" s="14" t="s">
+        <v>599</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
       </c>
       <c r="F446" s="1">
         <f>VLOOKUP(D446,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5006</v>
+        <v>5206</v>
       </c>
       <c r="G446" s="1">
         <v>1000</v>
@@ -16498,23 +16502,23 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B447" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C447" s="1">
         <v>1</v>
       </c>
-      <c r="D447" s="1" t="s">
-        <v>560</v>
+      <c r="D447" s="14" t="s">
+        <v>600</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
       </c>
       <c r="F447" s="1">
         <f>VLOOKUP(D447,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5207</v>
       </c>
       <c r="G447" s="1">
         <v>1000</v>
@@ -16528,23 +16532,23 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B448" s="1">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C448" s="1">
         <v>1</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
       </c>
       <c r="F448" s="1">
         <f>VLOOKUP(D448,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5019</v>
       </c>
       <c r="G448" s="1">
         <v>1000</v>
@@ -16567,14 +16571,14 @@
         <v>1</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
       </c>
       <c r="F449" s="1">
         <f>VLOOKUP(D449,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5006</v>
       </c>
       <c r="G449" s="1">
         <v>1000</v>
@@ -16597,14 +16601,14 @@
         <v>1</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
       </c>
       <c r="F450" s="1">
         <f>VLOOKUP(D450,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="G450" s="1">
         <v>1000</v>
@@ -16627,14 +16631,14 @@
         <v>1</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
       </c>
       <c r="F451" s="1">
         <f>VLOOKUP(D451,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="G451" s="1">
         <v>1000</v>
@@ -16657,14 +16661,14 @@
         <v>1</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
       </c>
       <c r="F452" s="1">
         <f>VLOOKUP(D452,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5002</v>
       </c>
       <c r="G452" s="1">
         <v>1000</v>
@@ -16687,14 +16691,14 @@
         <v>1</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E453" s="1">
         <v>0</v>
       </c>
       <c r="F453" s="1">
         <f>VLOOKUP(D453,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5003</v>
       </c>
       <c r="G453" s="1">
         <v>1000</v>
@@ -16717,14 +16721,14 @@
         <v>1</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
       </c>
       <c r="F454" s="1">
         <f>VLOOKUP(D454,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5018</v>
       </c>
       <c r="G454" s="1">
         <v>1000</v>
@@ -16747,14 +16751,14 @@
         <v>1</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="E455" s="1">
         <v>0</v>
       </c>
       <c r="F455" s="1">
         <f>VLOOKUP(D455,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5007</v>
+        <v>5027</v>
       </c>
       <c r="G455" s="1">
         <v>1000</v>
@@ -16777,14 +16781,14 @@
         <v>1</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
       </c>
       <c r="F456" s="1">
         <f>VLOOKUP(D456,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5017</v>
+        <v>5028</v>
       </c>
       <c r="G456" s="1">
         <v>1000</v>
@@ -16807,14 +16811,14 @@
         <v>1</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
       </c>
       <c r="F457" s="1">
         <f>VLOOKUP(D457,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5019</v>
+        <v>5029</v>
       </c>
       <c r="G457" s="1">
         <v>1000</v>
@@ -16828,23 +16832,23 @@
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B458" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C458" s="1">
         <v>1</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
       </c>
       <c r="F458" s="1">
         <f>VLOOKUP(D458,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5001</v>
+        <v>5007</v>
       </c>
       <c r="G458" s="1">
         <v>1000</v>
@@ -16858,23 +16862,23 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B459" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C459" s="1">
         <v>1</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
       </c>
       <c r="F459" s="1">
         <f>VLOOKUP(D459,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5014</v>
+        <v>5017</v>
       </c>
       <c r="G459" s="1">
         <v>1000</v>
@@ -16888,23 +16892,23 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B460" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C460" s="1">
         <v>1</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
       </c>
       <c r="F460" s="1">
         <f>VLOOKUP(D460,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5019</v>
       </c>
       <c r="G460" s="1">
         <v>1000</v>
@@ -16918,23 +16922,23 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B461" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C461" s="1">
         <v>1</v>
       </c>
-      <c r="D461" s="1" t="s">
-        <v>554</v>
+      <c r="D461" s="14" t="s">
+        <v>601</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
       </c>
       <c r="F461" s="1">
         <f>VLOOKUP(D461,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5203</v>
       </c>
       <c r="G461" s="1">
         <v>1000</v>
@@ -16948,23 +16952,23 @@
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B462" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C462" s="1">
         <v>1</v>
       </c>
-      <c r="D462" s="1" t="s">
-        <v>555</v>
+      <c r="D462" s="14" t="s">
+        <v>602</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
       </c>
       <c r="F462" s="1">
         <f>VLOOKUP(D462,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5204</v>
       </c>
       <c r="G462" s="1">
         <v>1000</v>
@@ -16978,23 +16982,23 @@
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B463" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C463" s="1">
         <v>1</v>
       </c>
-      <c r="D463" s="1" t="s">
-        <v>556</v>
+      <c r="D463" s="14" t="s">
+        <v>599</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
       </c>
       <c r="F463" s="1">
         <f>VLOOKUP(D463,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5206</v>
       </c>
       <c r="G463" s="1">
         <v>1000</v>
@@ -17008,23 +17012,23 @@
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B464" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C464" s="1">
         <v>1</v>
       </c>
-      <c r="D464" s="1" t="s">
-        <v>557</v>
+      <c r="D464" s="14" t="s">
+        <v>600</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
       </c>
       <c r="F464" s="1">
         <f>VLOOKUP(D464,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5207</v>
       </c>
       <c r="G464" s="1">
         <v>1000</v>
@@ -17038,23 +17042,23 @@
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B465" s="1">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C465" s="1">
         <v>1</v>
       </c>
-      <c r="D465" s="1" t="s">
-        <v>558</v>
+      <c r="D465" s="14" t="s">
+        <v>603</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
       </c>
       <c r="F465" s="1">
         <f>VLOOKUP(D465,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5205</v>
       </c>
       <c r="G465" s="1">
         <v>1000</v>
@@ -17068,23 +17072,23 @@
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B466" s="1">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C466" s="1">
         <v>1</v>
       </c>
-      <c r="D466" t="s">
-        <v>553</v>
+      <c r="D466" s="14" t="s">
+        <v>604</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
       </c>
       <c r="F466" s="1">
         <f>VLOOKUP(D466,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5002</v>
+        <v>5208</v>
       </c>
       <c r="G466" s="1">
         <v>1000</v>
@@ -17098,23 +17102,23 @@
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B467" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C467" s="1">
         <v>1</v>
       </c>
-      <c r="D467" t="s">
-        <v>554</v>
+      <c r="D467" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
       </c>
       <c r="F467" s="1">
         <f>VLOOKUP(D467,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="G467" s="1">
         <v>1000</v>
@@ -17128,23 +17132,23 @@
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B468" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C468" s="1">
         <v>1</v>
       </c>
-      <c r="D468" t="s">
-        <v>555</v>
+      <c r="D468" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
       </c>
       <c r="F468" s="1">
         <f>VLOOKUP(D468,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="G468" s="1">
         <v>1000</v>
@@ -17158,23 +17162,23 @@
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B469" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C469" s="1">
         <v>1</v>
       </c>
-      <c r="D469" t="s">
-        <v>556</v>
+      <c r="D469" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
       </c>
       <c r="F469" s="1">
         <f>VLOOKUP(D469,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5027</v>
+        <v>5002</v>
       </c>
       <c r="G469" s="1">
         <v>1000</v>
@@ -17188,23 +17192,23 @@
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B470" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C470" s="1">
         <v>1</v>
       </c>
-      <c r="D470" t="s">
-        <v>557</v>
+      <c r="D470" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
       </c>
       <c r="F470" s="1">
         <f>VLOOKUP(D470,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5028</v>
+        <v>5003</v>
       </c>
       <c r="G470" s="1">
         <v>1000</v>
@@ -17218,23 +17222,23 @@
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B471" s="1">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C471" s="1">
         <v>1</v>
       </c>
-      <c r="D471" t="s">
-        <v>558</v>
+      <c r="D471" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
       </c>
       <c r="F471" s="1">
         <f>VLOOKUP(D471,Sheet2!$G$249:$H$290,2,FALSE)</f>
-        <v>5029</v>
+        <v>5018</v>
       </c>
       <c r="G471" s="1">
         <v>1000</v>
@@ -17243,6 +17247,426 @@
         <v>1</v>
       </c>
       <c r="I471" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A472" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B472" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C472" s="1">
+        <v>1</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E472" s="1">
+        <v>0</v>
+      </c>
+      <c r="F472" s="1">
+        <f>VLOOKUP(D472,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G472" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H472" s="1">
+        <v>1</v>
+      </c>
+      <c r="I472" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A473" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B473" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C473" s="1">
+        <v>1</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E473" s="1">
+        <v>0</v>
+      </c>
+      <c r="F473" s="1">
+        <f>VLOOKUP(D473,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G473" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H473" s="1">
+        <v>1</v>
+      </c>
+      <c r="I473" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A474" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B474" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C474" s="1">
+        <v>1</v>
+      </c>
+      <c r="D474" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="E474" s="1">
+        <v>0</v>
+      </c>
+      <c r="F474" s="1">
+        <f>VLOOKUP(D474,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5203</v>
+      </c>
+      <c r="G474" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H474" s="1">
+        <v>1</v>
+      </c>
+      <c r="I474" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A475" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B475" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C475" s="1">
+        <v>1</v>
+      </c>
+      <c r="D475" s="14" t="s">
+        <v>602</v>
+      </c>
+      <c r="E475" s="1">
+        <v>0</v>
+      </c>
+      <c r="F475" s="1">
+        <f>VLOOKUP(D475,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5204</v>
+      </c>
+      <c r="G475" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H475" s="1">
+        <v>1</v>
+      </c>
+      <c r="I475" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A476" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B476" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C476" s="1">
+        <v>1</v>
+      </c>
+      <c r="D476" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="E476" s="1">
+        <v>0</v>
+      </c>
+      <c r="F476" s="1">
+        <f>VLOOKUP(D476,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5206</v>
+      </c>
+      <c r="G476" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H476" s="1">
+        <v>1</v>
+      </c>
+      <c r="I476" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A477" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B477" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C477" s="1">
+        <v>1</v>
+      </c>
+      <c r="D477" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="E477" s="1">
+        <v>0</v>
+      </c>
+      <c r="F477" s="1">
+        <f>VLOOKUP(D477,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5207</v>
+      </c>
+      <c r="G477" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H477" s="1">
+        <v>1</v>
+      </c>
+      <c r="I477" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A478" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B478" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C478" s="1">
+        <v>1</v>
+      </c>
+      <c r="D478" t="s">
+        <v>553</v>
+      </c>
+      <c r="E478" s="1">
+        <v>0</v>
+      </c>
+      <c r="F478" s="1">
+        <f>VLOOKUP(D478,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5002</v>
+      </c>
+      <c r="G478" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H478" s="1">
+        <v>1</v>
+      </c>
+      <c r="I478" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A479" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B479" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C479" s="1">
+        <v>1</v>
+      </c>
+      <c r="D479" t="s">
+        <v>554</v>
+      </c>
+      <c r="E479" s="1">
+        <v>0</v>
+      </c>
+      <c r="F479" s="1">
+        <f>VLOOKUP(D479,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5003</v>
+      </c>
+      <c r="G479" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H479" s="1">
+        <v>1</v>
+      </c>
+      <c r="I479" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A480" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B480" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C480" s="1">
+        <v>1</v>
+      </c>
+      <c r="D480" t="s">
+        <v>555</v>
+      </c>
+      <c r="E480" s="1">
+        <v>0</v>
+      </c>
+      <c r="F480" s="1">
+        <f>VLOOKUP(D480,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5018</v>
+      </c>
+      <c r="G480" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H480" s="1">
+        <v>1</v>
+      </c>
+      <c r="I480" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A481" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B481" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C481" s="1">
+        <v>1</v>
+      </c>
+      <c r="D481" t="s">
+        <v>556</v>
+      </c>
+      <c r="E481" s="1">
+        <v>0</v>
+      </c>
+      <c r="F481" s="1">
+        <f>VLOOKUP(D481,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5027</v>
+      </c>
+      <c r="G481" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H481" s="1">
+        <v>1</v>
+      </c>
+      <c r="I481" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A482" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B482" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C482" s="1">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>557</v>
+      </c>
+      <c r="E482" s="1">
+        <v>0</v>
+      </c>
+      <c r="F482" s="1">
+        <f>VLOOKUP(D482,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5028</v>
+      </c>
+      <c r="G482" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H482" s="1">
+        <v>1</v>
+      </c>
+      <c r="I482" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A483" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B483" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C483" s="1">
+        <v>1</v>
+      </c>
+      <c r="D483" t="s">
+        <v>558</v>
+      </c>
+      <c r="E483" s="1">
+        <v>0</v>
+      </c>
+      <c r="F483" s="1">
+        <f>VLOOKUP(D483,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5029</v>
+      </c>
+      <c r="G483" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H483" s="1">
+        <v>1</v>
+      </c>
+      <c r="I483" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A484" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B484" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C484" s="1">
+        <v>1</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E484" s="1">
+        <v>0</v>
+      </c>
+      <c r="F484" s="1">
+        <f>VLOOKUP(D484,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5203</v>
+      </c>
+      <c r="G484" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H484" s="1">
+        <v>1</v>
+      </c>
+      <c r="I484" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A485" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B485" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C485" s="1">
+        <v>1</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E485" s="1">
+        <v>0</v>
+      </c>
+      <c r="F485" s="1">
+        <f>VLOOKUP(D485,Sheet2!$G$249:$H$290,2,FALSE)</f>
+        <v>5204</v>
+      </c>
+      <c r="G485" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H485" s="1">
+        <v>1</v>
+      </c>
+      <c r="I485" s="1">
         <v>1</v>
       </c>
     </row>
@@ -19139,7 +19563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B7:I290"/>
+  <dimension ref="B7:I289"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="9" customWidth="1"/>
@@ -23788,7 +24212,7 @@
     </row>
     <row r="284" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G284" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="H284">
         <v>5203</v>
@@ -23796,7 +24220,7 @@
     </row>
     <row r="285" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G285" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="H285">
         <v>5204</v>
@@ -23804,7 +24228,7 @@
     </row>
     <row r="286" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G286" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="H286">
         <v>5205</v>
@@ -23812,7 +24236,7 @@
     </row>
     <row r="287" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G287" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="H287">
         <v>5206</v>
@@ -23820,7 +24244,7 @@
     </row>
     <row r="288" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G288" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H288">
         <v>5207</v>
@@ -23828,18 +24252,10 @@
     </row>
     <row r="289" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G289" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="H289">
         <v>5208</v>
-      </c>
-    </row>
-    <row r="290" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G290" t="s">
-        <v>581</v>
-      </c>
-      <c r="H290">
-        <v>5209</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="667">
   <si>
     <t>text</t>
   </si>
@@ -2105,13 +2105,75 @@
   </si>
   <si>
     <t>亮灯</t>
+  </si>
+  <si>
+    <t>早上闲逛地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后山</t>
+  </si>
+  <si>
+    <t>山坡</t>
+  </si>
+  <si>
+    <t>码头</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>2355</t>
+  </si>
+  <si>
+    <t>2497</t>
+  </si>
+  <si>
+    <t>白天闲逛地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门</t>
+  </si>
+  <si>
+    <t>商店街</t>
+  </si>
+  <si>
+    <t>住宅区</t>
+  </si>
+  <si>
+    <t>中央广场</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>傍晚闲逛地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上闲逛地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深夜闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2138,6 +2200,12 @@
       <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2184,7 +2252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2223,6 +2291,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3685,7 +3755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I924"/>
+  <dimension ref="A1:I952"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -3694,8 +3764,8 @@
     <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
-    <col min="8" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="8" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -31394,6 +31464,818 @@
         <v>1</v>
       </c>
       <c r="I924" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A925" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B925" s="1">
+        <v>60001</v>
+      </c>
+      <c r="C925" s="1">
+        <v>1</v>
+      </c>
+      <c r="D925" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E925" s="1">
+        <v>0</v>
+      </c>
+      <c r="F925" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G925" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H925" s="1">
+        <v>1</v>
+      </c>
+      <c r="I925" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A926" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B926" s="1">
+        <v>60001</v>
+      </c>
+      <c r="C926" s="1">
+        <v>1</v>
+      </c>
+      <c r="D926" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="E926" s="1">
+        <v>0</v>
+      </c>
+      <c r="F926" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G926" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H926" s="1">
+        <v>1</v>
+      </c>
+      <c r="I926" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A927" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B927" s="1">
+        <v>60001</v>
+      </c>
+      <c r="C927" s="1">
+        <v>1</v>
+      </c>
+      <c r="D927" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="E927" s="1">
+        <v>0</v>
+      </c>
+      <c r="F927" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G927" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H927" s="1">
+        <v>1</v>
+      </c>
+      <c r="I927" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A928" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B928" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C928" s="1">
+        <v>1</v>
+      </c>
+      <c r="D928" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E928" s="1">
+        <v>0</v>
+      </c>
+      <c r="F928" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G928" s="1">
+        <v>300</v>
+      </c>
+      <c r="H928" s="1">
+        <v>1</v>
+      </c>
+      <c r="I928" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A929" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B929" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C929" s="1">
+        <v>1</v>
+      </c>
+      <c r="D929" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="E929" s="1">
+        <v>0</v>
+      </c>
+      <c r="F929" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G929" s="1">
+        <v>500</v>
+      </c>
+      <c r="H929" s="1">
+        <v>1</v>
+      </c>
+      <c r="I929" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A930" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B930" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C930" s="1">
+        <v>1</v>
+      </c>
+      <c r="D930" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="E930" s="1">
+        <v>0</v>
+      </c>
+      <c r="F930" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G930" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H930" s="1">
+        <v>1</v>
+      </c>
+      <c r="I930" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A931" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B931" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C931" s="1">
+        <v>1</v>
+      </c>
+      <c r="D931" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="E931" s="1">
+        <v>0</v>
+      </c>
+      <c r="F931" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G931" s="1">
+        <v>500</v>
+      </c>
+      <c r="H931" s="1">
+        <v>1</v>
+      </c>
+      <c r="I931" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A932" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B932" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C932" s="1">
+        <v>1</v>
+      </c>
+      <c r="D932" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E932" s="1">
+        <v>0</v>
+      </c>
+      <c r="F932" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="G932" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H932" s="1">
+        <v>1</v>
+      </c>
+      <c r="I932" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A933" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B933" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C933" s="1">
+        <v>1</v>
+      </c>
+      <c r="D933" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E933" s="1">
+        <v>0</v>
+      </c>
+      <c r="F933" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G933" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H933" s="1">
+        <v>1</v>
+      </c>
+      <c r="I933" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A934" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B934" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C934" s="1">
+        <v>1</v>
+      </c>
+      <c r="D934" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="E934" s="1">
+        <v>0</v>
+      </c>
+      <c r="F934" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="G934" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H934" s="1">
+        <v>1</v>
+      </c>
+      <c r="I934" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A935" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B935" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C935" s="1">
+        <v>1</v>
+      </c>
+      <c r="D935" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E935" s="1">
+        <v>0</v>
+      </c>
+      <c r="F935" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G935" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H935" s="1">
+        <v>1</v>
+      </c>
+      <c r="I935" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A936" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B936" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C936" s="1">
+        <v>1</v>
+      </c>
+      <c r="D936" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="E936" s="1">
+        <v>0</v>
+      </c>
+      <c r="F936" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G936" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H936" s="1">
+        <v>1</v>
+      </c>
+      <c r="I936" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A937" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B937" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C937" s="1">
+        <v>1</v>
+      </c>
+      <c r="D937" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="E937" s="1">
+        <v>0</v>
+      </c>
+      <c r="F937" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G937" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H937" s="1">
+        <v>1</v>
+      </c>
+      <c r="I937" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A938" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B938" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C938" s="1">
+        <v>1</v>
+      </c>
+      <c r="D938" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="E938" s="1">
+        <v>0</v>
+      </c>
+      <c r="F938" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G938" s="1">
+        <v>800</v>
+      </c>
+      <c r="H938" s="1">
+        <v>1</v>
+      </c>
+      <c r="I938" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A939" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B939" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C939" s="1">
+        <v>1</v>
+      </c>
+      <c r="D939" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E939" s="1">
+        <v>0</v>
+      </c>
+      <c r="F939" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="G939" s="1">
+        <v>500</v>
+      </c>
+      <c r="H939" s="1">
+        <v>1</v>
+      </c>
+      <c r="I939" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A940" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B940" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C940" s="1">
+        <v>1</v>
+      </c>
+      <c r="D940" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E940" s="1">
+        <v>0</v>
+      </c>
+      <c r="F940" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G940" s="1">
+        <v>500</v>
+      </c>
+      <c r="H940" s="1">
+        <v>1</v>
+      </c>
+      <c r="I940" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A941" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B941" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C941" s="1">
+        <v>1</v>
+      </c>
+      <c r="D941" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="E941" s="1">
+        <v>0</v>
+      </c>
+      <c r="F941" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="G941" s="1">
+        <v>500</v>
+      </c>
+      <c r="H941" s="1">
+        <v>1</v>
+      </c>
+      <c r="I941" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A942" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B942" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C942" s="1">
+        <v>1</v>
+      </c>
+      <c r="D942" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E942" s="1">
+        <v>0</v>
+      </c>
+      <c r="F942" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G942" s="1">
+        <v>200</v>
+      </c>
+      <c r="H942" s="1">
+        <v>1</v>
+      </c>
+      <c r="I942" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A943" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B943" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C943" s="1">
+        <v>1</v>
+      </c>
+      <c r="D943" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="E943" s="1">
+        <v>0</v>
+      </c>
+      <c r="F943" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G943" s="1">
+        <v>200</v>
+      </c>
+      <c r="H943" s="1">
+        <v>1</v>
+      </c>
+      <c r="I943" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A944" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B944" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C944" s="1">
+        <v>1</v>
+      </c>
+      <c r="D944" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="E944" s="1">
+        <v>0</v>
+      </c>
+      <c r="F944" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G944" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H944" s="1">
+        <v>1</v>
+      </c>
+      <c r="I944" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A945" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B945" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C945" s="1">
+        <v>1</v>
+      </c>
+      <c r="D945" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="E945" s="1">
+        <v>0</v>
+      </c>
+      <c r="F945" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G945" s="1">
+        <v>500</v>
+      </c>
+      <c r="H945" s="1">
+        <v>1</v>
+      </c>
+      <c r="I945" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A946" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B946" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C946" s="1">
+        <v>1</v>
+      </c>
+      <c r="D946" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E946" s="1">
+        <v>0</v>
+      </c>
+      <c r="F946" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="G946" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H946" s="1">
+        <v>1</v>
+      </c>
+      <c r="I946" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A947" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B947" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C947" s="1">
+        <v>1</v>
+      </c>
+      <c r="D947" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E947" s="1">
+        <v>0</v>
+      </c>
+      <c r="F947" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G947" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H947" s="1">
+        <v>1</v>
+      </c>
+      <c r="I947" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A948" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B948" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C948" s="1">
+        <v>1</v>
+      </c>
+      <c r="D948" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="E948" s="1">
+        <v>0</v>
+      </c>
+      <c r="F948" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="G948" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H948" s="1">
+        <v>1</v>
+      </c>
+      <c r="I948" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A949" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B949" s="1">
+        <v>60005</v>
+      </c>
+      <c r="C949" s="1">
+        <v>1</v>
+      </c>
+      <c r="D949" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="E949" s="1">
+        <v>0</v>
+      </c>
+      <c r="F949" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G949" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H949" s="1">
+        <v>1</v>
+      </c>
+      <c r="I949" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A950" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B950" s="1">
+        <v>60005</v>
+      </c>
+      <c r="C950" s="1">
+        <v>1</v>
+      </c>
+      <c r="D950" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="E950" s="1">
+        <v>0</v>
+      </c>
+      <c r="F950" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="G950" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H950" s="1">
+        <v>1</v>
+      </c>
+      <c r="I950" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A951" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B951" s="1">
+        <v>60005</v>
+      </c>
+      <c r="C951" s="1">
+        <v>1</v>
+      </c>
+      <c r="D951" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E951" s="1">
+        <v>0</v>
+      </c>
+      <c r="F951" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G951" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H951" s="1">
+        <v>1</v>
+      </c>
+      <c r="I951" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A952" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B952" s="1">
+        <v>60005</v>
+      </c>
+      <c r="C952" s="1">
+        <v>1</v>
+      </c>
+      <c r="D952" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="E952" s="1">
+        <v>0</v>
+      </c>
+      <c r="F952" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="G952" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H952" s="1">
+        <v>1</v>
+      </c>
+      <c r="I952" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="699">
   <si>
     <t>text</t>
   </si>
@@ -2167,6 +2167,102 @@
   <si>
     <t>深夜闲逛</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹对话</t>
+  </si>
+  <si>
+    <t>玛德琳对话</t>
+  </si>
+  <si>
+    <t>丝特芬妮对话</t>
+  </si>
+  <si>
+    <t>格吉尔对话</t>
+  </si>
+  <si>
+    <t>亚度尼斯对话</t>
+  </si>
+  <si>
+    <t>琼对话</t>
+  </si>
+  <si>
+    <t>占卜婆婆对话</t>
+  </si>
+  <si>
+    <t>坎蒂丝对话</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚对话</t>
+  </si>
+  <si>
+    <t>希拉对话</t>
+  </si>
+  <si>
+    <t>希尔达对话</t>
+  </si>
+  <si>
+    <t>布拉德利对话</t>
+  </si>
+  <si>
+    <t>布蓝达对话</t>
+  </si>
+  <si>
+    <t>希贝儿对话</t>
+  </si>
+  <si>
+    <t>帕特里克对话</t>
+  </si>
+  <si>
+    <t>朵儿洁对话</t>
+  </si>
+  <si>
+    <t>梅林对话</t>
+  </si>
+  <si>
+    <t>摩尔根对话</t>
+  </si>
+  <si>
+    <t>马勒第兹对话</t>
+  </si>
+  <si>
+    <t>考波特对话</t>
+  </si>
+  <si>
+    <t>夏佐对话</t>
+  </si>
+  <si>
+    <t>爱格伯特对话</t>
+  </si>
+  <si>
+    <t>强尼对话</t>
+  </si>
+  <si>
+    <t>瓦尔特对话</t>
+  </si>
+  <si>
+    <t>阿普敦对话</t>
+  </si>
+  <si>
+    <t>艾琳娜对话</t>
+  </si>
+  <si>
+    <t>莱特对话</t>
+  </si>
+  <si>
+    <t>爱丽丝对话</t>
+  </si>
+  <si>
+    <t>阿尔杰农对话</t>
+  </si>
+  <si>
+    <t>黛芙妮对话</t>
+  </si>
+  <si>
+    <t>纺织婆婆对话</t>
+  </si>
+  <si>
+    <t>班尼迪克对话</t>
   </si>
 </sst>
 </file>
@@ -3755,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I952"/>
+  <dimension ref="A1:I1082"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -32276,6 +32372,3386 @@
         <v>1</v>
       </c>
       <c r="I952" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A953" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B953" s="1">
+        <v>70001</v>
+      </c>
+      <c r="C953" s="1">
+        <v>1</v>
+      </c>
+      <c r="E953" s="1">
+        <v>0</v>
+      </c>
+      <c r="F953" s="2">
+        <v>4001</v>
+      </c>
+      <c r="G953" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H953" s="1">
+        <v>1</v>
+      </c>
+      <c r="I953" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A954" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B954" s="1">
+        <v>70001</v>
+      </c>
+      <c r="C954" s="1">
+        <v>1</v>
+      </c>
+      <c r="E954" s="1">
+        <v>0</v>
+      </c>
+      <c r="F954" s="2">
+        <v>4002</v>
+      </c>
+      <c r="G954" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H954" s="1">
+        <v>1</v>
+      </c>
+      <c r="I954" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A955" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B955" s="1">
+        <v>70001</v>
+      </c>
+      <c r="C955" s="1">
+        <v>1</v>
+      </c>
+      <c r="E955" s="1">
+        <v>0</v>
+      </c>
+      <c r="F955" s="2">
+        <v>4003</v>
+      </c>
+      <c r="G955" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H955" s="1">
+        <v>1</v>
+      </c>
+      <c r="I955" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A956" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B956" s="1">
+        <v>70001</v>
+      </c>
+      <c r="C956" s="1">
+        <v>1</v>
+      </c>
+      <c r="E956" s="1">
+        <v>0</v>
+      </c>
+      <c r="F956" s="2">
+        <v>4004</v>
+      </c>
+      <c r="G956" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H956" s="1">
+        <v>1</v>
+      </c>
+      <c r="I956" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A957" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B957" s="1">
+        <v>70002</v>
+      </c>
+      <c r="C957" s="1">
+        <v>1</v>
+      </c>
+      <c r="E957" s="1">
+        <v>0</v>
+      </c>
+      <c r="F957" s="2">
+        <v>4006</v>
+      </c>
+      <c r="G957" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H957" s="1">
+        <v>1</v>
+      </c>
+      <c r="I957" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A958" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B958" s="1">
+        <v>70002</v>
+      </c>
+      <c r="C958" s="1">
+        <v>1</v>
+      </c>
+      <c r="E958" s="1">
+        <v>0</v>
+      </c>
+      <c r="F958" s="2">
+        <v>4007</v>
+      </c>
+      <c r="G958" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H958" s="1">
+        <v>1</v>
+      </c>
+      <c r="I958" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A959" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B959" s="1">
+        <v>70002</v>
+      </c>
+      <c r="C959" s="1">
+        <v>1</v>
+      </c>
+      <c r="E959" s="1">
+        <v>0</v>
+      </c>
+      <c r="F959" s="2">
+        <v>4008</v>
+      </c>
+      <c r="G959" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H959" s="1">
+        <v>1</v>
+      </c>
+      <c r="I959" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A960" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B960" s="1">
+        <v>70002</v>
+      </c>
+      <c r="C960" s="1">
+        <v>1</v>
+      </c>
+      <c r="E960" s="1">
+        <v>0</v>
+      </c>
+      <c r="F960" s="2">
+        <v>4009</v>
+      </c>
+      <c r="G960" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H960" s="1">
+        <v>1</v>
+      </c>
+      <c r="I960" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A961" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B961" s="1">
+        <v>70002</v>
+      </c>
+      <c r="C961" s="1">
+        <v>1</v>
+      </c>
+      <c r="E961" s="1">
+        <v>0</v>
+      </c>
+      <c r="F961" s="2">
+        <v>4010</v>
+      </c>
+      <c r="G961" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H961" s="1">
+        <v>1</v>
+      </c>
+      <c r="I961" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A962" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B962" s="1">
+        <v>70003</v>
+      </c>
+      <c r="C962" s="1">
+        <v>1</v>
+      </c>
+      <c r="E962" s="1">
+        <v>0</v>
+      </c>
+      <c r="F962" s="2">
+        <v>4012</v>
+      </c>
+      <c r="G962" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H962" s="1">
+        <v>1</v>
+      </c>
+      <c r="I962" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A963" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B963" s="1">
+        <v>70003</v>
+      </c>
+      <c r="C963" s="1">
+        <v>1</v>
+      </c>
+      <c r="E963" s="1">
+        <v>0</v>
+      </c>
+      <c r="F963" s="2">
+        <v>4013</v>
+      </c>
+      <c r="G963" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H963" s="1">
+        <v>1</v>
+      </c>
+      <c r="I963" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A964" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B964" s="1">
+        <v>70003</v>
+      </c>
+      <c r="C964" s="1">
+        <v>1</v>
+      </c>
+      <c r="E964" s="1">
+        <v>0</v>
+      </c>
+      <c r="F964" s="2">
+        <v>4014</v>
+      </c>
+      <c r="G964" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H964" s="1">
+        <v>1</v>
+      </c>
+      <c r="I964" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A965" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B965" s="1">
+        <v>70003</v>
+      </c>
+      <c r="C965" s="1">
+        <v>1</v>
+      </c>
+      <c r="E965" s="1">
+        <v>0</v>
+      </c>
+      <c r="F965" s="2">
+        <v>4015</v>
+      </c>
+      <c r="G965" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H965" s="1">
+        <v>1</v>
+      </c>
+      <c r="I965" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A966" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B966" s="1">
+        <v>70004</v>
+      </c>
+      <c r="C966" s="1">
+        <v>1</v>
+      </c>
+      <c r="E966" s="1">
+        <v>0</v>
+      </c>
+      <c r="F966" s="2">
+        <v>4017</v>
+      </c>
+      <c r="G966" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H966" s="1">
+        <v>1</v>
+      </c>
+      <c r="I966" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A967" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B967" s="1">
+        <v>70004</v>
+      </c>
+      <c r="C967" s="1">
+        <v>1</v>
+      </c>
+      <c r="E967" s="1">
+        <v>0</v>
+      </c>
+      <c r="F967" s="2">
+        <v>4018</v>
+      </c>
+      <c r="G967" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H967" s="1">
+        <v>1</v>
+      </c>
+      <c r="I967" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A968" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B968" s="1">
+        <v>70004</v>
+      </c>
+      <c r="C968" s="1">
+        <v>1</v>
+      </c>
+      <c r="E968" s="1">
+        <v>0</v>
+      </c>
+      <c r="F968" s="2">
+        <v>4019</v>
+      </c>
+      <c r="G968" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H968" s="1">
+        <v>1</v>
+      </c>
+      <c r="I968" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A969" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B969" s="1">
+        <v>70004</v>
+      </c>
+      <c r="C969" s="1">
+        <v>1</v>
+      </c>
+      <c r="E969" s="1">
+        <v>0</v>
+      </c>
+      <c r="F969" s="2">
+        <v>4020</v>
+      </c>
+      <c r="G969" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H969" s="1">
+        <v>1</v>
+      </c>
+      <c r="I969" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A970" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B970" s="1">
+        <v>70005</v>
+      </c>
+      <c r="C970" s="1">
+        <v>1</v>
+      </c>
+      <c r="E970" s="1">
+        <v>0</v>
+      </c>
+      <c r="F970" s="9">
+        <v>4022</v>
+      </c>
+      <c r="G970" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H970" s="1">
+        <v>1</v>
+      </c>
+      <c r="I970" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A971" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B971" s="1">
+        <v>70005</v>
+      </c>
+      <c r="C971" s="1">
+        <v>1</v>
+      </c>
+      <c r="E971" s="1">
+        <v>0</v>
+      </c>
+      <c r="F971" s="9">
+        <v>4023</v>
+      </c>
+      <c r="G971" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H971" s="1">
+        <v>1</v>
+      </c>
+      <c r="I971" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A972" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B972" s="1">
+        <v>70005</v>
+      </c>
+      <c r="C972" s="1">
+        <v>1</v>
+      </c>
+      <c r="E972" s="1">
+        <v>0</v>
+      </c>
+      <c r="F972" s="9">
+        <v>4024</v>
+      </c>
+      <c r="G972" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H972" s="1">
+        <v>1</v>
+      </c>
+      <c r="I972" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A973" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B973" s="1">
+        <v>70005</v>
+      </c>
+      <c r="C973" s="1">
+        <v>1</v>
+      </c>
+      <c r="E973" s="1">
+        <v>0</v>
+      </c>
+      <c r="F973" s="9">
+        <v>4025</v>
+      </c>
+      <c r="G973" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H973" s="1">
+        <v>1</v>
+      </c>
+      <c r="I973" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A974" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B974" s="1">
+        <v>70006</v>
+      </c>
+      <c r="C974" s="1">
+        <v>1</v>
+      </c>
+      <c r="E974" s="1">
+        <v>0</v>
+      </c>
+      <c r="F974" s="9">
+        <v>4027</v>
+      </c>
+      <c r="G974" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H974" s="1">
+        <v>1</v>
+      </c>
+      <c r="I974" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A975" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B975" s="1">
+        <v>70006</v>
+      </c>
+      <c r="C975" s="1">
+        <v>1</v>
+      </c>
+      <c r="E975" s="1">
+        <v>0</v>
+      </c>
+      <c r="F975" s="9">
+        <v>4028</v>
+      </c>
+      <c r="G975" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H975" s="1">
+        <v>1</v>
+      </c>
+      <c r="I975" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A976" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B976" s="1">
+        <v>70006</v>
+      </c>
+      <c r="C976" s="1">
+        <v>1</v>
+      </c>
+      <c r="E976" s="1">
+        <v>0</v>
+      </c>
+      <c r="F976" s="9">
+        <v>4029</v>
+      </c>
+      <c r="G976" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H976" s="1">
+        <v>1</v>
+      </c>
+      <c r="I976" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A977" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B977" s="1">
+        <v>70006</v>
+      </c>
+      <c r="C977" s="1">
+        <v>1</v>
+      </c>
+      <c r="E977" s="1">
+        <v>0</v>
+      </c>
+      <c r="F977" s="9">
+        <v>4030</v>
+      </c>
+      <c r="G977" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H977" s="1">
+        <v>1</v>
+      </c>
+      <c r="I977" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A978" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B978" s="1">
+        <v>70007</v>
+      </c>
+      <c r="C978" s="1">
+        <v>1</v>
+      </c>
+      <c r="E978" s="1">
+        <v>0</v>
+      </c>
+      <c r="F978" s="9">
+        <v>4032</v>
+      </c>
+      <c r="G978" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H978" s="1">
+        <v>1</v>
+      </c>
+      <c r="I978" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A979" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B979" s="1">
+        <v>70007</v>
+      </c>
+      <c r="C979" s="1">
+        <v>1</v>
+      </c>
+      <c r="E979" s="1">
+        <v>0</v>
+      </c>
+      <c r="F979" s="9">
+        <v>4033</v>
+      </c>
+      <c r="G979" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H979" s="1">
+        <v>1</v>
+      </c>
+      <c r="I979" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A980" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B980" s="1">
+        <v>70007</v>
+      </c>
+      <c r="C980" s="1">
+        <v>1</v>
+      </c>
+      <c r="E980" s="1">
+        <v>0</v>
+      </c>
+      <c r="F980" s="9">
+        <v>4034</v>
+      </c>
+      <c r="G980" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H980" s="1">
+        <v>1</v>
+      </c>
+      <c r="I980" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A981" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B981" s="1">
+        <v>70007</v>
+      </c>
+      <c r="C981" s="1">
+        <v>1</v>
+      </c>
+      <c r="E981" s="1">
+        <v>0</v>
+      </c>
+      <c r="F981" s="9">
+        <v>4035</v>
+      </c>
+      <c r="G981" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H981" s="1">
+        <v>1</v>
+      </c>
+      <c r="I981" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A982" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B982" s="1">
+        <v>70008</v>
+      </c>
+      <c r="C982" s="1">
+        <v>1</v>
+      </c>
+      <c r="E982" s="1">
+        <v>0</v>
+      </c>
+      <c r="F982" s="9">
+        <v>4037</v>
+      </c>
+      <c r="G982" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H982" s="1">
+        <v>1</v>
+      </c>
+      <c r="I982" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A983" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B983" s="1">
+        <v>70008</v>
+      </c>
+      <c r="C983" s="1">
+        <v>1</v>
+      </c>
+      <c r="E983" s="1">
+        <v>0</v>
+      </c>
+      <c r="F983" s="9">
+        <v>4038</v>
+      </c>
+      <c r="G983" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H983" s="1">
+        <v>1</v>
+      </c>
+      <c r="I983" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A984" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B984" s="1">
+        <v>70008</v>
+      </c>
+      <c r="C984" s="1">
+        <v>1</v>
+      </c>
+      <c r="E984" s="1">
+        <v>0</v>
+      </c>
+      <c r="F984" s="9">
+        <v>4039</v>
+      </c>
+      <c r="G984" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H984" s="1">
+        <v>1</v>
+      </c>
+      <c r="I984" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A985" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B985" s="1">
+        <v>70008</v>
+      </c>
+      <c r="C985" s="1">
+        <v>1</v>
+      </c>
+      <c r="E985" s="1">
+        <v>0</v>
+      </c>
+      <c r="F985" s="9">
+        <v>4040</v>
+      </c>
+      <c r="G985" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H985" s="1">
+        <v>1</v>
+      </c>
+      <c r="I985" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A986" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B986" s="1">
+        <v>70009</v>
+      </c>
+      <c r="C986" s="1">
+        <v>1</v>
+      </c>
+      <c r="E986" s="1">
+        <v>0</v>
+      </c>
+      <c r="F986" s="9">
+        <v>4042</v>
+      </c>
+      <c r="G986" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H986" s="1">
+        <v>1</v>
+      </c>
+      <c r="I986" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A987" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B987" s="1">
+        <v>70009</v>
+      </c>
+      <c r="C987" s="1">
+        <v>1</v>
+      </c>
+      <c r="E987" s="1">
+        <v>0</v>
+      </c>
+      <c r="F987" s="9">
+        <v>4043</v>
+      </c>
+      <c r="G987" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H987" s="1">
+        <v>1</v>
+      </c>
+      <c r="I987" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A988" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B988" s="1">
+        <v>70009</v>
+      </c>
+      <c r="C988" s="1">
+        <v>1</v>
+      </c>
+      <c r="E988" s="1">
+        <v>0</v>
+      </c>
+      <c r="F988" s="9">
+        <v>4044</v>
+      </c>
+      <c r="G988" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H988" s="1">
+        <v>1</v>
+      </c>
+      <c r="I988" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A989" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B989" s="1">
+        <v>70009</v>
+      </c>
+      <c r="C989" s="1">
+        <v>1</v>
+      </c>
+      <c r="E989" s="1">
+        <v>0</v>
+      </c>
+      <c r="F989" s="9">
+        <v>4045</v>
+      </c>
+      <c r="G989" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H989" s="1">
+        <v>1</v>
+      </c>
+      <c r="I989" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A990" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B990" s="1">
+        <v>70010</v>
+      </c>
+      <c r="C990" s="1">
+        <v>1</v>
+      </c>
+      <c r="E990" s="1">
+        <v>0</v>
+      </c>
+      <c r="F990" s="9">
+        <v>4047</v>
+      </c>
+      <c r="G990" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H990" s="1">
+        <v>1</v>
+      </c>
+      <c r="I990" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A991" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B991" s="1">
+        <v>70010</v>
+      </c>
+      <c r="C991" s="1">
+        <v>1</v>
+      </c>
+      <c r="E991" s="1">
+        <v>0</v>
+      </c>
+      <c r="F991" s="9">
+        <v>4048</v>
+      </c>
+      <c r="G991" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H991" s="1">
+        <v>1</v>
+      </c>
+      <c r="I991" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A992" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B992" s="1">
+        <v>70010</v>
+      </c>
+      <c r="C992" s="1">
+        <v>1</v>
+      </c>
+      <c r="E992" s="1">
+        <v>0</v>
+      </c>
+      <c r="F992" s="9">
+        <v>4049</v>
+      </c>
+      <c r="G992" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H992" s="1">
+        <v>1</v>
+      </c>
+      <c r="I992" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A993" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B993" s="1">
+        <v>70010</v>
+      </c>
+      <c r="C993" s="1">
+        <v>1</v>
+      </c>
+      <c r="E993" s="1">
+        <v>0</v>
+      </c>
+      <c r="F993" s="9">
+        <v>4050</v>
+      </c>
+      <c r="G993" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H993" s="1">
+        <v>1</v>
+      </c>
+      <c r="I993" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A994" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B994" s="1">
+        <v>70011</v>
+      </c>
+      <c r="C994" s="1">
+        <v>1</v>
+      </c>
+      <c r="E994" s="1">
+        <v>0</v>
+      </c>
+      <c r="F994" s="9">
+        <v>4052</v>
+      </c>
+      <c r="G994" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H994" s="1">
+        <v>1</v>
+      </c>
+      <c r="I994" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A995" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B995" s="1">
+        <v>70011</v>
+      </c>
+      <c r="C995" s="1">
+        <v>1</v>
+      </c>
+      <c r="E995" s="1">
+        <v>0</v>
+      </c>
+      <c r="F995" s="9">
+        <v>4053</v>
+      </c>
+      <c r="G995" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H995" s="1">
+        <v>1</v>
+      </c>
+      <c r="I995" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A996" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B996" s="1">
+        <v>70011</v>
+      </c>
+      <c r="C996" s="1">
+        <v>1</v>
+      </c>
+      <c r="E996" s="1">
+        <v>0</v>
+      </c>
+      <c r="F996" s="9">
+        <v>4054</v>
+      </c>
+      <c r="G996" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H996" s="1">
+        <v>1</v>
+      </c>
+      <c r="I996" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A997" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B997" s="1">
+        <v>70011</v>
+      </c>
+      <c r="C997" s="1">
+        <v>1</v>
+      </c>
+      <c r="E997" s="1">
+        <v>0</v>
+      </c>
+      <c r="F997" s="9">
+        <v>4055</v>
+      </c>
+      <c r="G997" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H997" s="1">
+        <v>1</v>
+      </c>
+      <c r="I997" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A998" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B998" s="1">
+        <v>70012</v>
+      </c>
+      <c r="C998" s="1">
+        <v>1</v>
+      </c>
+      <c r="E998" s="1">
+        <v>0</v>
+      </c>
+      <c r="F998" s="9">
+        <v>4057</v>
+      </c>
+      <c r="G998" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H998" s="1">
+        <v>1</v>
+      </c>
+      <c r="I998" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A999" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B999" s="1">
+        <v>70012</v>
+      </c>
+      <c r="C999" s="1">
+        <v>1</v>
+      </c>
+      <c r="E999" s="1">
+        <v>0</v>
+      </c>
+      <c r="F999" s="9">
+        <v>4058</v>
+      </c>
+      <c r="G999" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H999" s="1">
+        <v>1</v>
+      </c>
+      <c r="I999" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1000" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1000" s="1">
+        <v>70012</v>
+      </c>
+      <c r="C1000" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1000" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1000" s="9">
+        <v>4059</v>
+      </c>
+      <c r="G1000" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1000" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1000" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1001" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1001" s="1">
+        <v>70012</v>
+      </c>
+      <c r="C1001" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1001" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1001" s="9">
+        <v>4060</v>
+      </c>
+      <c r="G1001" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1001" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1001" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1002" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B1002" s="1">
+        <v>70013</v>
+      </c>
+      <c r="C1002" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1002" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1002" s="9">
+        <v>4062</v>
+      </c>
+      <c r="G1002" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1002" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1002" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1003" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B1003" s="1">
+        <v>70013</v>
+      </c>
+      <c r="C1003" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1003" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1003" s="9">
+        <v>4063</v>
+      </c>
+      <c r="G1003" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1003" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1003" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1004" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B1004" s="1">
+        <v>70013</v>
+      </c>
+      <c r="C1004" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1004" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1004" s="9">
+        <v>4064</v>
+      </c>
+      <c r="G1004" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1004" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1004" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1005" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B1005" s="1">
+        <v>70013</v>
+      </c>
+      <c r="C1005" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1005" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1005" s="9">
+        <v>4065</v>
+      </c>
+      <c r="G1005" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1005" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1005" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1006" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1006" s="1">
+        <v>70014</v>
+      </c>
+      <c r="C1006" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1006" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1006" s="9">
+        <v>4067</v>
+      </c>
+      <c r="G1006" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1006" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1006" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1007" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1007" s="1">
+        <v>70014</v>
+      </c>
+      <c r="C1007" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1007" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1007" s="9">
+        <v>4068</v>
+      </c>
+      <c r="G1007" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1007" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1007" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1008" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1008" s="1">
+        <v>70014</v>
+      </c>
+      <c r="C1008" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1008" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1008" s="9">
+        <v>4069</v>
+      </c>
+      <c r="G1008" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1008" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1008" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1009" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1009" s="1">
+        <v>70014</v>
+      </c>
+      <c r="C1009" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1009" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1009" s="9">
+        <v>4070</v>
+      </c>
+      <c r="G1009" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1009" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1009" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1010" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1010" s="1">
+        <v>70015</v>
+      </c>
+      <c r="C1010" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1010" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1010" s="9">
+        <v>4072</v>
+      </c>
+      <c r="G1010" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1010" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1010" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1011" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1011" s="1">
+        <v>70015</v>
+      </c>
+      <c r="C1011" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1011" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1011" s="9">
+        <v>4073</v>
+      </c>
+      <c r="G1011" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1011" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1011" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1012" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1012" s="1">
+        <v>70015</v>
+      </c>
+      <c r="C1012" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1012" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1012" s="9">
+        <v>4074</v>
+      </c>
+      <c r="G1012" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1012" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1012" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1013" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1013" s="1">
+        <v>70015</v>
+      </c>
+      <c r="C1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1013" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1013" s="9">
+        <v>4075</v>
+      </c>
+      <c r="G1013" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1013" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1014" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1014" s="1">
+        <v>70016</v>
+      </c>
+      <c r="C1014" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1014" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1014" s="9">
+        <v>4077</v>
+      </c>
+      <c r="G1014" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1014" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1014" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1015" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1015" s="1">
+        <v>70016</v>
+      </c>
+      <c r="C1015" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1015" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1015" s="9">
+        <v>4078</v>
+      </c>
+      <c r="G1015" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1015" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1015" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1016" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1016" s="1">
+        <v>70016</v>
+      </c>
+      <c r="C1016" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1016" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1016" s="9">
+        <v>4079</v>
+      </c>
+      <c r="G1016" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1016" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1016" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1017" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1017" s="1">
+        <v>70016</v>
+      </c>
+      <c r="C1017" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1017" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1017" s="9">
+        <v>4080</v>
+      </c>
+      <c r="G1017" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1017" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1017" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1018" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1018" s="1">
+        <v>70017</v>
+      </c>
+      <c r="C1018" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1018" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1018" s="9">
+        <v>4082</v>
+      </c>
+      <c r="G1018" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1018" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1018" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1019" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1019" s="1">
+        <v>70017</v>
+      </c>
+      <c r="C1019" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1019" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1019" s="9">
+        <v>4083</v>
+      </c>
+      <c r="G1019" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1019" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1019" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1020" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1020" s="1">
+        <v>70017</v>
+      </c>
+      <c r="C1020" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1020" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1020" s="9">
+        <v>4084</v>
+      </c>
+      <c r="G1020" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1020" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1020" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1021" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1021" s="1">
+        <v>70017</v>
+      </c>
+      <c r="C1021" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1021" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1021" s="9">
+        <v>4085</v>
+      </c>
+      <c r="G1021" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1021" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1021" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1022" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1022" s="1">
+        <v>70018</v>
+      </c>
+      <c r="C1022" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1022" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1022" s="9">
+        <v>4087</v>
+      </c>
+      <c r="G1022" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1022" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1022" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1023" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1023" s="1">
+        <v>70018</v>
+      </c>
+      <c r="C1023" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1023" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1023" s="9">
+        <v>4088</v>
+      </c>
+      <c r="G1023" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1023" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1023" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1024" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1024" s="1">
+        <v>70018</v>
+      </c>
+      <c r="C1024" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1024" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1024" s="9">
+        <v>4089</v>
+      </c>
+      <c r="G1024" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1024" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1024" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1025" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1025" s="1">
+        <v>70018</v>
+      </c>
+      <c r="C1025" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1025" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1025" s="9">
+        <v>4090</v>
+      </c>
+      <c r="G1025" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1025" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1025" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1026" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1026" s="1">
+        <v>70019</v>
+      </c>
+      <c r="C1026" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1026" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1026" s="9">
+        <v>4092</v>
+      </c>
+      <c r="G1026" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1026" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1026" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1027" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1027" s="1">
+        <v>70019</v>
+      </c>
+      <c r="C1027" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1027" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1027" s="9">
+        <v>4093</v>
+      </c>
+      <c r="G1027" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1027" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1027" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1028" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1028" s="1">
+        <v>70019</v>
+      </c>
+      <c r="C1028" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1028" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1028" s="9">
+        <v>4094</v>
+      </c>
+      <c r="G1028" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1028" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1028" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1029" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1029" s="1">
+        <v>70019</v>
+      </c>
+      <c r="C1029" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1029" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1029" s="9">
+        <v>4095</v>
+      </c>
+      <c r="G1029" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1029" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1029" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1030" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1030" s="1">
+        <v>70020</v>
+      </c>
+      <c r="C1030" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1030" s="9">
+        <v>4097</v>
+      </c>
+      <c r="G1030" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1030" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1030" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1031" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1031" s="1">
+        <v>70020</v>
+      </c>
+      <c r="C1031" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1031" s="9">
+        <v>4098</v>
+      </c>
+      <c r="G1031" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1031" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1031" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1032" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1032" s="1">
+        <v>70020</v>
+      </c>
+      <c r="C1032" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1032" s="9">
+        <v>4099</v>
+      </c>
+      <c r="G1032" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1032" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1032" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1033" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1033" s="1">
+        <v>70020</v>
+      </c>
+      <c r="C1033" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1033" s="9">
+        <v>4100</v>
+      </c>
+      <c r="G1033" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1033" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1033" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1034" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1034" s="1">
+        <v>70021</v>
+      </c>
+      <c r="C1034" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1034" s="9">
+        <v>4102</v>
+      </c>
+      <c r="G1034" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1034" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1034" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1035" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1035" s="1">
+        <v>70021</v>
+      </c>
+      <c r="C1035" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1035" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1035" s="9">
+        <v>4103</v>
+      </c>
+      <c r="G1035" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1035" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1035" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1036" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1036" s="1">
+        <v>70021</v>
+      </c>
+      <c r="C1036" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1036" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1036" s="9">
+        <v>4104</v>
+      </c>
+      <c r="G1036" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1036" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1036" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1037" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1037" s="1">
+        <v>70021</v>
+      </c>
+      <c r="C1037" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1037" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1037" s="9">
+        <v>4105</v>
+      </c>
+      <c r="G1037" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1037" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1037" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1038" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1038" s="1">
+        <v>70022</v>
+      </c>
+      <c r="C1038" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1038" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1038" s="9">
+        <v>4107</v>
+      </c>
+      <c r="G1038" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1038" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1038" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1039" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1039" s="1">
+        <v>70022</v>
+      </c>
+      <c r="C1039" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1039" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1039" s="9">
+        <v>4108</v>
+      </c>
+      <c r="G1039" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1039" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1039" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1040" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1040" s="1">
+        <v>70022</v>
+      </c>
+      <c r="C1040" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1040" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1040" s="9">
+        <v>4109</v>
+      </c>
+      <c r="G1040" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1040" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1040" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1041" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1041" s="1">
+        <v>70022</v>
+      </c>
+      <c r="C1041" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1041" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1041" s="9">
+        <v>4110</v>
+      </c>
+      <c r="G1041" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1041" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1041" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1042" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1042" s="1">
+        <v>70023</v>
+      </c>
+      <c r="C1042" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1042" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1042" s="9">
+        <v>4112</v>
+      </c>
+      <c r="G1042" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1042" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1042" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1043" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1043" s="1">
+        <v>70023</v>
+      </c>
+      <c r="C1043" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1043" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1043" s="9">
+        <v>4113</v>
+      </c>
+      <c r="G1043" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1043" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1043" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1044" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1044" s="1">
+        <v>70023</v>
+      </c>
+      <c r="C1044" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1044" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1044" s="9">
+        <v>4114</v>
+      </c>
+      <c r="G1044" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1044" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1044" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1045" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1045" s="1">
+        <v>70023</v>
+      </c>
+      <c r="C1045" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1045" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1045" s="9">
+        <v>4115</v>
+      </c>
+      <c r="G1045" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1045" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1045" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1046" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1046" s="1">
+        <v>70024</v>
+      </c>
+      <c r="C1046" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1046" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1046" s="9">
+        <v>4117</v>
+      </c>
+      <c r="G1046" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1046" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1046" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1047" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1047" s="1">
+        <v>70024</v>
+      </c>
+      <c r="C1047" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1047" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1047" s="9">
+        <v>4118</v>
+      </c>
+      <c r="G1047" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1047" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1047" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1048" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1048" s="1">
+        <v>70024</v>
+      </c>
+      <c r="C1048" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1048" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1048" s="9">
+        <v>4119</v>
+      </c>
+      <c r="G1048" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1048" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1048" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1049" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1049" s="1">
+        <v>70024</v>
+      </c>
+      <c r="C1049" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1049" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1049" s="9">
+        <v>4120</v>
+      </c>
+      <c r="G1049" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1049" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1049" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1050" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1050" s="1">
+        <v>70025</v>
+      </c>
+      <c r="C1050" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1050" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1050" s="9">
+        <v>4122</v>
+      </c>
+      <c r="G1050" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1050" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1050" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1051" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1051" s="1">
+        <v>70025</v>
+      </c>
+      <c r="C1051" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1051" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1051" s="9">
+        <v>4123</v>
+      </c>
+      <c r="G1051" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1051" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1051" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1052" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1052" s="1">
+        <v>70025</v>
+      </c>
+      <c r="C1052" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1052" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1052" s="9">
+        <v>4124</v>
+      </c>
+      <c r="G1052" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1052" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1052" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1053" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1053" s="1">
+        <v>70025</v>
+      </c>
+      <c r="C1053" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1053" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1053" s="9">
+        <v>4125</v>
+      </c>
+      <c r="G1053" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1053" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1053" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1054" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1054" s="1">
+        <v>70026</v>
+      </c>
+      <c r="C1054" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1054" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1054" s="9">
+        <v>4127</v>
+      </c>
+      <c r="G1054" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1054" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1054" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1055" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1055" s="1">
+        <v>70026</v>
+      </c>
+      <c r="C1055" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1055" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1055" s="9">
+        <v>4128</v>
+      </c>
+      <c r="G1055" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1055" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1055" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1056" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1056" s="1">
+        <v>70026</v>
+      </c>
+      <c r="C1056" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1056" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1056" s="9">
+        <v>4129</v>
+      </c>
+      <c r="G1056" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1056" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1056" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1057" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1057" s="1">
+        <v>70026</v>
+      </c>
+      <c r="C1057" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1057" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1057" s="9">
+        <v>4130</v>
+      </c>
+      <c r="G1057" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1057" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1057" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1058" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1058" s="1">
+        <v>70026</v>
+      </c>
+      <c r="C1058" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1058" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1058" s="9">
+        <v>4131</v>
+      </c>
+      <c r="G1058" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1058" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1058" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1059" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1059" s="1">
+        <v>70027</v>
+      </c>
+      <c r="C1059" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1059" s="9">
+        <v>4133</v>
+      </c>
+      <c r="G1059" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1059" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1059" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1060" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1060" s="1">
+        <v>70027</v>
+      </c>
+      <c r="C1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1060" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1060" s="9">
+        <v>4134</v>
+      </c>
+      <c r="G1060" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1060" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1061" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1061" s="1">
+        <v>70027</v>
+      </c>
+      <c r="C1061" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1061" s="9">
+        <v>4135</v>
+      </c>
+      <c r="G1061" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1061" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1061" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1062" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1062" s="1">
+        <v>70027</v>
+      </c>
+      <c r="C1062" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1062" s="9">
+        <v>4136</v>
+      </c>
+      <c r="G1062" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1062" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1062" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1063" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1063" s="1">
+        <v>70028</v>
+      </c>
+      <c r="C1063" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1063" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1063" s="9">
+        <v>4138</v>
+      </c>
+      <c r="G1063" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1063" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1063" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1064" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1064" s="1">
+        <v>70028</v>
+      </c>
+      <c r="C1064" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1064" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1064" s="9">
+        <v>4139</v>
+      </c>
+      <c r="G1064" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1064" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1064" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1065" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1065" s="1">
+        <v>70028</v>
+      </c>
+      <c r="C1065" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1065" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1065" s="9">
+        <v>4140</v>
+      </c>
+      <c r="G1065" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1065" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1065" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1066" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1066" s="1">
+        <v>70028</v>
+      </c>
+      <c r="C1066" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1066" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1066" s="9">
+        <v>4141</v>
+      </c>
+      <c r="G1066" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1066" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1066" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1067" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1067" s="1">
+        <v>70029</v>
+      </c>
+      <c r="C1067" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1067" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1067" s="9">
+        <v>4143</v>
+      </c>
+      <c r="G1067" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1067" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1067" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1068" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1068" s="1">
+        <v>70029</v>
+      </c>
+      <c r="C1068" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1068" s="9">
+        <v>4144</v>
+      </c>
+      <c r="G1068" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1068" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1068" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1069" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1069" s="1">
+        <v>70029</v>
+      </c>
+      <c r="C1069" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1069" s="9">
+        <v>4145</v>
+      </c>
+      <c r="G1069" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1069" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1069" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1070" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1070" s="1">
+        <v>70029</v>
+      </c>
+      <c r="C1070" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1070" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1070" s="9">
+        <v>4146</v>
+      </c>
+      <c r="G1070" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1070" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1070" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1071" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1071" s="1">
+        <v>70030</v>
+      </c>
+      <c r="C1071" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1071" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1071" s="9">
+        <v>4148</v>
+      </c>
+      <c r="G1071" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1071" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1071" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1072" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1072" s="1">
+        <v>70030</v>
+      </c>
+      <c r="C1072" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1072" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1072" s="9">
+        <v>4149</v>
+      </c>
+      <c r="G1072" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1072" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1072" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1073" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1073" s="1">
+        <v>70030</v>
+      </c>
+      <c r="C1073" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1073" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1073" s="9">
+        <v>4150</v>
+      </c>
+      <c r="G1073" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1073" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1073" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1074" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1074" s="1">
+        <v>70030</v>
+      </c>
+      <c r="C1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1074" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1074" s="9">
+        <v>4151</v>
+      </c>
+      <c r="G1074" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1074" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1075" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1075" s="1">
+        <v>70031</v>
+      </c>
+      <c r="C1075" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1075" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1075" s="9">
+        <v>4153</v>
+      </c>
+      <c r="G1075" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1075" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1075" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1076" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1076" s="1">
+        <v>70031</v>
+      </c>
+      <c r="C1076" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1076" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1076" s="9">
+        <v>4154</v>
+      </c>
+      <c r="G1076" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1076" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1076" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1077" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1077" s="1">
+        <v>70031</v>
+      </c>
+      <c r="C1077" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1077" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1077" s="9">
+        <v>4155</v>
+      </c>
+      <c r="G1077" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1077" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1077" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1078" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1078" s="1">
+        <v>70031</v>
+      </c>
+      <c r="C1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1078" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1078" s="9">
+        <v>4156</v>
+      </c>
+      <c r="G1078" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1078" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1079" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1079" s="1">
+        <v>70032</v>
+      </c>
+      <c r="C1079" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1079" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1079" s="9">
+        <v>4158</v>
+      </c>
+      <c r="G1079" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1079" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1079" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1080" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1080" s="1">
+        <v>70032</v>
+      </c>
+      <c r="C1080" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1080" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1080" s="9">
+        <v>4159</v>
+      </c>
+      <c r="G1080" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1080" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1080" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1081" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1081" s="1">
+        <v>70032</v>
+      </c>
+      <c r="C1081" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1081" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1081" s="9">
+        <v>4160</v>
+      </c>
+      <c r="G1081" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1081" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1081" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1082" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1082" s="1">
+        <v>70032</v>
+      </c>
+      <c r="C1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1082" s="9">
+        <v>4161</v>
+      </c>
+      <c r="G1082" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1082" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3804" uniqueCount="967">
   <si>
     <t>text</t>
   </si>
@@ -2637,6 +2637,553 @@
   <si>
     <t>城门鱼池冬</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+  </si>
+  <si>
+    <t>三明治</t>
+  </si>
+  <si>
+    <t>腌萝卜</t>
+  </si>
+  <si>
+    <t>拉面</t>
+  </si>
+  <si>
+    <t>蜂蜜蛋糕</t>
+  </si>
+  <si>
+    <t>披萨</t>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+  </si>
+  <si>
+    <t>水煮蛋</t>
+  </si>
+  <si>
+    <t>烤肉串</t>
+  </si>
+  <si>
+    <t>饭团</t>
+  </si>
+  <si>
+    <t>面包</t>
+  </si>
+  <si>
+    <t>烤海苔</t>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+  </si>
+  <si>
+    <t>海鲜饭</t>
+  </si>
+  <si>
+    <t>烤玉米</t>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+  </si>
+  <si>
+    <t>烤茄子</t>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>炖菜</t>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+  </si>
+  <si>
+    <t>红菜汤</t>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+  </si>
+  <si>
+    <t>盐烤鲑鱼</t>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+  </si>
+  <si>
+    <t>烤海鳗</t>
+  </si>
+  <si>
+    <t>烤比目鱼</t>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏特加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗姆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇异果汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>菠萝汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜菜汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄油</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓牛奶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉茶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>食物配方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒水配方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸造配方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫配方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>书写配方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>长剑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地之剑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰之刃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁枪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥之枪</t>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
+  </si>
+  <si>
+    <t>铁铠甲</t>
+  </si>
+  <si>
+    <t>红莲之铠</t>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+  </si>
+  <si>
+    <t>钢刃锁甲</t>
+  </si>
+  <si>
+    <t>士兵长靴</t>
+  </si>
+  <si>
+    <t>骑士护胫</t>
+  </si>
+  <si>
+    <t>士兵头盔</t>
+  </si>
+  <si>
+    <t>尖角头盔</t>
+  </si>
+  <si>
+    <t>战争头盔</t>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤鞭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王鞭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>布衣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮铠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁子甲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛皮斗篷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽背心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞铠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗之袍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾风背心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法铠甲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝织长袍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之羽衣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长裙</t>
+  </si>
+  <si>
+    <t>幸运之衣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>布鞋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮鞋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山者之靴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动鞋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵族长靴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道鞋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>贤者之履</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>风神之履</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏浪长靴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草帽</t>
+  </si>
+  <si>
+    <t>暮光草帽</t>
+  </si>
+  <si>
+    <t>法师帽</t>
+  </si>
+  <si>
+    <t>幸运头巾</t>
+  </si>
+  <si>
+    <t>绅士礼帽</t>
+  </si>
+  <si>
+    <t>贵族头巾</t>
+  </si>
+  <si>
+    <t>回春卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>振奋卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>昏睡卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感电卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰氛卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火氛卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉默卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魅惑卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2678,7 +3225,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2709,8 +3256,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2718,11 +3277,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2763,11 +3337,53 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4225,7 +4841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1283"/>
+  <dimension ref="A1:I1435"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -41926,6 +42542,4414 @@
         <v>1</v>
       </c>
       <c r="I1283" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1284" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1284" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1284" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1284" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="E1284" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1284" s="1">
+        <v>3013</v>
+      </c>
+      <c r="G1284" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1284" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1284" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1285" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1285" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1285" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1285" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="E1285" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1285" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G1285" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1285" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1285" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1286" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1286" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1286" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1286" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="E1286" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1286" s="1">
+        <v>3015</v>
+      </c>
+      <c r="G1286" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1286" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1286" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1287" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1287" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1287" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1287" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="E1287" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1287" s="1">
+        <v>3016</v>
+      </c>
+      <c r="G1287" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1287" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1287" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1288" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1288" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1288" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1288" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="E1288" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1288" s="1">
+        <v>3017</v>
+      </c>
+      <c r="G1288" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1288" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1288" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1289" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1289" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1289" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1289" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="E1289" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1289" s="1">
+        <v>3018</v>
+      </c>
+      <c r="G1289" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1289" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1289" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1290" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1290" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1290" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1290" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="E1290" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1290" s="1">
+        <v>3019</v>
+      </c>
+      <c r="G1290" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1290" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1290" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1291" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1291" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1291" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1291" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="E1291" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1291" s="1">
+        <v>3020</v>
+      </c>
+      <c r="G1291" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1291" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1291" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1292" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1292" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1292" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1292" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="E1292" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1292" s="1">
+        <v>3021</v>
+      </c>
+      <c r="G1292" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1292" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1292" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1293" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1293" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1293" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1293" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="E1293" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1293" s="1">
+        <v>3022</v>
+      </c>
+      <c r="G1293" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1293" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1293" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1294" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1294" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1294" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1294" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="E1294" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1294" s="1">
+        <v>3023</v>
+      </c>
+      <c r="G1294" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1294" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1294" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1295" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1295" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1295" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1295" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="E1295" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1295" s="1">
+        <v>3024</v>
+      </c>
+      <c r="G1295" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1295" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1295" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1296" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1296" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1296" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1296" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="E1296" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1296" s="1">
+        <v>3025</v>
+      </c>
+      <c r="G1296" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1296" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1296" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1297" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1297" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1297" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1297" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="E1297" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1297" s="1">
+        <v>3026</v>
+      </c>
+      <c r="G1297" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1297" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1297" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1298" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1298" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1298" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1298" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="E1298" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1298" s="1">
+        <v>3027</v>
+      </c>
+      <c r="G1298" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1298" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1298" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1299" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1299" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1299" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1299" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="E1299" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1299" s="1">
+        <v>3028</v>
+      </c>
+      <c r="G1299" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1299" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1299" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1300" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1300" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1300" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1300" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="E1300" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1300" s="1">
+        <v>3029</v>
+      </c>
+      <c r="G1300" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1300" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1300" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1301" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1301" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1301" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1301" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="E1301" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1301" s="1">
+        <v>3030</v>
+      </c>
+      <c r="G1301" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1301" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1301" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1302" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1302" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1302" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1302" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="E1302" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1302" s="1">
+        <v>3031</v>
+      </c>
+      <c r="G1302" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1302" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1302" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1303" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1303" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1303" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1303" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="E1303" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1303" s="1">
+        <v>3032</v>
+      </c>
+      <c r="G1303" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1303" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1303" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1304" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1304" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1304" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1304" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="E1304" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1304" s="1">
+        <v>3041</v>
+      </c>
+      <c r="G1304" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1304" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1304" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1305" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1305" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1305" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1305" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="E1305" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1305" s="1">
+        <v>3044</v>
+      </c>
+      <c r="G1305" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1305" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1305" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1306" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1306" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1306" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1306" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="E1306" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1306" s="1">
+        <v>3045</v>
+      </c>
+      <c r="G1306" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1306" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1306" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1307" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1307" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1307" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1307" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="E1307" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1307" s="1">
+        <v>3046</v>
+      </c>
+      <c r="G1307" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1307" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1307" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1308" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1308" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1308" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1308" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="E1308" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1308" s="1">
+        <v>3047</v>
+      </c>
+      <c r="G1308" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1308" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1308" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1309" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1309" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1309" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1309" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="E1309" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1309" s="1">
+        <v>3048</v>
+      </c>
+      <c r="G1309" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1309" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1309" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1310" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1310" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1310" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1310" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="E1310" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1310" s="1">
+        <v>3049</v>
+      </c>
+      <c r="G1310" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1310" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1310" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1311" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1311" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1311" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1311" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="E1311" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1311" s="1">
+        <v>3052</v>
+      </c>
+      <c r="G1311" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1311" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1311" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1312" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1312" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1312" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1312" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="E1312" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1312" s="1">
+        <v>3063</v>
+      </c>
+      <c r="G1312" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1312" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1312" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1313" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1313" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1313" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1313" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="E1313" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1313" s="1">
+        <v>3064</v>
+      </c>
+      <c r="G1313" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1313" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1313" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1314" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1314" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1314" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1314" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="E1314" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1314" s="1">
+        <v>3065</v>
+      </c>
+      <c r="G1314" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1314" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1314" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1315" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1315" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1315" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1315" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="E1315" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1315" s="1">
+        <v>3066</v>
+      </c>
+      <c r="G1315" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1315" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1315" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1316" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1316" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1316" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1316" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="E1316" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1316" s="1">
+        <v>3067</v>
+      </c>
+      <c r="G1316" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1316" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1316" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1317" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1317" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1317" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1317" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="E1317" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1317" s="1">
+        <v>3068</v>
+      </c>
+      <c r="G1317" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1317" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1317" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1318" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1318" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1318" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1318" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="E1318" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1318" s="1">
+        <v>3069</v>
+      </c>
+      <c r="G1318" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1318" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1318" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1319" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1319" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1319" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1319" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="E1319" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1319" s="1">
+        <v>3070</v>
+      </c>
+      <c r="G1319" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1319" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1319" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1320" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1320" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1320" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1320" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="E1320" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1320" s="1">
+        <v>3071</v>
+      </c>
+      <c r="G1320" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1320" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1320" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1321" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1321" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1321" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1321" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1321" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1321" s="1">
+        <v>3072</v>
+      </c>
+      <c r="G1321" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1321" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1321" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1322" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1322" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1322" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1322" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="E1322" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1322" s="1">
+        <v>3073</v>
+      </c>
+      <c r="G1322" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1322" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1322" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1323" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1323" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1323" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1323" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="E1323" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1323" s="1">
+        <v>3074</v>
+      </c>
+      <c r="G1323" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1323" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1323" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1324" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1324" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1324" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1324" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="E1324" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1324" s="1">
+        <v>3075</v>
+      </c>
+      <c r="G1324" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1324" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1324" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1325" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1325" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1325" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1325" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="E1325" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1325" s="1">
+        <v>3076</v>
+      </c>
+      <c r="G1325" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1325" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1325" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1326" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1326" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1326" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1326" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="E1326" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1326" s="1">
+        <v>3077</v>
+      </c>
+      <c r="G1326" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1326" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1326" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1327" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1327" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1327" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1327" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="E1327" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1327" s="1">
+        <v>3078</v>
+      </c>
+      <c r="G1327" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1327" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1327" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1328" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1328" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1328" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="E1328" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1328" s="1">
+        <v>3079</v>
+      </c>
+      <c r="G1328" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1328" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1329" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1329" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1329" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1329" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="E1329" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1329" s="1">
+        <v>3080</v>
+      </c>
+      <c r="G1329" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1329" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1329" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1330" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1330" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1330" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1330" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="E1330" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1330" s="1">
+        <v>3081</v>
+      </c>
+      <c r="G1330" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1330" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1330" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1331" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1331" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1331" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1331" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="E1331" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1331" s="1">
+        <v>3082</v>
+      </c>
+      <c r="G1331" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1331" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1331" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1332" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1332" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1332" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1332" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="E1332" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1332" s="1">
+        <v>3083</v>
+      </c>
+      <c r="G1332" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1332" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1332" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1333" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1333" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1333" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1333" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="E1333" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1333" s="1">
+        <v>3084</v>
+      </c>
+      <c r="G1333" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1333" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1333" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1334" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1334" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1334" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1334" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="E1334" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1334" s="1">
+        <v>3085</v>
+      </c>
+      <c r="G1334" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1334" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1334" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1335" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1335" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1335" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1335" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="E1335" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1335" s="1">
+        <v>3086</v>
+      </c>
+      <c r="G1335" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1335" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1335" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1336" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1336" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1336" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1336" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="E1336" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1336" s="1">
+        <v>3087</v>
+      </c>
+      <c r="G1336" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1336" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1336" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1337" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1337" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1337" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1337" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="E1337" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1337" s="1">
+        <v>3088</v>
+      </c>
+      <c r="G1337" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1337" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1337" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1338" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1338" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1338" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1338" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="E1338" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1338" s="1">
+        <v>3089</v>
+      </c>
+      <c r="G1338" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1338" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1338" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1339" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1339" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1339" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1339" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="E1339" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1339" s="1">
+        <v>3090</v>
+      </c>
+      <c r="G1339" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1339" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1339" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1340" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1340" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1340" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1340" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="E1340" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1340" s="1">
+        <v>3091</v>
+      </c>
+      <c r="G1340" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1340" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1340" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1341" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1341" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1341" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1341" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="E1341" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1341" s="18">
+        <v>3043</v>
+      </c>
+      <c r="G1341" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1341" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1341" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1342" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1342" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1342" s="19" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1342" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1342" s="18">
+        <v>3012</v>
+      </c>
+      <c r="G1342" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1342" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1343" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1343" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1343" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1343" s="19" t="s">
+        <v>869</v>
+      </c>
+      <c r="E1343" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1343" s="18">
+        <v>3055</v>
+      </c>
+      <c r="G1343" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1343" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1343" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1344" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1344" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1344" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1344" s="19" t="s">
+        <v>870</v>
+      </c>
+      <c r="E1344" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1344" s="18">
+        <v>3056</v>
+      </c>
+      <c r="G1344" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1344" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1344" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1345" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1345" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1345" s="19" t="s">
+        <v>871</v>
+      </c>
+      <c r="E1345" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1345" s="18">
+        <v>3057</v>
+      </c>
+      <c r="G1345" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1345" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1346" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1346" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1346" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1346" s="19" t="s">
+        <v>872</v>
+      </c>
+      <c r="E1346" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1346" s="18">
+        <v>3058</v>
+      </c>
+      <c r="G1346" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1346" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1346" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1347" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1347" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1347" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1347" s="19" t="s">
+        <v>873</v>
+      </c>
+      <c r="E1347" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1347" s="18">
+        <v>3059</v>
+      </c>
+      <c r="G1347" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1347" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1347" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1348" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1348" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1348" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1348" s="19" t="s">
+        <v>874</v>
+      </c>
+      <c r="E1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1348" s="18">
+        <v>3060</v>
+      </c>
+      <c r="G1348" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1348" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1348" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1349" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1349" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1349" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1349" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="E1349" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1349" s="18">
+        <v>3061</v>
+      </c>
+      <c r="G1349" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1349" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1349" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1350" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1350" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1350" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1350" s="19" t="s">
+        <v>876</v>
+      </c>
+      <c r="E1350" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1350" s="18">
+        <v>3062</v>
+      </c>
+      <c r="G1350" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1350" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1350" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1351" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1351" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1351" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1351" s="19" t="s">
+        <v>877</v>
+      </c>
+      <c r="E1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1351" s="18">
+        <v>3033</v>
+      </c>
+      <c r="G1351" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1351" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1351" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1352" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1352" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1352" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1352" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="E1352" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1352" s="18">
+        <v>3034</v>
+      </c>
+      <c r="G1352" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1352" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1352" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1353" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1353" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1353" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1353" s="19" t="s">
+        <v>879</v>
+      </c>
+      <c r="E1353" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1353" s="18">
+        <v>3035</v>
+      </c>
+      <c r="G1353" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1353" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1353" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1354" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1354" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1354" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1354" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="E1354" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1354" s="18">
+        <v>3036</v>
+      </c>
+      <c r="G1354" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1354" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1354" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1355" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1355" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1355" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1355" s="19" t="s">
+        <v>881</v>
+      </c>
+      <c r="E1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1355" s="18">
+        <v>3037</v>
+      </c>
+      <c r="G1355" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1355" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1355" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1356" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1356" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1356" s="19" t="s">
+        <v>882</v>
+      </c>
+      <c r="E1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1356" s="18">
+        <v>3038</v>
+      </c>
+      <c r="G1356" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1356" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1357" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1357" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1357" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1357" s="19" t="s">
+        <v>883</v>
+      </c>
+      <c r="E1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1357" s="18">
+        <v>3039</v>
+      </c>
+      <c r="G1357" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1357" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1357" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1358" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1358" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1358" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1358" s="19" t="s">
+        <v>884</v>
+      </c>
+      <c r="E1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1358" s="18">
+        <v>3040</v>
+      </c>
+      <c r="G1358" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1358" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1358" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1359" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1359" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1359" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1359" s="19" t="s">
+        <v>885</v>
+      </c>
+      <c r="E1359" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1359" s="18">
+        <v>3042</v>
+      </c>
+      <c r="G1359" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1359" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1359" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1360" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1360" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1360" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1360" s="19" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1360" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1360" s="18">
+        <v>3012</v>
+      </c>
+      <c r="G1360" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1360" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1360" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1361" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1361" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1361" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1361" s="19" t="s">
+        <v>887</v>
+      </c>
+      <c r="E1361" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1361" s="18">
+        <v>3050</v>
+      </c>
+      <c r="G1361" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1361" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1361" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1362" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1362" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1362" s="19" t="s">
+        <v>888</v>
+      </c>
+      <c r="E1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1362" s="18">
+        <v>3051</v>
+      </c>
+      <c r="G1362" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1362" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1363" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1363" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1363" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1363" s="19" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1363" s="18">
+        <v>3053</v>
+      </c>
+      <c r="G1363" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1363" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1363" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1364" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1364" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1364" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1364" s="19" t="s">
+        <v>890</v>
+      </c>
+      <c r="E1364" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1364" s="18">
+        <v>3054</v>
+      </c>
+      <c r="G1364" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1364" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1364" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1365" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1365" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C1365" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1365" s="20" t="s">
+        <v>891</v>
+      </c>
+      <c r="E1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1365" s="18">
+        <v>3092</v>
+      </c>
+      <c r="G1365" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1365" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1365" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1366" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1366" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1366" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1366" s="21" t="s">
+        <v>897</v>
+      </c>
+      <c r="E1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1366">
+        <v>4000</v>
+      </c>
+      <c r="G1366" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1366" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1366" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1367" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1367" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1367" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1367" s="21" t="s">
+        <v>898</v>
+      </c>
+      <c r="E1367" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1367">
+        <v>4001</v>
+      </c>
+      <c r="G1367" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1367" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1367" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1368" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1368" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1368" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1368" s="22" t="s">
+        <v>899</v>
+      </c>
+      <c r="E1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1368">
+        <v>4002</v>
+      </c>
+      <c r="G1368" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1368" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1368" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1369" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1369" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1369" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1369" s="21" t="s">
+        <v>900</v>
+      </c>
+      <c r="E1369" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1369">
+        <v>4003</v>
+      </c>
+      <c r="G1369" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1369" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1369" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1370" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1370" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1370" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1370" s="21" t="s">
+        <v>901</v>
+      </c>
+      <c r="E1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1370">
+        <v>4004</v>
+      </c>
+      <c r="G1370" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1370" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1370" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1371" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1371" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1371" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1371" s="21" t="s">
+        <v>902</v>
+      </c>
+      <c r="E1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1371">
+        <v>4005</v>
+      </c>
+      <c r="G1371" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1371" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1371" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1372" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1372" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1372" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1372" s="21" t="s">
+        <v>903</v>
+      </c>
+      <c r="E1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1372">
+        <v>4006</v>
+      </c>
+      <c r="G1372" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1372" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1372" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1373" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1373" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1373" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1373" s="21" t="s">
+        <v>904</v>
+      </c>
+      <c r="E1373" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1373">
+        <v>4007</v>
+      </c>
+      <c r="G1373" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1373" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1373" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1374" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1374" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1374" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1374" s="21" t="s">
+        <v>905</v>
+      </c>
+      <c r="E1374" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1374">
+        <v>4008</v>
+      </c>
+      <c r="G1374" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1374" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1374" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1375" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1375" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1375" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1375" s="23" t="s">
+        <v>906</v>
+      </c>
+      <c r="E1375" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1375">
+        <v>4009</v>
+      </c>
+      <c r="G1375" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1375" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1375" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1376" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1376" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1376" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1376" s="23" t="s">
+        <v>907</v>
+      </c>
+      <c r="E1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1376">
+        <v>4010</v>
+      </c>
+      <c r="G1376" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1376" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1376" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1377" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1377" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1377" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1377" s="21" t="s">
+        <v>908</v>
+      </c>
+      <c r="E1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1377">
+        <v>4011</v>
+      </c>
+      <c r="G1377" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1377" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1377" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1378" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1378" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1378" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1378" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="E1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1378">
+        <v>4012</v>
+      </c>
+      <c r="G1378" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1378" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1378" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1379" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1379" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1379" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1379" s="21" t="s">
+        <v>910</v>
+      </c>
+      <c r="E1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1379">
+        <v>4013</v>
+      </c>
+      <c r="G1379" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1379" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1379" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1380" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1380" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1380" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="E1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1380">
+        <v>4014</v>
+      </c>
+      <c r="G1380" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1380" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1381" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1381" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1381" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1381" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="E1381" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1381">
+        <v>4019</v>
+      </c>
+      <c r="G1381" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1381" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1381" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1382" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1382" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1382" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1382" s="12" t="s">
+        <v>913</v>
+      </c>
+      <c r="E1382" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1382">
+        <v>4020</v>
+      </c>
+      <c r="G1382" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1382" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1382" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1383" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1383" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1383" s="12" t="s">
+        <v>914</v>
+      </c>
+      <c r="E1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1383">
+        <v>4025</v>
+      </c>
+      <c r="G1383" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1383" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1384" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1384" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1384" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1384" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="E1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1384">
+        <v>4026</v>
+      </c>
+      <c r="G1384" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1384" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1384" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1385" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1385" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1385" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1385" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1385" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1385">
+        <v>4027</v>
+      </c>
+      <c r="G1385" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1385" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1385" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1386" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1386" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1386" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1386" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="E1386" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1386">
+        <v>4033</v>
+      </c>
+      <c r="G1386" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1386" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1386" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1387" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1387" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1387" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1387" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1387">
+        <v>4040</v>
+      </c>
+      <c r="G1387" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1387" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1387" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1388" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1388" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1388" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1388" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="E1388" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1388">
+        <v>4045</v>
+      </c>
+      <c r="G1388" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1388" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1388" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1389" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1389" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1389" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="E1389" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1389">
+        <v>4052</v>
+      </c>
+      <c r="G1389" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1389" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1390" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1390" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1390" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1390" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="E1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1390">
+        <v>4053</v>
+      </c>
+      <c r="G1390" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1390" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1390" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1391" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1391" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C1391" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1391" s="12" t="s">
+        <v>922</v>
+      </c>
+      <c r="E1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1391">
+        <v>4057</v>
+      </c>
+      <c r="G1391" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1391" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1391" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1392" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1392" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1392" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1392" s="21" t="s">
+        <v>923</v>
+      </c>
+      <c r="E1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1392" s="1">
+        <v>4015</v>
+      </c>
+      <c r="G1392" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1392" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1392" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1393" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1393" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1393" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1393" s="21" t="s">
+        <v>924</v>
+      </c>
+      <c r="E1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1393" s="1">
+        <v>4016</v>
+      </c>
+      <c r="G1393" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1393" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1393" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1394" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1394" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1394" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1394" s="21" t="s">
+        <v>925</v>
+      </c>
+      <c r="E1394" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1394" s="1">
+        <v>4017</v>
+      </c>
+      <c r="G1394" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1394" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1394" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1395" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1395" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1395" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1395" s="21" t="s">
+        <v>926</v>
+      </c>
+      <c r="E1395" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1395" s="1">
+        <v>4018</v>
+      </c>
+      <c r="G1395" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1395" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1395" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1396" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1396" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1396" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1396" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="E1396" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1396" s="1">
+        <v>4021</v>
+      </c>
+      <c r="G1396" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1396" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1396" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1397" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1397" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1397" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1397" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="E1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1397" s="1">
+        <v>4022</v>
+      </c>
+      <c r="G1397" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1397" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1397" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1398" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1398" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1398" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1398" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="E1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1398" s="1">
+        <v>4023</v>
+      </c>
+      <c r="G1398" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1398" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1398" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1399" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1399" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1399" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1399" s="22" t="s">
+        <v>930</v>
+      </c>
+      <c r="E1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1399" s="1">
+        <v>4024</v>
+      </c>
+      <c r="G1399" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1399" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1399" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1400" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1400" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1400" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1400" s="22" t="s">
+        <v>931</v>
+      </c>
+      <c r="E1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1400" s="1">
+        <v>4028</v>
+      </c>
+      <c r="G1400" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1400" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1400" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1401" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1401" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1401" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1401" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1401" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1401" s="1">
+        <v>4029</v>
+      </c>
+      <c r="G1401" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1401" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1401" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1402" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1402" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1402" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1402" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="E1402" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1402" s="1">
+        <v>4030</v>
+      </c>
+      <c r="G1402" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1402" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1402" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1403" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1403" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1403" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1403" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="E1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1403" s="1">
+        <v>4031</v>
+      </c>
+      <c r="G1403" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1403" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1403" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1404" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1404" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1404" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1404" s="22" t="s">
+        <v>935</v>
+      </c>
+      <c r="E1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1404" s="1">
+        <v>4032</v>
+      </c>
+      <c r="G1404" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1404" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1404" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1405" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1405" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1405" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1405" s="22" t="s">
+        <v>936</v>
+      </c>
+      <c r="E1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1405" s="1">
+        <v>4034</v>
+      </c>
+      <c r="G1405" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1405" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1405" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1406" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1406" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1406" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1406" s="22" t="s">
+        <v>937</v>
+      </c>
+      <c r="E1406" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1406" s="1">
+        <v>4035</v>
+      </c>
+      <c r="G1406" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1406" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1406" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1407" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1407" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1407" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1407" s="22" t="s">
+        <v>938</v>
+      </c>
+      <c r="E1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1407" s="1">
+        <v>4036</v>
+      </c>
+      <c r="G1407" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1407" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1407" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1408" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1408" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1408" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1408" s="11" t="s">
+        <v>939</v>
+      </c>
+      <c r="E1408" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1408" s="1">
+        <v>4037</v>
+      </c>
+      <c r="G1408" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1408" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1408" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1409" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1409" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1409" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1409" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="E1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1409" s="1">
+        <v>4038</v>
+      </c>
+      <c r="G1409" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1409" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1409" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1410" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1410" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1410" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1410" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="E1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1410" s="1">
+        <v>4039</v>
+      </c>
+      <c r="G1410" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1410" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1410" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1411" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1411" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1411" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1411" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="E1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1411" s="1">
+        <v>4041</v>
+      </c>
+      <c r="G1411" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1411" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1411" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1412" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1412" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1412" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1412" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="E1412" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1412" s="1">
+        <v>4042</v>
+      </c>
+      <c r="G1412" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1412" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1412" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1413" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1413" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1413" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1413" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="E1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1413" s="1">
+        <v>4043</v>
+      </c>
+      <c r="G1413" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1413" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1413" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1414" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1414" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1414" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1414" s="11" t="s">
+        <v>945</v>
+      </c>
+      <c r="E1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1414" s="1">
+        <v>4044</v>
+      </c>
+      <c r="G1414" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1414" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1414" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1415" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1415" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1415" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1415" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="E1415" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1415" s="1">
+        <v>4046</v>
+      </c>
+      <c r="G1415" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1415" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1415" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1416" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1416" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1416" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1416" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="E1416" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1416" s="1">
+        <v>4047</v>
+      </c>
+      <c r="G1416" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1416" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1416" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1417" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1417" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1417" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1417" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="E1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1417" s="1">
+        <v>4048</v>
+      </c>
+      <c r="G1417" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1417" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1417" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1418" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1418" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1418" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>949</v>
+      </c>
+      <c r="E1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1418" s="1">
+        <v>4049</v>
+      </c>
+      <c r="G1418" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1418" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1418" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1419" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1419" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1419" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>950</v>
+      </c>
+      <c r="E1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1419" s="1">
+        <v>4050</v>
+      </c>
+      <c r="G1419" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1419" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1419" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1420" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1420" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1420" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>951</v>
+      </c>
+      <c r="E1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1420" s="1">
+        <v>4051</v>
+      </c>
+      <c r="G1420" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1420" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1420" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1421" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1421" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1421" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>952</v>
+      </c>
+      <c r="E1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1421" s="1">
+        <v>4054</v>
+      </c>
+      <c r="G1421" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1421" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1421" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1422" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1422" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1422" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>953</v>
+      </c>
+      <c r="E1422" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1422" s="1">
+        <v>4055</v>
+      </c>
+      <c r="G1422" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1422" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1422" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1423" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1423" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C1423" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>954</v>
+      </c>
+      <c r="E1423" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1423" s="1">
+        <v>4056</v>
+      </c>
+      <c r="G1423" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1423" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1423" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1424" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1424" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1424" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1424" s="24" t="s">
+        <v>955</v>
+      </c>
+      <c r="E1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1424">
+        <v>2100</v>
+      </c>
+      <c r="G1424" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1424" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1424" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1425" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1425" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1425" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1425" s="24" t="s">
+        <v>956</v>
+      </c>
+      <c r="E1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1425">
+        <v>2101</v>
+      </c>
+      <c r="G1425" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1425" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1425" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1426" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1426" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1426" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1426" s="24" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1426">
+        <v>2102</v>
+      </c>
+      <c r="G1426" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1426" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1426" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1427" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1427" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1427" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1427" s="24" t="s">
+        <v>958</v>
+      </c>
+      <c r="E1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1427">
+        <v>2103</v>
+      </c>
+      <c r="G1427" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1427" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1427" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1428" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1428" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1428" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1428" s="24" t="s">
+        <v>959</v>
+      </c>
+      <c r="E1428" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1428">
+        <v>2104</v>
+      </c>
+      <c r="G1428" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1428" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1428" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1429" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1429" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1429" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1429" s="24" t="s">
+        <v>960</v>
+      </c>
+      <c r="E1429" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1429">
+        <v>2105</v>
+      </c>
+      <c r="G1429" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1429" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1429" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1430" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1430" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1430" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1430" s="24" t="s">
+        <v>961</v>
+      </c>
+      <c r="E1430" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1430">
+        <v>2106</v>
+      </c>
+      <c r="G1430" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1430" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1430" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1431" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1431" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1431" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1431" s="24" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1431" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1431">
+        <v>2107</v>
+      </c>
+      <c r="G1431" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1431" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1431" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1432" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1432" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1432" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1432" s="24" t="s">
+        <v>963</v>
+      </c>
+      <c r="E1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1432">
+        <v>2108</v>
+      </c>
+      <c r="G1432" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1432" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1432" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1433" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1433" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1433" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1433" s="24" t="s">
+        <v>964</v>
+      </c>
+      <c r="E1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1433">
+        <v>2109</v>
+      </c>
+      <c r="G1433" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1433" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1433" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1434" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1434" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1434" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1434" s="24" t="s">
+        <v>965</v>
+      </c>
+      <c r="E1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1434">
+        <v>2110</v>
+      </c>
+      <c r="G1434" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1434" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1434" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1435" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1435" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C1435" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1435" s="24" t="s">
+        <v>966</v>
+      </c>
+      <c r="E1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1435">
+        <v>2111</v>
+      </c>
+      <c r="G1435" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H1435" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1435" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/GameRandomDataList.xlsx
+++ b/Datas/GameRandomDataList.xlsx
@@ -3362,28 +3362,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4940,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -4969,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -4998,7 +4977,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -5027,7 +5006,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -5056,7 +5035,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -5085,7 +5064,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
@@ -5114,7 +5093,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -5143,7 +5122,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -5172,7 +5151,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -5201,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
@@ -5230,7 +5209,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -5259,7 +5238,7 @@
         <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -5288,7 +5267,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -5317,7 +5296,7 @@
         <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -5346,7 +5325,7 @@
         <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
@@ -5375,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -5404,7 +5383,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -5433,7 +5412,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -5462,7 +5441,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -5491,7 +5470,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -5520,7 +5499,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -5549,7 +5528,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -5578,7 +5557,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -5607,7 +5586,7 @@
         <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
@@ -5636,7 +5615,7 @@
         <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
@@ -5665,7 +5644,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H29" s="1">
         <v>1</v>
@@ -5694,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -5723,7 +5702,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H31" s="1">
         <v>1</v>
@@ -5752,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -5781,7 +5760,7 @@
         <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -5810,7 +5789,7 @@
         <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -5839,7 +5818,7 @@
         <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -5868,7 +5847,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -5897,7 +5876,7 @@
         <v>9</v>
       </c>
       <c r="G37" s="1">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H37" s="1">
         <v>1</v>
@@ -5926,7 +5905,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="1">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
